--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755528</v>
+        <v>125755409</v>
       </c>
       <c r="B9" t="n">
-        <v>78634</v>
+        <v>79585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483525</v>
+        <v>483587</v>
       </c>
       <c r="R9" t="n">
-        <v>6829111</v>
+        <v>6829364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755409</v>
+        <v>125755528</v>
       </c>
       <c r="B10" t="n">
-        <v>79585</v>
+        <v>78634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483587</v>
+        <v>483525</v>
       </c>
       <c r="R10" t="n">
-        <v>6829364</v>
+        <v>6829111</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125746158</v>
+        <v>125755442</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5663,34 +5663,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483342</v>
+        <v>483201</v>
       </c>
       <c r="R53" t="n">
-        <v>6828971</v>
+        <v>6828916</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5737,19 +5737,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755483</v>
+        <v>125746158</v>
       </c>
       <c r="B54" t="n">
         <v>78967</v>
@@ -5780,14 +5780,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>482971</v>
+        <v>483342</v>
       </c>
       <c r="R54" t="n">
-        <v>6828738</v>
+        <v>6828971</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5834,44 +5834,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755437</v>
+        <v>125755458</v>
       </c>
       <c r="B55" t="n">
-        <v>80071</v>
+        <v>58325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>103044</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483307</v>
+        <v>483319</v>
       </c>
       <c r="R55" t="n">
-        <v>6829287</v>
+        <v>6829293</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755491</v>
+        <v>125755483</v>
       </c>
       <c r="B56" t="n">
         <v>78967</v>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483015</v>
+        <v>482971</v>
       </c>
       <c r="R56" t="n">
-        <v>6828753</v>
+        <v>6828738</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6040,32 +6040,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755458</v>
+        <v>125755437</v>
       </c>
       <c r="B57" t="n">
-        <v>58325</v>
+        <v>80071</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103044</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483319</v>
+        <v>483307</v>
       </c>
       <c r="R57" t="n">
-        <v>6829293</v>
+        <v>6829287</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755442</v>
+        <v>125755491</v>
       </c>
       <c r="B58" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483201</v>
+        <v>483015</v>
       </c>
       <c r="R58" t="n">
-        <v>6828916</v>
+        <v>6828753</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7015,50 +7015,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755431</v>
+        <v>125755533</v>
       </c>
       <c r="B67" t="n">
-        <v>56843</v>
+        <v>78373</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483099</v>
+        <v>483472</v>
       </c>
       <c r="R67" t="n">
-        <v>6828858</v>
+        <v>6829305</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7117,10 +7112,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755433</v>
+        <v>125755517</v>
       </c>
       <c r="B68" t="n">
-        <v>57811</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7128,21 +7123,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7152,10 +7147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483307</v>
+        <v>483386</v>
       </c>
       <c r="R68" t="n">
-        <v>6829287</v>
+        <v>6829003</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7214,45 +7209,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755525</v>
+        <v>125755431</v>
       </c>
       <c r="B69" t="n">
-        <v>78634</v>
+        <v>56843</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483442</v>
+        <v>483099</v>
       </c>
       <c r="R69" t="n">
-        <v>6829028</v>
+        <v>6828858</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7311,10 +7311,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755533</v>
+        <v>125755433</v>
       </c>
       <c r="B70" t="n">
-        <v>78373</v>
+        <v>57811</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7322,21 +7322,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483472</v>
+        <v>483307</v>
       </c>
       <c r="R70" t="n">
-        <v>6829305</v>
+        <v>6829287</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755517</v>
+        <v>125755525</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483386</v>
+        <v>483442</v>
       </c>
       <c r="R71" t="n">
-        <v>6829003</v>
+        <v>6829028</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755424</v>
+        <v>125755412</v>
       </c>
       <c r="B72" t="n">
-        <v>78999</v>
+        <v>79585</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,21 +7516,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483162</v>
+        <v>482912</v>
       </c>
       <c r="R72" t="n">
-        <v>6828879</v>
+        <v>6828922</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125748016</v>
+        <v>125755472</v>
       </c>
       <c r="B73" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7613,39 +7613,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483071</v>
+        <v>483203</v>
       </c>
       <c r="R73" t="n">
-        <v>6828797</v>
+        <v>6829189</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7692,22 +7687,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755412</v>
+        <v>125755489</v>
       </c>
       <c r="B74" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7715,21 +7710,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7739,10 +7734,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>482912</v>
+        <v>483001</v>
       </c>
       <c r="R74" t="n">
-        <v>6828922</v>
+        <v>6828740</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7801,10 +7796,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755472</v>
+        <v>125755451</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7812,21 +7807,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7836,10 +7831,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483203</v>
+        <v>483278</v>
       </c>
       <c r="R75" t="n">
-        <v>6829189</v>
+        <v>6828932</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7898,10 +7893,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755489</v>
+        <v>125748016</v>
       </c>
       <c r="B76" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,34 +7904,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483001</v>
+        <v>483071</v>
       </c>
       <c r="R76" t="n">
-        <v>6828740</v>
+        <v>6828797</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7983,22 +7983,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755451</v>
+        <v>125755424</v>
       </c>
       <c r="B77" t="n">
-        <v>78725</v>
+        <v>78999</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483278</v>
+        <v>483162</v>
       </c>
       <c r="R77" t="n">
-        <v>6828932</v>
+        <v>6828879</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125755426</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125755430</v>
       </c>
       <c r="B8" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755409</v>
+        <v>125755528</v>
       </c>
       <c r="B9" t="n">
-        <v>79585</v>
+        <v>78634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483587</v>
+        <v>483525</v>
       </c>
       <c r="R9" t="n">
-        <v>6829364</v>
+        <v>6829111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755528</v>
+        <v>125755409</v>
       </c>
       <c r="B10" t="n">
-        <v>78634</v>
+        <v>79585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483525</v>
+        <v>483587</v>
       </c>
       <c r="R10" t="n">
-        <v>6829111</v>
+        <v>6829364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755438</v>
+        <v>125755439</v>
       </c>
       <c r="B12" t="n">
-        <v>78991</v>
+        <v>78726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483600</v>
+        <v>483586</v>
       </c>
       <c r="R12" t="n">
-        <v>6829152</v>
+        <v>6829364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755452</v>
+        <v>125755438</v>
       </c>
       <c r="B13" t="n">
-        <v>78725</v>
+        <v>78991</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483587</v>
+        <v>483600</v>
       </c>
       <c r="R13" t="n">
-        <v>6829364</v>
+        <v>6829152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755439</v>
+        <v>125755452</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483586</v>
+        <v>483587</v>
       </c>
       <c r="R14" t="n">
         <v>6829364</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125746064</v>
+        <v>125755488</v>
       </c>
       <c r="B15" t="n">
         <v>78967</v>
@@ -1977,14 +1977,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483474</v>
+        <v>483019</v>
       </c>
       <c r="R15" t="n">
-        <v>6829119</v>
+        <v>6828737</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,22 +2031,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125746931</v>
+        <v>125755416</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,34 +2054,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483156</v>
+        <v>483454</v>
       </c>
       <c r="R16" t="n">
-        <v>6828728</v>
+        <v>6829082</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,11 +2116,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2133,22 +2128,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755416</v>
+        <v>125755475</v>
       </c>
       <c r="B17" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483454</v>
+        <v>483169</v>
       </c>
       <c r="R17" t="n">
-        <v>6829082</v>
+        <v>6829132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755488</v>
+        <v>125746064</v>
       </c>
       <c r="B18" t="n">
         <v>78967</v>
@@ -2273,14 +2268,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483019</v>
+        <v>483474</v>
       </c>
       <c r="R18" t="n">
-        <v>6828737</v>
+        <v>6829119</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,19 +2322,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755475</v>
+        <v>125746931</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2370,14 +2365,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483169</v>
+        <v>483156</v>
       </c>
       <c r="R19" t="n">
-        <v>6829132</v>
+        <v>6828728</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2412,6 +2407,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2424,22 +2424,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125745798</v>
+        <v>125755421</v>
       </c>
       <c r="B20" t="n">
-        <v>79585</v>
+        <v>78999</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483474</v>
+        <v>483044</v>
       </c>
       <c r="R20" t="n">
-        <v>6829119</v>
+        <v>6828792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,22 +2521,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755421</v>
+        <v>125745798</v>
       </c>
       <c r="B21" t="n">
-        <v>78999</v>
+        <v>79585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483044</v>
+        <v>483474</v>
       </c>
       <c r="R21" t="n">
-        <v>6828792</v>
+        <v>6829119</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2618,22 +2618,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755440</v>
+        <v>125755445</v>
       </c>
       <c r="B22" t="n">
-        <v>78726</v>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482960</v>
+        <v>482900</v>
       </c>
       <c r="R22" t="n">
-        <v>6828991</v>
+        <v>6828861</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755506</v>
+        <v>125755480</v>
       </c>
       <c r="B23" t="n">
         <v>78967</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483162</v>
+        <v>482885</v>
       </c>
       <c r="R23" t="n">
-        <v>6828887</v>
+        <v>6828897</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755480</v>
+        <v>125755494</v>
       </c>
       <c r="B24" t="n">
         <v>78967</v>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482885</v>
+        <v>483047</v>
       </c>
       <c r="R24" t="n">
-        <v>6828897</v>
+        <v>6828790</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755494</v>
+        <v>125755506</v>
       </c>
       <c r="B25" t="n">
         <v>78967</v>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483047</v>
+        <v>483162</v>
       </c>
       <c r="R25" t="n">
-        <v>6828790</v>
+        <v>6828887</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755445</v>
+        <v>125755440</v>
       </c>
       <c r="B26" t="n">
-        <v>80070</v>
+        <v>78726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482900</v>
+        <v>482960</v>
       </c>
       <c r="R26" t="n">
-        <v>6828861</v>
+        <v>6828991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755516</v>
+        <v>125755428</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483291</v>
+        <v>483280</v>
       </c>
       <c r="R30" t="n">
-        <v>6828969</v>
+        <v>6828942</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755428</v>
+        <v>125755516</v>
       </c>
       <c r="B32" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483280</v>
+        <v>483291</v>
       </c>
       <c r="R32" t="n">
-        <v>6828942</v>
+        <v>6828969</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755460</v>
+        <v>125755473</v>
       </c>
       <c r="B33" t="n">
-        <v>91380</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>482913</v>
+        <v>483182</v>
       </c>
       <c r="R33" t="n">
-        <v>6829095</v>
+        <v>6829175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755502</v>
+        <v>125755411</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483078</v>
+        <v>482945</v>
       </c>
       <c r="R34" t="n">
-        <v>6828839</v>
+        <v>6829125</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755473</v>
+        <v>125755502</v>
       </c>
       <c r="B35" t="n">
         <v>78967</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483182</v>
+        <v>483078</v>
       </c>
       <c r="R35" t="n">
-        <v>6829175</v>
+        <v>6828839</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,32 +3988,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755411</v>
+        <v>125755460</v>
       </c>
       <c r="B36" t="n">
-        <v>79585</v>
+        <v>91387</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>482945</v>
+        <v>482913</v>
       </c>
       <c r="R36" t="n">
-        <v>6829125</v>
+        <v>6829095</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125747249</v>
+        <v>125755501</v>
       </c>
       <c r="B39" t="n">
         <v>78967</v>
@@ -4310,14 +4310,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R39" t="n">
-        <v>6828658</v>
+        <v>6828833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4352,11 +4352,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4369,19 +4364,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125747099</v>
+        <v>125755482</v>
       </c>
       <c r="B40" t="n">
         <v>78967</v>
@@ -4412,14 +4407,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483090</v>
+        <v>482960</v>
       </c>
       <c r="R40" t="n">
-        <v>6828658</v>
+        <v>6828769</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,19 +4461,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125746848</v>
+        <v>125747249</v>
       </c>
       <c r="B41" t="n">
         <v>78967</v>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483247</v>
+        <v>483032</v>
       </c>
       <c r="R41" t="n">
-        <v>6828848</v>
+        <v>6828658</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4549,6 +4544,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4672,7 +4672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755501</v>
+        <v>125747099</v>
       </c>
       <c r="B43" t="n">
         <v>78967</v>
@@ -4703,14 +4703,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483071</v>
+        <v>483090</v>
       </c>
       <c r="R43" t="n">
-        <v>6828833</v>
+        <v>6828658</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4757,19 +4757,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755464</v>
+        <v>125746848</v>
       </c>
       <c r="B44" t="n">
         <v>78967</v>
@@ -4800,14 +4800,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483423</v>
+        <v>483247</v>
       </c>
       <c r="R44" t="n">
-        <v>6829325</v>
+        <v>6828848</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4854,19 +4854,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755508</v>
+        <v>125755464</v>
       </c>
       <c r="B45" t="n">
         <v>78967</v>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483189</v>
+        <v>483423</v>
       </c>
       <c r="R45" t="n">
-        <v>6828911</v>
+        <v>6829325</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755482</v>
+        <v>125755508</v>
       </c>
       <c r="B46" t="n">
         <v>78967</v>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>482960</v>
+        <v>483189</v>
       </c>
       <c r="R46" t="n">
-        <v>6828769</v>
+        <v>6828911</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755466</v>
+        <v>125755536</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,34 +5071,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483400</v>
+        <v>483037</v>
       </c>
       <c r="R47" t="n">
-        <v>6829318</v>
+        <v>6828775</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5131,6 +5136,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5157,10 +5167,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755456</v>
+        <v>125755466</v>
       </c>
       <c r="B48" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5178,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5202,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483114</v>
+        <v>483400</v>
       </c>
       <c r="R48" t="n">
-        <v>6828865</v>
+        <v>6829318</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,7 +5264,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755510</v>
+        <v>125755500</v>
       </c>
       <c r="B49" t="n">
         <v>78967</v>
@@ -5289,10 +5299,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483191</v>
+        <v>483068</v>
       </c>
       <c r="R49" t="n">
-        <v>6828929</v>
+        <v>6828819</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,7 +5458,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755500</v>
+        <v>125755510</v>
       </c>
       <c r="B51" t="n">
         <v>78967</v>
@@ -5483,10 +5493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483068</v>
+        <v>483191</v>
       </c>
       <c r="R51" t="n">
-        <v>6828819</v>
+        <v>6828929</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5545,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755536</v>
+        <v>125755456</v>
       </c>
       <c r="B52" t="n">
-        <v>57651</v>
+        <v>78725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,39 +5566,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483037</v>
+        <v>483114</v>
       </c>
       <c r="R52" t="n">
-        <v>6828775</v>
+        <v>6828865</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5621,11 +5626,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5652,10 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755442</v>
+        <v>125755483</v>
       </c>
       <c r="B53" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5663,21 +5663,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483201</v>
+        <v>482971</v>
       </c>
       <c r="R53" t="n">
-        <v>6828916</v>
+        <v>6828738</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125746158</v>
+        <v>125755437</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,34 +5760,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483342</v>
+        <v>483307</v>
       </c>
       <c r="R54" t="n">
-        <v>6828971</v>
+        <v>6829287</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5834,44 +5834,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755458</v>
+        <v>125755491</v>
       </c>
       <c r="B55" t="n">
-        <v>58325</v>
+        <v>78967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483319</v>
+        <v>483015</v>
       </c>
       <c r="R55" t="n">
-        <v>6829293</v>
+        <v>6828753</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755483</v>
+        <v>125746158</v>
       </c>
       <c r="B56" t="n">
         <v>78967</v>
@@ -5974,14 +5974,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>482971</v>
+        <v>483342</v>
       </c>
       <c r="R56" t="n">
-        <v>6828738</v>
+        <v>6828971</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,44 +6028,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755437</v>
+        <v>125755458</v>
       </c>
       <c r="B57" t="n">
-        <v>80071</v>
+        <v>58325</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>103044</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483307</v>
+        <v>483319</v>
       </c>
       <c r="R57" t="n">
-        <v>6829287</v>
+        <v>6829293</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755491</v>
+        <v>125755442</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483015</v>
+        <v>483201</v>
       </c>
       <c r="R58" t="n">
-        <v>6828753</v>
+        <v>6828916</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6234,7 +6234,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755492</v>
+        <v>125755498</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R59" t="n">
-        <v>6828773</v>
+        <v>6828809</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,45 +6331,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755498</v>
+        <v>125755432</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483071</v>
+        <v>483446</v>
       </c>
       <c r="R60" t="n">
-        <v>6828809</v>
+        <v>6829026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6525,50 +6530,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755432</v>
+        <v>125755492</v>
       </c>
       <c r="B62" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483446</v>
+        <v>483032</v>
       </c>
       <c r="R62" t="n">
-        <v>6829026</v>
+        <v>6828773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755459</v>
+        <v>125755463</v>
       </c>
       <c r="B63" t="n">
-        <v>91234</v>
+        <v>78967</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483398</v>
+        <v>483450</v>
       </c>
       <c r="R63" t="n">
-        <v>6829316</v>
+        <v>6829306</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755419</v>
+        <v>125755496</v>
       </c>
       <c r="B64" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6735,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483005</v>
+        <v>483054</v>
       </c>
       <c r="R64" t="n">
-        <v>6828754</v>
+        <v>6828788</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755496</v>
+        <v>125755459</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>91241</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483054</v>
+        <v>483398</v>
       </c>
       <c r="R65" t="n">
-        <v>6828788</v>
+        <v>6829316</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755463</v>
+        <v>125755419</v>
       </c>
       <c r="B66" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6929,21 +6929,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483450</v>
+        <v>483005</v>
       </c>
       <c r="R66" t="n">
-        <v>6829306</v>
+        <v>6828754</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755533</v>
+        <v>125755525</v>
       </c>
       <c r="B67" t="n">
-        <v>78373</v>
+        <v>78634</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483472</v>
+        <v>483442</v>
       </c>
       <c r="R67" t="n">
-        <v>6829305</v>
+        <v>6829028</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,45 +7112,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755517</v>
+        <v>125755431</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483386</v>
+        <v>483099</v>
       </c>
       <c r="R68" t="n">
-        <v>6829003</v>
+        <v>6828858</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7209,50 +7214,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755431</v>
+        <v>125755433</v>
       </c>
       <c r="B69" t="n">
-        <v>56843</v>
+        <v>57811</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483099</v>
+        <v>483307</v>
       </c>
       <c r="R69" t="n">
-        <v>6828858</v>
+        <v>6829287</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7311,10 +7311,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755433</v>
+        <v>125755533</v>
       </c>
       <c r="B70" t="n">
-        <v>57811</v>
+        <v>78373</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7322,21 +7322,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483307</v>
+        <v>483472</v>
       </c>
       <c r="R70" t="n">
-        <v>6829287</v>
+        <v>6829305</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755525</v>
+        <v>125755517</v>
       </c>
       <c r="B71" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483442</v>
+        <v>483386</v>
       </c>
       <c r="R71" t="n">
-        <v>6829028</v>
+        <v>6829003</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755412</v>
+        <v>125748016</v>
       </c>
       <c r="B72" t="n">
-        <v>79585</v>
+        <v>57651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,34 +7516,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>482912</v>
+        <v>483071</v>
       </c>
       <c r="R72" t="n">
-        <v>6828922</v>
+        <v>6828797</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7590,22 +7595,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755472</v>
+        <v>125755424</v>
       </c>
       <c r="B73" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7613,21 +7618,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7637,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483203</v>
+        <v>483162</v>
       </c>
       <c r="R73" t="n">
-        <v>6829189</v>
+        <v>6828879</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7699,10 +7704,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755489</v>
+        <v>125755441</v>
       </c>
       <c r="B74" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7710,21 +7715,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7734,10 +7739,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483001</v>
+        <v>483114</v>
       </c>
       <c r="R74" t="n">
-        <v>6828740</v>
+        <v>6828865</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7796,10 +7801,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755451</v>
+        <v>125755489</v>
       </c>
       <c r="B75" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,21 +7812,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7831,10 +7836,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483278</v>
+        <v>483001</v>
       </c>
       <c r="R75" t="n">
-        <v>6828932</v>
+        <v>6828740</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7893,10 +7898,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125748016</v>
+        <v>125755451</v>
       </c>
       <c r="B76" t="n">
-        <v>57651</v>
+        <v>78725</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7904,39 +7909,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483071</v>
+        <v>483278</v>
       </c>
       <c r="R76" t="n">
-        <v>6828797</v>
+        <v>6828932</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7983,22 +7983,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755424</v>
+        <v>125755412</v>
       </c>
       <c r="B77" t="n">
-        <v>78999</v>
+        <v>79585</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483162</v>
+        <v>482912</v>
       </c>
       <c r="R77" t="n">
-        <v>6828879</v>
+        <v>6828922</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8092,10 +8092,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755441</v>
+        <v>125755472</v>
       </c>
       <c r="B78" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8103,21 +8103,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483114</v>
+        <v>483203</v>
       </c>
       <c r="R78" t="n">
-        <v>6828865</v>
+        <v>6829189</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8189,10 +8189,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755522</v>
+        <v>125755503</v>
       </c>
       <c r="B79" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8200,21 +8200,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483303</v>
+        <v>483095</v>
       </c>
       <c r="R79" t="n">
-        <v>6829017</v>
+        <v>6828845</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,7 +8286,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755515</v>
+        <v>125755518</v>
       </c>
       <c r="B80" t="n">
         <v>78967</v>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483280</v>
+        <v>483467</v>
       </c>
       <c r="R80" t="n">
-        <v>6828952</v>
+        <v>6829027</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8383,7 +8383,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755514</v>
+        <v>125755515</v>
       </c>
       <c r="B81" t="n">
         <v>78967</v>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483220</v>
+        <v>483280</v>
       </c>
       <c r="R81" t="n">
-        <v>6828907</v>
+        <v>6828952</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755518</v>
+        <v>125755514</v>
       </c>
       <c r="B82" t="n">
         <v>78967</v>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483467</v>
+        <v>483220</v>
       </c>
       <c r="R82" t="n">
-        <v>6829027</v>
+        <v>6828907</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,7 +8577,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755503</v>
+        <v>125755474</v>
       </c>
       <c r="B83" t="n">
         <v>78967</v>
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483095</v>
+        <v>483188</v>
       </c>
       <c r="R83" t="n">
-        <v>6828845</v>
+        <v>6829143</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8674,10 +8674,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755474</v>
+        <v>125755522</v>
       </c>
       <c r="B84" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8685,21 +8685,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483188</v>
+        <v>483303</v>
       </c>
       <c r="R84" t="n">
-        <v>6829143</v>
+        <v>6829017</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8868,7 +8868,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755511</v>
+        <v>125755512</v>
       </c>
       <c r="B86" t="n">
         <v>78967</v>
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483188</v>
+        <v>483190</v>
       </c>
       <c r="R86" t="n">
-        <v>6828936</v>
+        <v>6828942</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8965,10 +8965,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755504</v>
+        <v>125755414</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8976,21 +8976,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483117</v>
+        <v>483240</v>
       </c>
       <c r="R87" t="n">
-        <v>6828857</v>
+        <v>6828921</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9062,7 +9062,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755484</v>
+        <v>125755511</v>
       </c>
       <c r="B88" t="n">
         <v>78967</v>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482976</v>
+        <v>483188</v>
       </c>
       <c r="R88" t="n">
-        <v>6828720</v>
+        <v>6828936</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755414</v>
+        <v>125755504</v>
       </c>
       <c r="B89" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9170,21 +9170,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483240</v>
+        <v>483117</v>
       </c>
       <c r="R89" t="n">
-        <v>6828921</v>
+        <v>6828857</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755512</v>
+        <v>125755484</v>
       </c>
       <c r="B91" t="n">
         <v>78967</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483190</v>
+        <v>482976</v>
       </c>
       <c r="R91" t="n">
-        <v>6828942</v>
+        <v>6828720</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755526</v>
+        <v>125755413</v>
       </c>
       <c r="B93" t="n">
-        <v>78634</v>
+        <v>79585</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9558,21 +9558,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483499</v>
+        <v>482962</v>
       </c>
       <c r="R93" t="n">
-        <v>6829120</v>
+        <v>6828771</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755469</v>
+        <v>125755444</v>
       </c>
       <c r="B94" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483342</v>
+        <v>483272</v>
       </c>
       <c r="R94" t="n">
         <v>6829286</v>
@@ -9741,7 +9741,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755493</v>
+        <v>125755469</v>
       </c>
       <c r="B95" t="n">
         <v>78967</v>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483037</v>
+        <v>483342</v>
       </c>
       <c r="R95" t="n">
-        <v>6828788</v>
+        <v>6829286</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9935,10 +9935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755413</v>
+        <v>125755526</v>
       </c>
       <c r="B97" t="n">
-        <v>79585</v>
+        <v>78634</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>482962</v>
+        <v>483499</v>
       </c>
       <c r="R97" t="n">
-        <v>6828771</v>
+        <v>6829120</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,32 +10032,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755520</v>
+        <v>125755493</v>
       </c>
       <c r="B98" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483458</v>
+        <v>483037</v>
       </c>
       <c r="R98" t="n">
-        <v>6829089</v>
+        <v>6828788</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,32 +10129,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755444</v>
+        <v>125755520</v>
       </c>
       <c r="B99" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483272</v>
+        <v>483458</v>
       </c>
       <c r="R99" t="n">
-        <v>6829286</v>
+        <v>6829089</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755507</v>
+        <v>125755415</v>
       </c>
       <c r="B101" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483178</v>
+        <v>483456</v>
       </c>
       <c r="R101" t="n">
-        <v>6828902</v>
+        <v>6829062</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755415</v>
+        <v>125755422</v>
       </c>
       <c r="B102" t="n">
-        <v>79585</v>
+        <v>78999</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483456</v>
+        <v>483099</v>
       </c>
       <c r="R102" t="n">
-        <v>6829062</v>
+        <v>6828854</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755422</v>
+        <v>125755507</v>
       </c>
       <c r="B103" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483099</v>
+        <v>483178</v>
       </c>
       <c r="R103" t="n">
-        <v>6828854</v>
+        <v>6828902</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10808,7 +10808,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755485</v>
+        <v>125755497</v>
       </c>
       <c r="B106" t="n">
         <v>78967</v>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483002</v>
+        <v>483063</v>
       </c>
       <c r="R106" t="n">
-        <v>6828695</v>
+        <v>6828803</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755497</v>
+        <v>125755485</v>
       </c>
       <c r="B107" t="n">
         <v>78967</v>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483063</v>
+        <v>483002</v>
       </c>
       <c r="R107" t="n">
-        <v>6828803</v>
+        <v>6828695</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11002,10 +11002,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125747874</v>
+        <v>125755523</v>
       </c>
       <c r="B108" t="n">
-        <v>57651</v>
+        <v>78634</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,39 +11013,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483012</v>
+        <v>483313</v>
       </c>
       <c r="R108" t="n">
-        <v>6828723</v>
+        <v>6829017</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11092,22 +11087,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125746396</v>
+        <v>125747874</v>
       </c>
       <c r="B109" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11115,34 +11110,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483265</v>
+        <v>483012</v>
       </c>
       <c r="R109" t="n">
-        <v>6828852</v>
+        <v>6828723</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11201,10 +11201,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755523</v>
+        <v>125746396</v>
       </c>
       <c r="B110" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11212,34 +11212,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483313</v>
+        <v>483265</v>
       </c>
       <c r="R110" t="n">
-        <v>6829017</v>
+        <v>6828852</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11286,12 +11286,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11492,50 +11492,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755457</v>
+        <v>125755436</v>
       </c>
       <c r="B113" t="n">
-        <v>56834</v>
+        <v>80099</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483040</v>
+        <v>483303</v>
       </c>
       <c r="R113" t="n">
-        <v>6828774</v>
+        <v>6829290</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11594,10 +11589,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755427</v>
+        <v>125755486</v>
       </c>
       <c r="B114" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11605,21 +11600,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11629,10 +11624,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483472</v>
+        <v>483015</v>
       </c>
       <c r="R114" t="n">
-        <v>6829305</v>
+        <v>6828711</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11691,32 +11686,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755436</v>
+        <v>125755471</v>
       </c>
       <c r="B115" t="n">
-        <v>80099</v>
+        <v>78967</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11726,10 +11721,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R115" t="n">
-        <v>6829290</v>
+        <v>6829193</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11788,10 +11783,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755486</v>
+        <v>125755457</v>
       </c>
       <c r="B116" t="n">
-        <v>78967</v>
+        <v>56834</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11799,34 +11794,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483015</v>
+        <v>483040</v>
       </c>
       <c r="R116" t="n">
-        <v>6828711</v>
+        <v>6828774</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11885,10 +11885,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755471</v>
+        <v>125755427</v>
       </c>
       <c r="B117" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11896,21 +11896,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11920,10 +11920,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483206</v>
+        <v>483472</v>
       </c>
       <c r="R117" t="n">
-        <v>6829193</v>
+        <v>6829305</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1946,7 +1946,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755488</v>
+        <v>125746064</v>
       </c>
       <c r="B15" t="n">
         <v>78967</v>
@@ -1977,14 +1977,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483019</v>
+        <v>483474</v>
       </c>
       <c r="R15" t="n">
-        <v>6828737</v>
+        <v>6829119</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,22 +2031,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755416</v>
+        <v>125746931</v>
       </c>
       <c r="B16" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,34 +2054,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483454</v>
+        <v>483156</v>
       </c>
       <c r="R16" t="n">
-        <v>6829082</v>
+        <v>6828728</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,6 +2116,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2128,19 +2133,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755475</v>
+        <v>125755488</v>
       </c>
       <c r="B17" t="n">
         <v>78967</v>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483169</v>
+        <v>483019</v>
       </c>
       <c r="R17" t="n">
-        <v>6829132</v>
+        <v>6828737</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125746064</v>
+        <v>125755416</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,34 +2253,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483474</v>
+        <v>483454</v>
       </c>
       <c r="R18" t="n">
-        <v>6829119</v>
+        <v>6829082</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2322,19 +2327,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125746931</v>
+        <v>125755475</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2365,14 +2370,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483156</v>
+        <v>483169</v>
       </c>
       <c r="R19" t="n">
-        <v>6828728</v>
+        <v>6829132</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2407,11 +2412,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2424,22 +2424,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755421</v>
+        <v>125745798</v>
       </c>
       <c r="B20" t="n">
-        <v>78999</v>
+        <v>79585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483044</v>
+        <v>483474</v>
       </c>
       <c r="R20" t="n">
-        <v>6828792</v>
+        <v>6829119</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,22 +2521,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125745798</v>
+        <v>125755445</v>
       </c>
       <c r="B21" t="n">
-        <v>79585</v>
+        <v>80070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483474</v>
+        <v>482900</v>
       </c>
       <c r="R21" t="n">
-        <v>6829119</v>
+        <v>6828861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2618,22 +2618,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755445</v>
+        <v>125755480</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482900</v>
+        <v>482885</v>
       </c>
       <c r="R22" t="n">
-        <v>6828861</v>
+        <v>6828897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755480</v>
+        <v>125755494</v>
       </c>
       <c r="B23" t="n">
         <v>78967</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482885</v>
+        <v>483047</v>
       </c>
       <c r="R23" t="n">
-        <v>6828897</v>
+        <v>6828790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755494</v>
+        <v>125755506</v>
       </c>
       <c r="B24" t="n">
         <v>78967</v>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483047</v>
+        <v>483162</v>
       </c>
       <c r="R24" t="n">
-        <v>6828790</v>
+        <v>6828887</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755506</v>
+        <v>125755440</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,21 +2932,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483162</v>
+        <v>482960</v>
       </c>
       <c r="R25" t="n">
-        <v>6828887</v>
+        <v>6828991</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755440</v>
+        <v>125755421</v>
       </c>
       <c r="B26" t="n">
-        <v>78726</v>
+        <v>78999</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482960</v>
+        <v>483044</v>
       </c>
       <c r="R26" t="n">
-        <v>6828991</v>
+        <v>6828792</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755428</v>
+        <v>125755481</v>
       </c>
       <c r="B30" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483280</v>
+        <v>482929</v>
       </c>
       <c r="R30" t="n">
-        <v>6828942</v>
+        <v>6828797</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755481</v>
+        <v>125755516</v>
       </c>
       <c r="B31" t="n">
         <v>78967</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>482929</v>
+        <v>483291</v>
       </c>
       <c r="R31" t="n">
-        <v>6828797</v>
+        <v>6828969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755516</v>
+        <v>125755428</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483291</v>
+        <v>483280</v>
       </c>
       <c r="R32" t="n">
-        <v>6828969</v>
+        <v>6828942</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755473</v>
+        <v>125755502</v>
       </c>
       <c r="B33" t="n">
         <v>78967</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483182</v>
+        <v>483078</v>
       </c>
       <c r="R33" t="n">
-        <v>6829175</v>
+        <v>6828839</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755411</v>
+        <v>125755473</v>
       </c>
       <c r="B34" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>482945</v>
+        <v>483182</v>
       </c>
       <c r="R34" t="n">
-        <v>6829125</v>
+        <v>6829175</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755502</v>
+        <v>125755411</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483078</v>
+        <v>482945</v>
       </c>
       <c r="R35" t="n">
-        <v>6828839</v>
+        <v>6829125</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755501</v>
+        <v>125747249</v>
       </c>
       <c r="B39" t="n">
         <v>78967</v>
@@ -4310,14 +4310,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R39" t="n">
-        <v>6828833</v>
+        <v>6828658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4352,6 +4352,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4364,22 +4369,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755482</v>
+        <v>125748935</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,34 +4392,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>482960</v>
+        <v>483071</v>
       </c>
       <c r="R40" t="n">
-        <v>6828769</v>
+        <v>6828797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4461,19 +4466,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125747249</v>
+        <v>125747099</v>
       </c>
       <c r="B41" t="n">
         <v>78967</v>
@@ -4508,7 +4513,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483032</v>
+        <v>483090</v>
       </c>
       <c r="R41" t="n">
         <v>6828658</v>
@@ -4544,11 +4549,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125748935</v>
+        <v>125746848</v>
       </c>
       <c r="B42" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483071</v>
+        <v>483247</v>
       </c>
       <c r="R42" t="n">
-        <v>6828797</v>
+        <v>6828848</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125747099</v>
+        <v>125755501</v>
       </c>
       <c r="B43" t="n">
         <v>78967</v>
@@ -4703,14 +4703,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483090</v>
+        <v>483071</v>
       </c>
       <c r="R43" t="n">
-        <v>6828658</v>
+        <v>6828833</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4757,19 +4757,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125746848</v>
+        <v>125755482</v>
       </c>
       <c r="B44" t="n">
         <v>78967</v>
@@ -4800,14 +4800,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483247</v>
+        <v>482960</v>
       </c>
       <c r="R44" t="n">
-        <v>6828848</v>
+        <v>6828769</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4854,12 +4854,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755536</v>
+        <v>125755466</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,39 +5071,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483037</v>
+        <v>483400</v>
       </c>
       <c r="R47" t="n">
-        <v>6828775</v>
+        <v>6829318</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5136,11 +5131,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5167,7 +5157,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755466</v>
+        <v>125755500</v>
       </c>
       <c r="B48" t="n">
         <v>78967</v>
@@ -5202,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483400</v>
+        <v>483068</v>
       </c>
       <c r="R48" t="n">
-        <v>6829318</v>
+        <v>6828819</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755500</v>
+        <v>125755453</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5275,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5299,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483068</v>
+        <v>482979</v>
       </c>
       <c r="R49" t="n">
-        <v>6828819</v>
+        <v>6829140</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5361,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755453</v>
+        <v>125755510</v>
       </c>
       <c r="B50" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5372,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5396,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>482979</v>
+        <v>483191</v>
       </c>
       <c r="R50" t="n">
-        <v>6829140</v>
+        <v>6828929</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5458,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755510</v>
+        <v>125755456</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5469,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5493,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483191</v>
+        <v>483114</v>
       </c>
       <c r="R51" t="n">
-        <v>6828929</v>
+        <v>6828865</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5555,10 +5545,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755456</v>
+        <v>125755536</v>
       </c>
       <c r="B52" t="n">
-        <v>78725</v>
+        <v>57651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,34 +5556,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483114</v>
+        <v>483037</v>
       </c>
       <c r="R52" t="n">
-        <v>6828865</v>
+        <v>6828775</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5626,6 +5621,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7015,10 +7015,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755525</v>
+        <v>125755533</v>
       </c>
       <c r="B67" t="n">
-        <v>78634</v>
+        <v>78373</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483442</v>
+        <v>483472</v>
       </c>
       <c r="R67" t="n">
-        <v>6829028</v>
+        <v>6829305</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,50 +7112,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755431</v>
+        <v>125755517</v>
       </c>
       <c r="B68" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483099</v>
+        <v>483386</v>
       </c>
       <c r="R68" t="n">
-        <v>6828858</v>
+        <v>6829003</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7214,45 +7209,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755433</v>
+        <v>125755431</v>
       </c>
       <c r="B69" t="n">
-        <v>57811</v>
+        <v>56843</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483307</v>
+        <v>483099</v>
       </c>
       <c r="R69" t="n">
-        <v>6829287</v>
+        <v>6828858</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7311,10 +7311,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755533</v>
+        <v>125755433</v>
       </c>
       <c r="B70" t="n">
-        <v>78373</v>
+        <v>57811</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7322,21 +7322,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483472</v>
+        <v>483307</v>
       </c>
       <c r="R70" t="n">
-        <v>6829305</v>
+        <v>6829287</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755517</v>
+        <v>125755525</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483386</v>
+        <v>483442</v>
       </c>
       <c r="R71" t="n">
-        <v>6829003</v>
+        <v>6829028</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9935,10 +9935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755526</v>
+        <v>125755435</v>
       </c>
       <c r="B97" t="n">
-        <v>78634</v>
+        <v>58129</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>103018</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483499</v>
+        <v>483450</v>
       </c>
       <c r="R97" t="n">
-        <v>6829120</v>
+        <v>6829302</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755493</v>
+        <v>125755526</v>
       </c>
       <c r="B98" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483037</v>
+        <v>483499</v>
       </c>
       <c r="R98" t="n">
-        <v>6828788</v>
+        <v>6829120</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,32 +10129,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755520</v>
+        <v>125755493</v>
       </c>
       <c r="B99" t="n">
-        <v>92509</v>
+        <v>78967</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483458</v>
+        <v>483037</v>
       </c>
       <c r="R99" t="n">
-        <v>6829089</v>
+        <v>6828788</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10226,32 +10226,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755435</v>
+        <v>125755520</v>
       </c>
       <c r="B100" t="n">
-        <v>58129</v>
+        <v>92509</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103018</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483450</v>
+        <v>483458</v>
       </c>
       <c r="R100" t="n">
-        <v>6829302</v>
+        <v>6829089</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755415</v>
+        <v>125755422</v>
       </c>
       <c r="B101" t="n">
-        <v>79585</v>
+        <v>78999</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483456</v>
+        <v>483099</v>
       </c>
       <c r="R101" t="n">
-        <v>6829062</v>
+        <v>6828854</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755422</v>
+        <v>125755507</v>
       </c>
       <c r="B102" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483099</v>
+        <v>483178</v>
       </c>
       <c r="R102" t="n">
-        <v>6828854</v>
+        <v>6828902</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755507</v>
+        <v>125755415</v>
       </c>
       <c r="B103" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483178</v>
+        <v>483456</v>
       </c>
       <c r="R103" t="n">
-        <v>6828902</v>
+        <v>6829062</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125746359</v>
+        <v>125755485</v>
       </c>
       <c r="B104" t="n">
         <v>78967</v>
@@ -10645,14 +10645,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483265</v>
+        <v>483002</v>
       </c>
       <c r="R104" t="n">
-        <v>6828852</v>
+        <v>6828695</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10699,19 +10699,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755490</v>
+        <v>125746359</v>
       </c>
       <c r="B105" t="n">
         <v>78967</v>
@@ -10742,14 +10742,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483007</v>
+        <v>483265</v>
       </c>
       <c r="R105" t="n">
-        <v>6828754</v>
+        <v>6828852</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10796,19 +10796,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755497</v>
+        <v>125755490</v>
       </c>
       <c r="B106" t="n">
         <v>78967</v>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483063</v>
+        <v>483007</v>
       </c>
       <c r="R106" t="n">
-        <v>6828803</v>
+        <v>6828754</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755485</v>
+        <v>125755497</v>
       </c>
       <c r="B107" t="n">
         <v>78967</v>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483002</v>
+        <v>483063</v>
       </c>
       <c r="R107" t="n">
-        <v>6828695</v>
+        <v>6828803</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755528</v>
+        <v>125755409</v>
       </c>
       <c r="B9" t="n">
-        <v>78634</v>
+        <v>79585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483525</v>
+        <v>483587</v>
       </c>
       <c r="R9" t="n">
-        <v>6829111</v>
+        <v>6829364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755409</v>
+        <v>125755528</v>
       </c>
       <c r="B10" t="n">
-        <v>79585</v>
+        <v>78634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483587</v>
+        <v>483525</v>
       </c>
       <c r="R10" t="n">
-        <v>6829364</v>
+        <v>6829111</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125746064</v>
+        <v>125755488</v>
       </c>
       <c r="B15" t="n">
         <v>78967</v>
@@ -1977,14 +1977,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483474</v>
+        <v>483019</v>
       </c>
       <c r="R15" t="n">
-        <v>6829119</v>
+        <v>6828737</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,22 +2031,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125746931</v>
+        <v>125755416</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,34 +2054,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483156</v>
+        <v>483454</v>
       </c>
       <c r="R16" t="n">
-        <v>6828728</v>
+        <v>6829082</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,11 +2116,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2133,19 +2128,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755488</v>
+        <v>125755475</v>
       </c>
       <c r="B17" t="n">
         <v>78967</v>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483019</v>
+        <v>483169</v>
       </c>
       <c r="R17" t="n">
-        <v>6828737</v>
+        <v>6829132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755416</v>
+        <v>125746064</v>
       </c>
       <c r="B18" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,34 +2248,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483454</v>
+        <v>483474</v>
       </c>
       <c r="R18" t="n">
-        <v>6829082</v>
+        <v>6829119</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,19 +2322,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755475</v>
+        <v>125746931</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2370,14 +2365,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483169</v>
+        <v>483156</v>
       </c>
       <c r="R19" t="n">
-        <v>6829132</v>
+        <v>6828728</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2412,6 +2407,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2424,12 +2424,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755502</v>
+        <v>125755473</v>
       </c>
       <c r="B33" t="n">
         <v>78967</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483078</v>
+        <v>483182</v>
       </c>
       <c r="R33" t="n">
-        <v>6828839</v>
+        <v>6829175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755473</v>
+        <v>125755411</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483182</v>
+        <v>482945</v>
       </c>
       <c r="R34" t="n">
-        <v>6829175</v>
+        <v>6829125</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755411</v>
+        <v>125755502</v>
       </c>
       <c r="B35" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>482945</v>
+        <v>483078</v>
       </c>
       <c r="R35" t="n">
-        <v>6829125</v>
+        <v>6828839</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755437</v>
+        <v>125755442</v>
       </c>
       <c r="B54" t="n">
-        <v>80071</v>
+        <v>78726</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483307</v>
+        <v>483201</v>
       </c>
       <c r="R54" t="n">
-        <v>6829287</v>
+        <v>6828916</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755491</v>
+        <v>125755437</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483015</v>
+        <v>483307</v>
       </c>
       <c r="R55" t="n">
-        <v>6828753</v>
+        <v>6829287</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125746158</v>
+        <v>125755491</v>
       </c>
       <c r="B56" t="n">
         <v>78967</v>
@@ -5974,14 +5974,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483342</v>
+        <v>483015</v>
       </c>
       <c r="R56" t="n">
-        <v>6828971</v>
+        <v>6828753</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,12 +6028,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755442</v>
+        <v>125746158</v>
       </c>
       <c r="B58" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6148,34 +6148,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483201</v>
+        <v>483342</v>
       </c>
       <c r="R58" t="n">
-        <v>6828916</v>
+        <v>6828971</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,19 +6222,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755498</v>
+        <v>125755468</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483071</v>
+        <v>483391</v>
       </c>
       <c r="R59" t="n">
-        <v>6828809</v>
+        <v>6829308</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,50 +6331,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755432</v>
+        <v>125755492</v>
       </c>
       <c r="B60" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483446</v>
+        <v>483032</v>
       </c>
       <c r="R60" t="n">
-        <v>6829026</v>
+        <v>6828773</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,7 +6428,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755468</v>
+        <v>125755498</v>
       </c>
       <c r="B61" t="n">
         <v>78967</v>
@@ -6468,10 +6463,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483391</v>
+        <v>483071</v>
       </c>
       <c r="R61" t="n">
-        <v>6829308</v>
+        <v>6828809</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,45 +6525,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755492</v>
+        <v>125755432</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483032</v>
+        <v>483446</v>
       </c>
       <c r="R62" t="n">
-        <v>6828773</v>
+        <v>6829026</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7607,10 +7607,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755424</v>
+        <v>125755441</v>
       </c>
       <c r="B73" t="n">
-        <v>78999</v>
+        <v>78726</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7618,21 +7618,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483162</v>
+        <v>483114</v>
       </c>
       <c r="R73" t="n">
-        <v>6828879</v>
+        <v>6828865</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7704,10 +7704,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755441</v>
+        <v>125755489</v>
       </c>
       <c r="B74" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7715,21 +7715,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483114</v>
+        <v>483001</v>
       </c>
       <c r="R74" t="n">
-        <v>6828865</v>
+        <v>6828740</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7801,10 +7801,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755489</v>
+        <v>125755451</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7812,21 +7812,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483001</v>
+        <v>483278</v>
       </c>
       <c r="R75" t="n">
-        <v>6828740</v>
+        <v>6828932</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7898,10 +7898,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755451</v>
+        <v>125755412</v>
       </c>
       <c r="B76" t="n">
-        <v>78725</v>
+        <v>79585</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,21 +7909,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483278</v>
+        <v>482912</v>
       </c>
       <c r="R76" t="n">
-        <v>6828932</v>
+        <v>6828922</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7995,10 +7995,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755412</v>
+        <v>125755472</v>
       </c>
       <c r="B77" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>482912</v>
+        <v>483203</v>
       </c>
       <c r="R77" t="n">
-        <v>6828922</v>
+        <v>6829189</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8092,10 +8092,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755472</v>
+        <v>125755424</v>
       </c>
       <c r="B78" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8103,21 +8103,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483203</v>
+        <v>483162</v>
       </c>
       <c r="R78" t="n">
-        <v>6829189</v>
+        <v>6828879</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9935,10 +9935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755435</v>
+        <v>125755526</v>
       </c>
       <c r="B97" t="n">
-        <v>58129</v>
+        <v>78634</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103018</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483450</v>
+        <v>483499</v>
       </c>
       <c r="R97" t="n">
-        <v>6829302</v>
+        <v>6829120</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755526</v>
+        <v>125755493</v>
       </c>
       <c r="B98" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483499</v>
+        <v>483037</v>
       </c>
       <c r="R98" t="n">
-        <v>6829120</v>
+        <v>6828788</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,32 +10129,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755493</v>
+        <v>125755520</v>
       </c>
       <c r="B99" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483037</v>
+        <v>483458</v>
       </c>
       <c r="R99" t="n">
-        <v>6828788</v>
+        <v>6829089</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10226,32 +10226,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755520</v>
+        <v>125755435</v>
       </c>
       <c r="B100" t="n">
-        <v>92509</v>
+        <v>58129</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>103018</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483458</v>
+        <v>483450</v>
       </c>
       <c r="R100" t="n">
-        <v>6829089</v>
+        <v>6829302</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11002,10 +11002,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755523</v>
+        <v>125747874</v>
       </c>
       <c r="B108" t="n">
-        <v>78634</v>
+        <v>57651</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,34 +11013,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483313</v>
+        <v>483012</v>
       </c>
       <c r="R108" t="n">
-        <v>6829017</v>
+        <v>6828723</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11087,22 +11092,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125747874</v>
+        <v>125746396</v>
       </c>
       <c r="B109" t="n">
-        <v>57651</v>
+        <v>78726</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11110,39 +11115,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483012</v>
+        <v>483265</v>
       </c>
       <c r="R109" t="n">
-        <v>6828723</v>
+        <v>6828852</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11201,10 +11201,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125746396</v>
+        <v>125755455</v>
       </c>
       <c r="B110" t="n">
-        <v>78726</v>
+        <v>78725</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11212,34 +11212,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483265</v>
+        <v>482942</v>
       </c>
       <c r="R110" t="n">
-        <v>6828852</v>
+        <v>6828979</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11286,44 +11286,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755455</v>
+        <v>125755532</v>
       </c>
       <c r="B111" t="n">
-        <v>78725</v>
+        <v>80105</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>482942</v>
+        <v>483294</v>
       </c>
       <c r="R111" t="n">
-        <v>6828979</v>
+        <v>6829294</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11395,32 +11395,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755532</v>
+        <v>125755523</v>
       </c>
       <c r="B112" t="n">
-        <v>80105</v>
+        <v>78634</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483294</v>
+        <v>483313</v>
       </c>
       <c r="R112" t="n">
-        <v>6829294</v>
+        <v>6829017</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12087,7 +12087,7 @@
         <v>125691576</v>
       </c>
       <c r="B119" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125755443</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125755429</v>
       </c>
       <c r="B3" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125755426</v>
       </c>
       <c r="B4" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125744833</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125755529</v>
       </c>
       <c r="B6" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125755447</v>
       </c>
       <c r="B7" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125755430</v>
       </c>
       <c r="B8" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125755409</v>
       </c>
       <c r="B9" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125755528</v>
       </c>
       <c r="B10" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125755448</v>
       </c>
       <c r="B11" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755439</v>
+        <v>125755452</v>
       </c>
       <c r="B12" t="n">
         <v>78726</v>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483586</v>
+        <v>483587</v>
       </c>
       <c r="R12" t="n">
         <v>6829364</v>
@@ -1755,7 +1755,7 @@
         <v>125755438</v>
       </c>
       <c r="B13" t="n">
-        <v>78991</v>
+        <v>78992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755452</v>
+        <v>125755439</v>
       </c>
       <c r="B14" t="n">
-        <v>78725</v>
+        <v>78727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483587</v>
+        <v>483586</v>
       </c>
       <c r="R14" t="n">
         <v>6829364</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755488</v>
+        <v>125755416</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483019</v>
+        <v>483454</v>
       </c>
       <c r="R15" t="n">
-        <v>6828737</v>
+        <v>6829082</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755416</v>
+        <v>125755488</v>
       </c>
       <c r="B16" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483454</v>
+        <v>483019</v>
       </c>
       <c r="R16" t="n">
-        <v>6829082</v>
+        <v>6828737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,7 +2143,7 @@
         <v>125755475</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>125746064</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>125746931</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125745798</v>
+        <v>125755421</v>
       </c>
       <c r="B20" t="n">
-        <v>79585</v>
+        <v>79000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483474</v>
+        <v>483044</v>
       </c>
       <c r="R20" t="n">
-        <v>6829119</v>
+        <v>6828792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,22 +2521,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755445</v>
+        <v>125745798</v>
       </c>
       <c r="B21" t="n">
-        <v>80070</v>
+        <v>79586</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482900</v>
+        <v>483474</v>
       </c>
       <c r="R21" t="n">
-        <v>6828861</v>
+        <v>6829119</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2618,22 +2618,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755480</v>
+        <v>125755440</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482885</v>
+        <v>482960</v>
       </c>
       <c r="R22" t="n">
-        <v>6828897</v>
+        <v>6828991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755494</v>
+        <v>125755506</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483047</v>
+        <v>483162</v>
       </c>
       <c r="R23" t="n">
-        <v>6828790</v>
+        <v>6828887</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755506</v>
+        <v>125755480</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483162</v>
+        <v>482885</v>
       </c>
       <c r="R24" t="n">
-        <v>6828887</v>
+        <v>6828897</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755440</v>
+        <v>125755494</v>
       </c>
       <c r="B25" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,21 +2932,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>482960</v>
+        <v>483047</v>
       </c>
       <c r="R25" t="n">
-        <v>6828991</v>
+        <v>6828790</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755421</v>
+        <v>125755445</v>
       </c>
       <c r="B26" t="n">
-        <v>78999</v>
+        <v>80071</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483044</v>
+        <v>482900</v>
       </c>
       <c r="R26" t="n">
-        <v>6828792</v>
+        <v>6828861</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3115,27 +3115,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125747349</v>
+        <v>125755530</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>80106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3146,14 +3146,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482981</v>
+        <v>483303</v>
       </c>
       <c r="R27" t="n">
-        <v>6828687</v>
+        <v>6829288</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3200,39 +3200,39 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755530</v>
+        <v>125755513</v>
       </c>
       <c r="B28" t="n">
-        <v>80105</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R28" t="n">
-        <v>6829288</v>
+        <v>6828917</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755513</v>
+        <v>125747349</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,14 +3340,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483206</v>
+        <v>482981</v>
       </c>
       <c r="R29" t="n">
-        <v>6828917</v>
+        <v>6828687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3394,22 +3394,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755481</v>
+        <v>125755428</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>79557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>482929</v>
+        <v>483280</v>
       </c>
       <c r="R30" t="n">
-        <v>6828797</v>
+        <v>6828942</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3506,7 +3506,7 @@
         <v>125755516</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755428</v>
+        <v>125755481</v>
       </c>
       <c r="B32" t="n">
-        <v>79556</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483280</v>
+        <v>482929</v>
       </c>
       <c r="R32" t="n">
-        <v>6828942</v>
+        <v>6828797</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755473</v>
+        <v>125755502</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483182</v>
+        <v>483078</v>
       </c>
       <c r="R33" t="n">
-        <v>6829175</v>
+        <v>6828839</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755411</v>
+        <v>125755473</v>
       </c>
       <c r="B34" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>482945</v>
+        <v>483182</v>
       </c>
       <c r="R34" t="n">
-        <v>6829125</v>
+        <v>6829175</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755502</v>
+        <v>125755411</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483078</v>
+        <v>482945</v>
       </c>
       <c r="R35" t="n">
-        <v>6828839</v>
+        <v>6829125</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,32 +3988,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755460</v>
+        <v>125755478</v>
       </c>
       <c r="B36" t="n">
-        <v>91387</v>
+        <v>78968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>482913</v>
+        <v>483147</v>
       </c>
       <c r="R36" t="n">
         <v>6829095</v>
@@ -4085,32 +4085,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755478</v>
+        <v>125755460</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>91389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483147</v>
+        <v>482913</v>
       </c>
       <c r="R37" t="n">
         <v>6829095</v>
@@ -4185,7 +4185,7 @@
         <v>125755417</v>
       </c>
       <c r="B38" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125747249</v>
+        <v>125748935</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R39" t="n">
-        <v>6828658</v>
+        <v>6828797</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4350,11 +4350,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4381,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125748935</v>
+        <v>125747249</v>
       </c>
       <c r="B40" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4392,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4416,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R40" t="n">
-        <v>6828797</v>
+        <v>6828658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4452,6 +4447,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4481,7 +4481,7 @@
         <v>125747099</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>125746848</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>125755501</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755482</v>
+        <v>125755464</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>482960</v>
+        <v>483423</v>
       </c>
       <c r="R44" t="n">
-        <v>6828769</v>
+        <v>6829325</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755464</v>
+        <v>125755508</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483423</v>
+        <v>483189</v>
       </c>
       <c r="R45" t="n">
-        <v>6829325</v>
+        <v>6828911</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755508</v>
+        <v>125755482</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483189</v>
+        <v>482960</v>
       </c>
       <c r="R46" t="n">
-        <v>6828911</v>
+        <v>6828769</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5063,7 +5063,7 @@
         <v>125755466</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755500</v>
+        <v>125755456</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483068</v>
+        <v>483114</v>
       </c>
       <c r="R48" t="n">
-        <v>6828819</v>
+        <v>6828865</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755453</v>
+        <v>125755510</v>
       </c>
       <c r="B49" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>482979</v>
+        <v>483191</v>
       </c>
       <c r="R49" t="n">
-        <v>6829140</v>
+        <v>6828929</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755510</v>
+        <v>125755453</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483191</v>
+        <v>482979</v>
       </c>
       <c r="R50" t="n">
-        <v>6828929</v>
+        <v>6829140</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755456</v>
+        <v>125755500</v>
       </c>
       <c r="B51" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483114</v>
+        <v>483068</v>
       </c>
       <c r="R51" t="n">
-        <v>6828865</v>
+        <v>6828819</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5655,7 +5655,7 @@
         <v>125755483</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755442</v>
+        <v>125755437</v>
       </c>
       <c r="B54" t="n">
-        <v>78726</v>
+        <v>80072</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483201</v>
+        <v>483307</v>
       </c>
       <c r="R54" t="n">
-        <v>6828916</v>
+        <v>6829287</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755437</v>
+        <v>125755491</v>
       </c>
       <c r="B55" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483307</v>
+        <v>483015</v>
       </c>
       <c r="R55" t="n">
-        <v>6829287</v>
+        <v>6828753</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755491</v>
+        <v>125746158</v>
       </c>
       <c r="B56" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5974,14 +5974,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483015</v>
+        <v>483342</v>
       </c>
       <c r="R56" t="n">
-        <v>6828753</v>
+        <v>6828971</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,12 +6028,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6043,7 +6043,7 @@
         <v>125755458</v>
       </c>
       <c r="B57" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125746158</v>
+        <v>125755442</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6148,34 +6148,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483342</v>
+        <v>483201</v>
       </c>
       <c r="R58" t="n">
-        <v>6828971</v>
+        <v>6828916</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755468</v>
+        <v>125755498</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483391</v>
+        <v>483071</v>
       </c>
       <c r="R59" t="n">
-        <v>6829308</v>
+        <v>6828809</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755492</v>
+        <v>125755468</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483032</v>
+        <v>483391</v>
       </c>
       <c r="R60" t="n">
-        <v>6828773</v>
+        <v>6829308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,45 +6428,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755498</v>
+        <v>125755432</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483071</v>
+        <v>483446</v>
       </c>
       <c r="R61" t="n">
-        <v>6828809</v>
+        <v>6829026</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6525,50 +6530,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755432</v>
+        <v>125755492</v>
       </c>
       <c r="B62" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483446</v>
+        <v>483032</v>
       </c>
       <c r="R62" t="n">
-        <v>6829026</v>
+        <v>6828773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755463</v>
+        <v>125755496</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483450</v>
+        <v>483054</v>
       </c>
       <c r="R63" t="n">
-        <v>6829306</v>
+        <v>6828788</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755496</v>
+        <v>125755463</v>
       </c>
       <c r="B64" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483054</v>
+        <v>483450</v>
       </c>
       <c r="R64" t="n">
-        <v>6828788</v>
+        <v>6829306</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6824,7 +6824,7 @@
         <v>125755459</v>
       </c>
       <c r="B65" t="n">
-        <v>91241</v>
+        <v>91242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>125755419</v>
       </c>
       <c r="B66" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755533</v>
+        <v>125755525</v>
       </c>
       <c r="B67" t="n">
-        <v>78373</v>
+        <v>78635</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483472</v>
+        <v>483442</v>
       </c>
       <c r="R67" t="n">
-        <v>6829305</v>
+        <v>6829028</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755517</v>
+        <v>125755533</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>78374</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483386</v>
+        <v>483472</v>
       </c>
       <c r="R68" t="n">
-        <v>6829003</v>
+        <v>6829305</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7209,50 +7209,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755431</v>
+        <v>125755517</v>
       </c>
       <c r="B69" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483099</v>
+        <v>483386</v>
       </c>
       <c r="R69" t="n">
-        <v>6828858</v>
+        <v>6829003</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7311,45 +7306,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755433</v>
+        <v>125755431</v>
       </c>
       <c r="B70" t="n">
-        <v>57811</v>
+        <v>56843</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483307</v>
+        <v>483099</v>
       </c>
       <c r="R70" t="n">
-        <v>6829287</v>
+        <v>6828858</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755525</v>
+        <v>125755433</v>
       </c>
       <c r="B71" t="n">
-        <v>78634</v>
+        <v>57811</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483442</v>
+        <v>483307</v>
       </c>
       <c r="R71" t="n">
-        <v>6829028</v>
+        <v>6829287</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125748016</v>
+        <v>125755412</v>
       </c>
       <c r="B72" t="n">
-        <v>57651</v>
+        <v>79586</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,39 +7516,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483071</v>
+        <v>482912</v>
       </c>
       <c r="R72" t="n">
-        <v>6828797</v>
+        <v>6828922</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7595,22 +7590,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755441</v>
+        <v>125755472</v>
       </c>
       <c r="B73" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7618,21 +7613,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7642,10 +7637,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483114</v>
+        <v>483203</v>
       </c>
       <c r="R73" t="n">
-        <v>6828865</v>
+        <v>6829189</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7707,7 +7702,7 @@
         <v>125755489</v>
       </c>
       <c r="B74" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7804,7 +7799,7 @@
         <v>125755451</v>
       </c>
       <c r="B75" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7898,10 +7893,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755412</v>
+        <v>125755424</v>
       </c>
       <c r="B76" t="n">
-        <v>79585</v>
+        <v>79000</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,21 +7904,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7933,10 +7928,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>482912</v>
+        <v>483162</v>
       </c>
       <c r="R76" t="n">
-        <v>6828922</v>
+        <v>6828879</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7995,10 +7990,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755472</v>
+        <v>125755441</v>
       </c>
       <c r="B77" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8006,21 +8001,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8030,10 +8025,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483203</v>
+        <v>483114</v>
       </c>
       <c r="R77" t="n">
-        <v>6829189</v>
+        <v>6828865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8092,10 +8087,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755424</v>
+        <v>125748016</v>
       </c>
       <c r="B78" t="n">
-        <v>78999</v>
+        <v>57651</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8103,34 +8098,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483162</v>
+        <v>483071</v>
       </c>
       <c r="R78" t="n">
-        <v>6828879</v>
+        <v>6828797</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8177,22 +8177,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755503</v>
+        <v>125755515</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483095</v>
+        <v>483280</v>
       </c>
       <c r="R79" t="n">
-        <v>6828845</v>
+        <v>6828952</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,10 +8286,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755518</v>
+        <v>125755514</v>
       </c>
       <c r="B80" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483467</v>
+        <v>483220</v>
       </c>
       <c r="R80" t="n">
-        <v>6829027</v>
+        <v>6828907</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755515</v>
+        <v>125755518</v>
       </c>
       <c r="B81" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483280</v>
+        <v>483467</v>
       </c>
       <c r="R81" t="n">
-        <v>6828952</v>
+        <v>6829027</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8480,10 +8480,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755514</v>
+        <v>125755503</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483220</v>
+        <v>483095</v>
       </c>
       <c r="R82" t="n">
-        <v>6828907</v>
+        <v>6828845</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8580,7 +8580,7 @@
         <v>125755474</v>
       </c>
       <c r="B83" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>125755522</v>
       </c>
       <c r="B84" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8771,10 +8771,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125747880</v>
+        <v>125755511</v>
       </c>
       <c r="B85" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8802,14 +8802,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483012</v>
+        <v>483188</v>
       </c>
       <c r="R85" t="n">
-        <v>6828723</v>
+        <v>6828936</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8856,22 +8856,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755512</v>
+        <v>125755504</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483190</v>
+        <v>483117</v>
       </c>
       <c r="R86" t="n">
-        <v>6828942</v>
+        <v>6828857</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8965,10 +8965,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755414</v>
+        <v>125755484</v>
       </c>
       <c r="B87" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8976,21 +8976,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483240</v>
+        <v>482976</v>
       </c>
       <c r="R87" t="n">
-        <v>6828921</v>
+        <v>6828720</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755511</v>
+        <v>125755414</v>
       </c>
       <c r="B88" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9073,21 +9073,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483188</v>
+        <v>483240</v>
       </c>
       <c r="R88" t="n">
-        <v>6828936</v>
+        <v>6828921</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755504</v>
+        <v>125755479</v>
       </c>
       <c r="B89" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483117</v>
+        <v>482918</v>
       </c>
       <c r="R89" t="n">
-        <v>6828857</v>
+        <v>6828932</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755479</v>
+        <v>125755512</v>
       </c>
       <c r="B90" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482918</v>
+        <v>483190</v>
       </c>
       <c r="R90" t="n">
-        <v>6828932</v>
+        <v>6828942</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755484</v>
+        <v>125755418</v>
       </c>
       <c r="B91" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>482976</v>
+        <v>482886</v>
       </c>
       <c r="R91" t="n">
-        <v>6828720</v>
+        <v>6828895</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755418</v>
+        <v>125747880</v>
       </c>
       <c r="B92" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9461,34 +9461,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>482886</v>
+        <v>483012</v>
       </c>
       <c r="R92" t="n">
-        <v>6828895</v>
+        <v>6828723</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9535,22 +9535,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755413</v>
+        <v>125755469</v>
       </c>
       <c r="B93" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9558,21 +9558,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>482962</v>
+        <v>483342</v>
       </c>
       <c r="R93" t="n">
-        <v>6828771</v>
+        <v>6829286</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755444</v>
+        <v>125755493</v>
       </c>
       <c r="B94" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483272</v>
+        <v>483037</v>
       </c>
       <c r="R94" t="n">
-        <v>6829286</v>
+        <v>6828788</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755469</v>
+        <v>125755446</v>
       </c>
       <c r="B95" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9752,21 +9752,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483342</v>
+        <v>482885</v>
       </c>
       <c r="R95" t="n">
-        <v>6829286</v>
+        <v>6828845</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755446</v>
+        <v>125755413</v>
       </c>
       <c r="B96" t="n">
-        <v>80070</v>
+        <v>79586</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9849,21 +9849,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>482885</v>
+        <v>482962</v>
       </c>
       <c r="R96" t="n">
-        <v>6828845</v>
+        <v>6828771</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9935,32 +9935,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755526</v>
+        <v>125755520</v>
       </c>
       <c r="B97" t="n">
-        <v>78634</v>
+        <v>92518</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483499</v>
+        <v>483458</v>
       </c>
       <c r="R97" t="n">
-        <v>6829120</v>
+        <v>6829089</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755493</v>
+        <v>125755444</v>
       </c>
       <c r="B98" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483037</v>
+        <v>483272</v>
       </c>
       <c r="R98" t="n">
-        <v>6828788</v>
+        <v>6829286</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,32 +10129,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755520</v>
+        <v>125755526</v>
       </c>
       <c r="B99" t="n">
-        <v>92509</v>
+        <v>78635</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483458</v>
+        <v>483499</v>
       </c>
       <c r="R99" t="n">
-        <v>6829089</v>
+        <v>6829120</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10229,7 +10229,7 @@
         <v>125755435</v>
       </c>
       <c r="B100" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755422</v>
+        <v>125755507</v>
       </c>
       <c r="B101" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483099</v>
+        <v>483178</v>
       </c>
       <c r="R101" t="n">
-        <v>6828854</v>
+        <v>6828902</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755507</v>
+        <v>125755415</v>
       </c>
       <c r="B102" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483178</v>
+        <v>483456</v>
       </c>
       <c r="R102" t="n">
-        <v>6828902</v>
+        <v>6829062</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755415</v>
+        <v>125755422</v>
       </c>
       <c r="B103" t="n">
-        <v>79585</v>
+        <v>79000</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483456</v>
+        <v>483099</v>
       </c>
       <c r="R103" t="n">
-        <v>6829062</v>
+        <v>6828854</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10614,10 +10614,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755485</v>
+        <v>125755497</v>
       </c>
       <c r="B104" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483002</v>
+        <v>483063</v>
       </c>
       <c r="R104" t="n">
-        <v>6828695</v>
+        <v>6828803</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10711,10 +10711,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125746359</v>
+        <v>125755490</v>
       </c>
       <c r="B105" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10742,14 +10742,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483265</v>
+        <v>483007</v>
       </c>
       <c r="R105" t="n">
-        <v>6828852</v>
+        <v>6828754</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10796,22 +10796,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755490</v>
+        <v>125755485</v>
       </c>
       <c r="B106" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483007</v>
+        <v>483002</v>
       </c>
       <c r="R106" t="n">
-        <v>6828754</v>
+        <v>6828695</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10905,10 +10905,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755497</v>
+        <v>125746359</v>
       </c>
       <c r="B107" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10936,14 +10936,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483063</v>
+        <v>483265</v>
       </c>
       <c r="R107" t="n">
-        <v>6828803</v>
+        <v>6828852</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10990,22 +10990,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125747874</v>
+        <v>125755455</v>
       </c>
       <c r="B108" t="n">
-        <v>57651</v>
+        <v>78726</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,39 +11013,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483012</v>
+        <v>482942</v>
       </c>
       <c r="R108" t="n">
-        <v>6828723</v>
+        <v>6828979</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11092,57 +11087,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125746396</v>
+        <v>125755532</v>
       </c>
       <c r="B109" t="n">
-        <v>78726</v>
+        <v>80106</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483265</v>
+        <v>483294</v>
       </c>
       <c r="R109" t="n">
-        <v>6828852</v>
+        <v>6829294</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11189,22 +11184,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755455</v>
+        <v>125755523</v>
       </c>
       <c r="B110" t="n">
-        <v>78725</v>
+        <v>78635</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11212,21 +11207,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11236,10 +11231,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>482942</v>
+        <v>483313</v>
       </c>
       <c r="R110" t="n">
-        <v>6828979</v>
+        <v>6829017</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11298,45 +11293,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755532</v>
+        <v>125746396</v>
       </c>
       <c r="B111" t="n">
-        <v>80105</v>
+        <v>78727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483294</v>
+        <v>483265</v>
       </c>
       <c r="R111" t="n">
-        <v>6829294</v>
+        <v>6828852</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11383,22 +11378,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755523</v>
+        <v>125747874</v>
       </c>
       <c r="B112" t="n">
-        <v>78634</v>
+        <v>57651</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11406,34 +11401,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483313</v>
+        <v>483012</v>
       </c>
       <c r="R112" t="n">
-        <v>6829017</v>
+        <v>6828723</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11480,44 +11480,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755436</v>
+        <v>125755427</v>
       </c>
       <c r="B113" t="n">
-        <v>80099</v>
+        <v>79557</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483303</v>
+        <v>483472</v>
       </c>
       <c r="R113" t="n">
-        <v>6829290</v>
+        <v>6829305</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11589,10 +11589,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755486</v>
+        <v>125755471</v>
       </c>
       <c r="B114" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483015</v>
+        <v>483206</v>
       </c>
       <c r="R114" t="n">
-        <v>6828711</v>
+        <v>6829193</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11686,32 +11686,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755471</v>
+        <v>125755436</v>
       </c>
       <c r="B115" t="n">
-        <v>78967</v>
+        <v>80100</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R115" t="n">
-        <v>6829193</v>
+        <v>6829290</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11783,10 +11783,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755457</v>
+        <v>125755486</v>
       </c>
       <c r="B116" t="n">
-        <v>56834</v>
+        <v>78968</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11794,39 +11794,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483040</v>
+        <v>483015</v>
       </c>
       <c r="R116" t="n">
-        <v>6828774</v>
+        <v>6828711</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11885,10 +11880,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755427</v>
+        <v>125755457</v>
       </c>
       <c r="B117" t="n">
-        <v>79556</v>
+        <v>56834</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11896,34 +11891,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>102612</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483472</v>
+        <v>483040</v>
       </c>
       <c r="R117" t="n">
-        <v>6829305</v>
+        <v>6828774</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11985,7 +11985,7 @@
         <v>125755462</v>
       </c>
       <c r="B118" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755421</v>
+        <v>125755506</v>
       </c>
       <c r="B20" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483044</v>
+        <v>483162</v>
       </c>
       <c r="R20" t="n">
-        <v>6828792</v>
+        <v>6828887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125745798</v>
+        <v>125755480</v>
       </c>
       <c r="B21" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483474</v>
+        <v>482885</v>
       </c>
       <c r="R21" t="n">
-        <v>6829119</v>
+        <v>6828897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2618,22 +2618,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755440</v>
+        <v>125755494</v>
       </c>
       <c r="B22" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482960</v>
+        <v>483047</v>
       </c>
       <c r="R22" t="n">
-        <v>6828991</v>
+        <v>6828790</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755506</v>
+        <v>125755445</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,21 +2738,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483162</v>
+        <v>482900</v>
       </c>
       <c r="R23" t="n">
-        <v>6828887</v>
+        <v>6828861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755480</v>
+        <v>125755421</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482885</v>
+        <v>483044</v>
       </c>
       <c r="R24" t="n">
-        <v>6828897</v>
+        <v>6828792</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755494</v>
+        <v>125745798</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483047</v>
+        <v>483474</v>
       </c>
       <c r="R25" t="n">
-        <v>6828790</v>
+        <v>6829119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,22 +3006,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755445</v>
+        <v>125755440</v>
       </c>
       <c r="B26" t="n">
-        <v>80071</v>
+        <v>78727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482900</v>
+        <v>482960</v>
       </c>
       <c r="R26" t="n">
-        <v>6828861</v>
+        <v>6828991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -6234,7 +6234,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755498</v>
+        <v>125755492</v>
       </c>
       <c r="B59" t="n">
         <v>78968</v>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R59" t="n">
-        <v>6828809</v>
+        <v>6828773</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755468</v>
+        <v>125755498</v>
       </c>
       <c r="B60" t="n">
         <v>78968</v>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483391</v>
+        <v>483071</v>
       </c>
       <c r="R60" t="n">
-        <v>6829308</v>
+        <v>6828809</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,50 +6428,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755432</v>
+        <v>125755468</v>
       </c>
       <c r="B61" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483446</v>
+        <v>483391</v>
       </c>
       <c r="R61" t="n">
-        <v>6829026</v>
+        <v>6829308</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,45 +6525,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755492</v>
+        <v>125755432</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483032</v>
+        <v>483446</v>
       </c>
       <c r="R62" t="n">
-        <v>6828773</v>
+        <v>6829026</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755496</v>
+        <v>125755459</v>
       </c>
       <c r="B63" t="n">
-        <v>78968</v>
+        <v>91242</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483054</v>
+        <v>483398</v>
       </c>
       <c r="R63" t="n">
-        <v>6828788</v>
+        <v>6829316</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755463</v>
+        <v>125755419</v>
       </c>
       <c r="B64" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6735,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483450</v>
+        <v>483005</v>
       </c>
       <c r="R64" t="n">
-        <v>6829306</v>
+        <v>6828754</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755459</v>
+        <v>125755496</v>
       </c>
       <c r="B65" t="n">
-        <v>91242</v>
+        <v>78968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483398</v>
+        <v>483054</v>
       </c>
       <c r="R65" t="n">
-        <v>6829316</v>
+        <v>6828788</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755419</v>
+        <v>125755463</v>
       </c>
       <c r="B66" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6929,21 +6929,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483005</v>
+        <v>483450</v>
       </c>
       <c r="R66" t="n">
-        <v>6828754</v>
+        <v>6829306</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7015,45 +7015,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755525</v>
+        <v>125755431</v>
       </c>
       <c r="B67" t="n">
-        <v>78635</v>
+        <v>56843</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483442</v>
+        <v>483099</v>
       </c>
       <c r="R67" t="n">
-        <v>6829028</v>
+        <v>6828858</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,10 +7117,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755533</v>
+        <v>125755525</v>
       </c>
       <c r="B68" t="n">
-        <v>78374</v>
+        <v>78635</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7123,21 +7128,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7147,10 +7152,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483472</v>
+        <v>483442</v>
       </c>
       <c r="R68" t="n">
-        <v>6829305</v>
+        <v>6829028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7209,10 +7214,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755517</v>
+        <v>125755533</v>
       </c>
       <c r="B69" t="n">
-        <v>78968</v>
+        <v>78374</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7220,21 +7225,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7244,10 +7249,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483386</v>
+        <v>483472</v>
       </c>
       <c r="R69" t="n">
-        <v>6829003</v>
+        <v>6829305</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7306,50 +7311,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755431</v>
+        <v>125755517</v>
       </c>
       <c r="B70" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483099</v>
+        <v>483386</v>
       </c>
       <c r="R70" t="n">
-        <v>6828858</v>
+        <v>6829003</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755469</v>
+        <v>125755435</v>
       </c>
       <c r="B93" t="n">
-        <v>78968</v>
+        <v>58130</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9558,21 +9558,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483342</v>
+        <v>483450</v>
       </c>
       <c r="R93" t="n">
-        <v>6829286</v>
+        <v>6829302</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,7 +9644,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755493</v>
+        <v>125755469</v>
       </c>
       <c r="B94" t="n">
         <v>78968</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483037</v>
+        <v>483342</v>
       </c>
       <c r="R94" t="n">
-        <v>6828788</v>
+        <v>6829286</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755446</v>
+        <v>125755493</v>
       </c>
       <c r="B95" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9752,21 +9752,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>482885</v>
+        <v>483037</v>
       </c>
       <c r="R95" t="n">
-        <v>6828845</v>
+        <v>6828788</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755413</v>
+        <v>125755446</v>
       </c>
       <c r="B96" t="n">
-        <v>79586</v>
+        <v>80071</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9849,21 +9849,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>482962</v>
+        <v>482885</v>
       </c>
       <c r="R96" t="n">
-        <v>6828771</v>
+        <v>6828845</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9935,32 +9935,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755520</v>
+        <v>125755413</v>
       </c>
       <c r="B97" t="n">
-        <v>92518</v>
+        <v>79586</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483458</v>
+        <v>482962</v>
       </c>
       <c r="R97" t="n">
-        <v>6829089</v>
+        <v>6828771</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,32 +10032,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755444</v>
+        <v>125755520</v>
       </c>
       <c r="B98" t="n">
-        <v>80071</v>
+        <v>92518</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483272</v>
+        <v>483458</v>
       </c>
       <c r="R98" t="n">
-        <v>6829286</v>
+        <v>6829089</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,10 +10129,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755526</v>
+        <v>125755444</v>
       </c>
       <c r="B99" t="n">
-        <v>78635</v>
+        <v>80071</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10140,21 +10140,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483499</v>
+        <v>483272</v>
       </c>
       <c r="R99" t="n">
-        <v>6829120</v>
+        <v>6829286</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755435</v>
+        <v>125755526</v>
       </c>
       <c r="B100" t="n">
-        <v>58130</v>
+        <v>78635</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103018</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483450</v>
+        <v>483499</v>
       </c>
       <c r="R100" t="n">
-        <v>6829302</v>
+        <v>6829120</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125755443</v>
       </c>
       <c r="B2" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125755429</v>
       </c>
       <c r="B3" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125755426</v>
       </c>
       <c r="B4" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125744833</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125755529</v>
       </c>
       <c r="B6" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125755447</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125755430</v>
       </c>
       <c r="B8" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125755409</v>
       </c>
       <c r="B9" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125755528</v>
       </c>
       <c r="B10" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125755448</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>125755452</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>125755438</v>
       </c>
       <c r="B13" t="n">
-        <v>78992</v>
+        <v>78996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>125755439</v>
       </c>
       <c r="B14" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755416</v>
+        <v>125746064</v>
       </c>
       <c r="B15" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,34 +1957,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483454</v>
+        <v>483474</v>
       </c>
       <c r="R15" t="n">
-        <v>6829082</v>
+        <v>6829119</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,22 +2031,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755488</v>
+        <v>125746931</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,14 +2074,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483019</v>
+        <v>483156</v>
       </c>
       <c r="R16" t="n">
-        <v>6828737</v>
+        <v>6828728</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,6 +2116,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2128,22 +2133,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755475</v>
+        <v>125755488</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483169</v>
+        <v>483019</v>
       </c>
       <c r="R17" t="n">
-        <v>6829132</v>
+        <v>6828737</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125746064</v>
+        <v>125755475</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,14 +2273,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483474</v>
+        <v>483169</v>
       </c>
       <c r="R18" t="n">
-        <v>6829119</v>
+        <v>6829132</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2322,22 +2327,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125746931</v>
+        <v>125755416</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,34 +2350,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483156</v>
+        <v>483454</v>
       </c>
       <c r="R19" t="n">
-        <v>6828728</v>
+        <v>6829082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2407,11 +2412,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2424,22 +2424,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755506</v>
+        <v>125755445</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483162</v>
+        <v>482900</v>
       </c>
       <c r="R20" t="n">
-        <v>6828887</v>
+        <v>6828861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755480</v>
+        <v>125755440</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482885</v>
+        <v>482960</v>
       </c>
       <c r="R21" t="n">
-        <v>6828897</v>
+        <v>6828991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755494</v>
+        <v>125755421</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483047</v>
+        <v>483044</v>
       </c>
       <c r="R22" t="n">
-        <v>6828790</v>
+        <v>6828792</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755445</v>
+        <v>125755506</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,21 +2738,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482900</v>
+        <v>483162</v>
       </c>
       <c r="R23" t="n">
-        <v>6828861</v>
+        <v>6828887</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755421</v>
+        <v>125755480</v>
       </c>
       <c r="B24" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483044</v>
+        <v>482885</v>
       </c>
       <c r="R24" t="n">
-        <v>6828792</v>
+        <v>6828897</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125745798</v>
+        <v>125755494</v>
       </c>
       <c r="B25" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483474</v>
+        <v>483047</v>
       </c>
       <c r="R25" t="n">
-        <v>6829119</v>
+        <v>6828790</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,22 +3006,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755440</v>
+        <v>125745798</v>
       </c>
       <c r="B26" t="n">
-        <v>78727</v>
+        <v>79590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482960</v>
+        <v>483474</v>
       </c>
       <c r="R26" t="n">
-        <v>6828991</v>
+        <v>6829119</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3103,39 +3103,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755530</v>
+        <v>125755513</v>
       </c>
       <c r="B27" t="n">
-        <v>80106</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R27" t="n">
-        <v>6829288</v>
+        <v>6828917</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3212,27 +3212,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755513</v>
+        <v>125755530</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>80110</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R28" t="n">
-        <v>6828917</v>
+        <v>6829288</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3312,7 +3312,7 @@
         <v>125747349</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755428</v>
+        <v>125755516</v>
       </c>
       <c r="B30" t="n">
-        <v>79557</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483280</v>
+        <v>483291</v>
       </c>
       <c r="R30" t="n">
-        <v>6828942</v>
+        <v>6828969</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755516</v>
+        <v>125755481</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483291</v>
+        <v>482929</v>
       </c>
       <c r="R31" t="n">
-        <v>6828969</v>
+        <v>6828797</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755481</v>
+        <v>125755428</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>79561</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>482929</v>
+        <v>483280</v>
       </c>
       <c r="R32" t="n">
-        <v>6828797</v>
+        <v>6828942</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755502</v>
+        <v>125755460</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>91393</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483078</v>
+        <v>482913</v>
       </c>
       <c r="R33" t="n">
-        <v>6828839</v>
+        <v>6829095</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755473</v>
+        <v>125755502</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483182</v>
+        <v>483078</v>
       </c>
       <c r="R34" t="n">
-        <v>6829175</v>
+        <v>6828839</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755411</v>
+        <v>125755473</v>
       </c>
       <c r="B35" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>482945</v>
+        <v>483182</v>
       </c>
       <c r="R35" t="n">
-        <v>6829125</v>
+        <v>6829175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>125755478</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,32 +4085,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755460</v>
+        <v>125755411</v>
       </c>
       <c r="B37" t="n">
-        <v>91389</v>
+        <v>79590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>482913</v>
+        <v>482945</v>
       </c>
       <c r="R37" t="n">
-        <v>6829095</v>
+        <v>6829125</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4185,7 +4185,7 @@
         <v>125755417</v>
       </c>
       <c r="B38" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125748935</v>
+        <v>125755464</v>
       </c>
       <c r="B39" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,34 +4290,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483071</v>
+        <v>483423</v>
       </c>
       <c r="R39" t="n">
-        <v>6828797</v>
+        <v>6829325</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4364,22 +4364,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125747249</v>
+        <v>125755482</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,14 +4407,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483032</v>
+        <v>482960</v>
       </c>
       <c r="R40" t="n">
-        <v>6828658</v>
+        <v>6828769</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4449,11 +4449,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4466,22 +4461,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125747099</v>
+        <v>125755501</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4509,14 +4504,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483090</v>
+        <v>483071</v>
       </c>
       <c r="R41" t="n">
-        <v>6828658</v>
+        <v>6828833</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4563,22 +4558,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125746848</v>
+        <v>125755508</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4606,14 +4601,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483247</v>
+        <v>483189</v>
       </c>
       <c r="R42" t="n">
-        <v>6828848</v>
+        <v>6828911</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4660,22 +4655,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755501</v>
+        <v>125747249</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4703,14 +4698,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R43" t="n">
-        <v>6828833</v>
+        <v>6828658</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4745,6 +4740,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4757,22 +4757,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755464</v>
+        <v>125746848</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4800,14 +4800,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483423</v>
+        <v>483247</v>
       </c>
       <c r="R44" t="n">
-        <v>6829325</v>
+        <v>6828848</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4854,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755508</v>
+        <v>125748935</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,34 +4877,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483189</v>
+        <v>483071</v>
       </c>
       <c r="R45" t="n">
-        <v>6828911</v>
+        <v>6828797</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4951,22 +4951,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755482</v>
+        <v>125747099</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4994,14 +4994,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>482960</v>
+        <v>483090</v>
       </c>
       <c r="R46" t="n">
-        <v>6828769</v>
+        <v>6828658</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5063,7 +5063,7 @@
         <v>125755466</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755456</v>
+        <v>125755510</v>
       </c>
       <c r="B48" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483114</v>
+        <v>483191</v>
       </c>
       <c r="R48" t="n">
-        <v>6828865</v>
+        <v>6828929</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755510</v>
+        <v>125755456</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483191</v>
+        <v>483114</v>
       </c>
       <c r="R49" t="n">
-        <v>6828929</v>
+        <v>6828865</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5354,7 +5354,7 @@
         <v>125755453</v>
       </c>
       <c r="B50" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125755500</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755483</v>
+        <v>125746158</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5683,14 +5683,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>482971</v>
+        <v>483342</v>
       </c>
       <c r="R53" t="n">
-        <v>6828738</v>
+        <v>6828971</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5737,44 +5737,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755437</v>
+        <v>125755458</v>
       </c>
       <c r="B54" t="n">
-        <v>80072</v>
+        <v>58326</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>103044</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483307</v>
+        <v>483319</v>
       </c>
       <c r="R54" t="n">
-        <v>6829287</v>
+        <v>6829293</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755491</v>
+        <v>125755442</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483015</v>
+        <v>483201</v>
       </c>
       <c r="R55" t="n">
-        <v>6828753</v>
+        <v>6828916</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125746158</v>
+        <v>125755491</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5974,14 +5974,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483342</v>
+        <v>483015</v>
       </c>
       <c r="R56" t="n">
-        <v>6828971</v>
+        <v>6828753</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,44 +6028,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755458</v>
+        <v>125755437</v>
       </c>
       <c r="B57" t="n">
-        <v>58326</v>
+        <v>80076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103044</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483319</v>
+        <v>483307</v>
       </c>
       <c r="R57" t="n">
-        <v>6829293</v>
+        <v>6829287</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755442</v>
+        <v>125755483</v>
       </c>
       <c r="B58" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483201</v>
+        <v>482971</v>
       </c>
       <c r="R58" t="n">
-        <v>6828916</v>
+        <v>6828738</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6237,7 +6237,7 @@
         <v>125755492</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>125755498</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>125755468</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755459</v>
+        <v>125755419</v>
       </c>
       <c r="B63" t="n">
-        <v>91242</v>
+        <v>79004</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483398</v>
+        <v>483005</v>
       </c>
       <c r="R63" t="n">
-        <v>6829316</v>
+        <v>6828754</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755419</v>
+        <v>125755463</v>
       </c>
       <c r="B64" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6735,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483005</v>
+        <v>483450</v>
       </c>
       <c r="R64" t="n">
-        <v>6828754</v>
+        <v>6829306</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755496</v>
+        <v>125755459</v>
       </c>
       <c r="B65" t="n">
-        <v>78968</v>
+        <v>91246</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483054</v>
+        <v>483398</v>
       </c>
       <c r="R65" t="n">
-        <v>6828788</v>
+        <v>6829316</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755463</v>
+        <v>125755496</v>
       </c>
       <c r="B66" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483450</v>
+        <v>483054</v>
       </c>
       <c r="R66" t="n">
-        <v>6829306</v>
+        <v>6828788</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7015,50 +7015,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755431</v>
+        <v>125755525</v>
       </c>
       <c r="B67" t="n">
-        <v>56843</v>
+        <v>78639</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483099</v>
+        <v>483442</v>
       </c>
       <c r="R67" t="n">
-        <v>6828858</v>
+        <v>6829028</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7117,10 +7112,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755525</v>
+        <v>125755517</v>
       </c>
       <c r="B68" t="n">
-        <v>78635</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7128,21 +7123,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7152,10 +7147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483442</v>
+        <v>483386</v>
       </c>
       <c r="R68" t="n">
-        <v>6829028</v>
+        <v>6829003</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7214,45 +7209,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755533</v>
+        <v>125755431</v>
       </c>
       <c r="B69" t="n">
-        <v>78374</v>
+        <v>56843</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483472</v>
+        <v>483099</v>
       </c>
       <c r="R69" t="n">
-        <v>6829305</v>
+        <v>6828858</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7311,10 +7311,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755517</v>
+        <v>125755533</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>78378</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7322,21 +7322,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483386</v>
+        <v>483472</v>
       </c>
       <c r="R70" t="n">
-        <v>6829003</v>
+        <v>6829305</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755412</v>
+        <v>125748016</v>
       </c>
       <c r="B72" t="n">
-        <v>79586</v>
+        <v>57651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,34 +7516,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>482912</v>
+        <v>483071</v>
       </c>
       <c r="R72" t="n">
-        <v>6828922</v>
+        <v>6828797</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7590,12 +7595,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7605,7 +7610,7 @@
         <v>125755472</v>
       </c>
       <c r="B73" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7699,10 +7704,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755489</v>
+        <v>125755412</v>
       </c>
       <c r="B74" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7710,21 +7715,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7734,10 +7739,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483001</v>
+        <v>482912</v>
       </c>
       <c r="R74" t="n">
-        <v>6828740</v>
+        <v>6828922</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7796,10 +7801,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755451</v>
+        <v>125755489</v>
       </c>
       <c r="B75" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,21 +7812,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7831,10 +7836,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483278</v>
+        <v>483001</v>
       </c>
       <c r="R75" t="n">
-        <v>6828932</v>
+        <v>6828740</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7893,10 +7898,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755424</v>
+        <v>125755451</v>
       </c>
       <c r="B76" t="n">
-        <v>79000</v>
+        <v>78730</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7904,21 +7909,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7928,10 +7933,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483162</v>
+        <v>483278</v>
       </c>
       <c r="R76" t="n">
-        <v>6828879</v>
+        <v>6828932</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7990,10 +7995,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755441</v>
+        <v>125755424</v>
       </c>
       <c r="B77" t="n">
-        <v>78727</v>
+        <v>79004</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8001,21 +8006,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8025,10 +8030,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483114</v>
+        <v>483162</v>
       </c>
       <c r="R77" t="n">
-        <v>6828865</v>
+        <v>6828879</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8087,10 +8092,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125748016</v>
+        <v>125755441</v>
       </c>
       <c r="B78" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8098,39 +8103,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483071</v>
+        <v>483114</v>
       </c>
       <c r="R78" t="n">
-        <v>6828797</v>
+        <v>6828865</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8177,22 +8177,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755515</v>
+        <v>125755522</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8200,21 +8200,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483280</v>
+        <v>483303</v>
       </c>
       <c r="R79" t="n">
-        <v>6828952</v>
+        <v>6829017</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,10 +8286,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755514</v>
+        <v>125755515</v>
       </c>
       <c r="B80" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483220</v>
+        <v>483280</v>
       </c>
       <c r="R80" t="n">
-        <v>6828907</v>
+        <v>6828952</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755518</v>
+        <v>125755514</v>
       </c>
       <c r="B81" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483467</v>
+        <v>483220</v>
       </c>
       <c r="R81" t="n">
-        <v>6829027</v>
+        <v>6828907</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8480,10 +8480,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755503</v>
+        <v>125755518</v>
       </c>
       <c r="B82" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483095</v>
+        <v>483467</v>
       </c>
       <c r="R82" t="n">
-        <v>6828845</v>
+        <v>6829027</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,10 +8577,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755474</v>
+        <v>125755503</v>
       </c>
       <c r="B83" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483188</v>
+        <v>483095</v>
       </c>
       <c r="R83" t="n">
-        <v>6829143</v>
+        <v>6828845</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8674,10 +8674,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755522</v>
+        <v>125755474</v>
       </c>
       <c r="B84" t="n">
-        <v>78635</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8685,21 +8685,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483303</v>
+        <v>483188</v>
       </c>
       <c r="R84" t="n">
-        <v>6829017</v>
+        <v>6829143</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8771,10 +8771,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755511</v>
+        <v>125755414</v>
       </c>
       <c r="B85" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8782,21 +8782,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483188</v>
+        <v>483240</v>
       </c>
       <c r="R85" t="n">
-        <v>6828936</v>
+        <v>6828921</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8868,10 +8868,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755504</v>
+        <v>125747880</v>
       </c>
       <c r="B86" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8899,14 +8899,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483117</v>
+        <v>483012</v>
       </c>
       <c r="R86" t="n">
-        <v>6828857</v>
+        <v>6828723</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8953,22 +8953,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755484</v>
+        <v>125755418</v>
       </c>
       <c r="B87" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8976,21 +8976,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>482976</v>
+        <v>482886</v>
       </c>
       <c r="R87" t="n">
-        <v>6828720</v>
+        <v>6828895</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755414</v>
+        <v>125755511</v>
       </c>
       <c r="B88" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9073,21 +9073,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483240</v>
+        <v>483188</v>
       </c>
       <c r="R88" t="n">
-        <v>6828921</v>
+        <v>6828936</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755479</v>
+        <v>125755504</v>
       </c>
       <c r="B89" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>482918</v>
+        <v>483117</v>
       </c>
       <c r="R89" t="n">
-        <v>6828932</v>
+        <v>6828857</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755512</v>
+        <v>125755484</v>
       </c>
       <c r="B90" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483190</v>
+        <v>482976</v>
       </c>
       <c r="R90" t="n">
-        <v>6828942</v>
+        <v>6828720</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755418</v>
+        <v>125755479</v>
       </c>
       <c r="B91" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>482886</v>
+        <v>482918</v>
       </c>
       <c r="R91" t="n">
-        <v>6828895</v>
+        <v>6828932</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125747880</v>
+        <v>125755512</v>
       </c>
       <c r="B92" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9481,14 +9481,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483012</v>
+        <v>483190</v>
       </c>
       <c r="R92" t="n">
-        <v>6828723</v>
+        <v>6828942</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9535,22 +9535,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755435</v>
+        <v>125755446</v>
       </c>
       <c r="B93" t="n">
-        <v>58130</v>
+        <v>80075</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9558,21 +9558,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483450</v>
+        <v>482885</v>
       </c>
       <c r="R93" t="n">
-        <v>6829302</v>
+        <v>6828845</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755469</v>
+        <v>125755413</v>
       </c>
       <c r="B94" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483342</v>
+        <v>482962</v>
       </c>
       <c r="R94" t="n">
-        <v>6829286</v>
+        <v>6828771</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755493</v>
+        <v>125755444</v>
       </c>
       <c r="B95" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9752,21 +9752,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483037</v>
+        <v>483272</v>
       </c>
       <c r="R95" t="n">
-        <v>6828788</v>
+        <v>6829286</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755446</v>
+        <v>125755435</v>
       </c>
       <c r="B96" t="n">
-        <v>80071</v>
+        <v>58130</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9849,21 +9849,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>482885</v>
+        <v>483450</v>
       </c>
       <c r="R96" t="n">
-        <v>6828845</v>
+        <v>6829302</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9935,10 +9935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755413</v>
+        <v>125755526</v>
       </c>
       <c r="B97" t="n">
-        <v>79586</v>
+        <v>78639</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>482962</v>
+        <v>483499</v>
       </c>
       <c r="R97" t="n">
-        <v>6828771</v>
+        <v>6829120</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,32 +10032,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755520</v>
+        <v>125755469</v>
       </c>
       <c r="B98" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483458</v>
+        <v>483342</v>
       </c>
       <c r="R98" t="n">
-        <v>6829089</v>
+        <v>6829286</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,10 +10129,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755444</v>
+        <v>125755493</v>
       </c>
       <c r="B99" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10140,21 +10140,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483272</v>
+        <v>483037</v>
       </c>
       <c r="R99" t="n">
-        <v>6829286</v>
+        <v>6828788</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10226,32 +10226,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755526</v>
+        <v>125755520</v>
       </c>
       <c r="B100" t="n">
-        <v>78635</v>
+        <v>92522</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483499</v>
+        <v>483458</v>
       </c>
       <c r="R100" t="n">
-        <v>6829120</v>
+        <v>6829089</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755507</v>
+        <v>125755422</v>
       </c>
       <c r="B101" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483178</v>
+        <v>483099</v>
       </c>
       <c r="R101" t="n">
-        <v>6828902</v>
+        <v>6828854</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755415</v>
+        <v>125755507</v>
       </c>
       <c r="B102" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483456</v>
+        <v>483178</v>
       </c>
       <c r="R102" t="n">
-        <v>6829062</v>
+        <v>6828902</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755422</v>
+        <v>125755415</v>
       </c>
       <c r="B103" t="n">
-        <v>79000</v>
+        <v>79590</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483099</v>
+        <v>483456</v>
       </c>
       <c r="R103" t="n">
-        <v>6828854</v>
+        <v>6829062</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10617,7 +10617,7 @@
         <v>125755497</v>
       </c>
       <c r="B104" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>125755490</v>
       </c>
       <c r="B105" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>125755485</v>
       </c>
       <c r="B106" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>125746359</v>
       </c>
       <c r="B107" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11002,10 +11002,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755455</v>
+        <v>125746396</v>
       </c>
       <c r="B108" t="n">
-        <v>78726</v>
+        <v>78731</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,34 +11013,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>482942</v>
+        <v>483265</v>
       </c>
       <c r="R108" t="n">
-        <v>6828979</v>
+        <v>6828852</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11087,57 +11087,62 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755532</v>
+        <v>125747874</v>
       </c>
       <c r="B109" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483294</v>
+        <v>483012</v>
       </c>
       <c r="R109" t="n">
-        <v>6829294</v>
+        <v>6828723</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11184,22 +11189,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755523</v>
+        <v>125755455</v>
       </c>
       <c r="B110" t="n">
-        <v>78635</v>
+        <v>78730</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11207,21 +11212,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11231,10 +11236,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483313</v>
+        <v>482942</v>
       </c>
       <c r="R110" t="n">
-        <v>6829017</v>
+        <v>6828979</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11293,45 +11298,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125746396</v>
+        <v>125755532</v>
       </c>
       <c r="B111" t="n">
-        <v>78727</v>
+        <v>80110</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483265</v>
+        <v>483294</v>
       </c>
       <c r="R111" t="n">
-        <v>6828852</v>
+        <v>6829294</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11378,22 +11383,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125747874</v>
+        <v>125755523</v>
       </c>
       <c r="B112" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11401,39 +11406,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483012</v>
+        <v>483313</v>
       </c>
       <c r="R112" t="n">
-        <v>6828723</v>
+        <v>6829017</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11480,22 +11480,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755427</v>
+        <v>125755457</v>
       </c>
       <c r="B113" t="n">
-        <v>79557</v>
+        <v>56834</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11503,34 +11503,39 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>102612</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483472</v>
+        <v>483040</v>
       </c>
       <c r="R113" t="n">
-        <v>6829305</v>
+        <v>6828774</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11589,10 +11594,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755471</v>
+        <v>125755486</v>
       </c>
       <c r="B114" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11624,10 +11629,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483206</v>
+        <v>483015</v>
       </c>
       <c r="R114" t="n">
-        <v>6829193</v>
+        <v>6828711</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11686,32 +11691,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755436</v>
+        <v>125755471</v>
       </c>
       <c r="B115" t="n">
-        <v>80100</v>
+        <v>78972</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11721,10 +11726,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R115" t="n">
-        <v>6829290</v>
+        <v>6829193</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11783,32 +11788,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755486</v>
+        <v>125755436</v>
       </c>
       <c r="B116" t="n">
-        <v>78968</v>
+        <v>80104</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11818,10 +11823,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483015</v>
+        <v>483303</v>
       </c>
       <c r="R116" t="n">
-        <v>6828711</v>
+        <v>6829290</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11880,10 +11885,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755457</v>
+        <v>125755427</v>
       </c>
       <c r="B117" t="n">
-        <v>56834</v>
+        <v>79561</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11891,39 +11896,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>102612</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483040</v>
+        <v>483472</v>
       </c>
       <c r="R117" t="n">
-        <v>6828774</v>
+        <v>6829305</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11985,7 +11985,7 @@
         <v>125755462</v>
       </c>
       <c r="B118" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>125691576</v>
       </c>
       <c r="B119" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755409</v>
+        <v>125755528</v>
       </c>
       <c r="B9" t="n">
-        <v>79590</v>
+        <v>78639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483587</v>
+        <v>483525</v>
       </c>
       <c r="R9" t="n">
-        <v>6829364</v>
+        <v>6829111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755528</v>
+        <v>125755409</v>
       </c>
       <c r="B10" t="n">
-        <v>78639</v>
+        <v>79590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483525</v>
+        <v>483587</v>
       </c>
       <c r="R10" t="n">
-        <v>6829111</v>
+        <v>6829364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755445</v>
+        <v>125755440</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482900</v>
+        <v>482960</v>
       </c>
       <c r="R20" t="n">
-        <v>6828861</v>
+        <v>6828991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755440</v>
+        <v>125755506</v>
       </c>
       <c r="B21" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482960</v>
+        <v>483162</v>
       </c>
       <c r="R21" t="n">
-        <v>6828991</v>
+        <v>6828887</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755421</v>
+        <v>125755480</v>
       </c>
       <c r="B22" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483044</v>
+        <v>482885</v>
       </c>
       <c r="R22" t="n">
-        <v>6828792</v>
+        <v>6828897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755506</v>
+        <v>125755494</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483162</v>
+        <v>483047</v>
       </c>
       <c r="R23" t="n">
-        <v>6828887</v>
+        <v>6828790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755480</v>
+        <v>125755445</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482885</v>
+        <v>482900</v>
       </c>
       <c r="R24" t="n">
-        <v>6828897</v>
+        <v>6828861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755494</v>
+        <v>125755421</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,21 +2932,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483047</v>
+        <v>483044</v>
       </c>
       <c r="R25" t="n">
-        <v>6828790</v>
+        <v>6828792</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755464</v>
+        <v>125747249</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4310,14 +4310,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483423</v>
+        <v>483032</v>
       </c>
       <c r="R39" t="n">
-        <v>6829325</v>
+        <v>6828658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4352,6 +4352,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4364,19 +4369,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755482</v>
+        <v>125746848</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4407,14 +4412,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>482960</v>
+        <v>483247</v>
       </c>
       <c r="R40" t="n">
-        <v>6828769</v>
+        <v>6828848</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4461,22 +4466,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755501</v>
+        <v>125748935</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4489,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>483071</v>
       </c>
       <c r="R41" t="n">
-        <v>6828833</v>
+        <v>6828797</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4558,19 +4563,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755508</v>
+        <v>125747099</v>
       </c>
       <c r="B42" t="n">
         <v>78972</v>
@@ -4601,14 +4606,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483189</v>
+        <v>483090</v>
       </c>
       <c r="R42" t="n">
-        <v>6828911</v>
+        <v>6828658</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4655,19 +4660,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125747249</v>
+        <v>125755501</v>
       </c>
       <c r="B43" t="n">
         <v>78972</v>
@@ -4698,14 +4703,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R43" t="n">
-        <v>6828658</v>
+        <v>6828833</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4740,11 +4745,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4757,19 +4757,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125746848</v>
+        <v>125755508</v>
       </c>
       <c r="B44" t="n">
         <v>78972</v>
@@ -4800,14 +4800,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483247</v>
+        <v>483189</v>
       </c>
       <c r="R44" t="n">
-        <v>6828848</v>
+        <v>6828911</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4854,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125748935</v>
+        <v>125755464</v>
       </c>
       <c r="B45" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,34 +4877,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483071</v>
+        <v>483423</v>
       </c>
       <c r="R45" t="n">
-        <v>6828797</v>
+        <v>6829325</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4951,19 +4951,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125747099</v>
+        <v>125755482</v>
       </c>
       <c r="B46" t="n">
         <v>78972</v>
@@ -4994,14 +4994,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483090</v>
+        <v>482960</v>
       </c>
       <c r="R46" t="n">
-        <v>6828658</v>
+        <v>6828769</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7015,45 +7015,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755525</v>
+        <v>125755431</v>
       </c>
       <c r="B67" t="n">
-        <v>78639</v>
+        <v>56843</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483442</v>
+        <v>483099</v>
       </c>
       <c r="R67" t="n">
-        <v>6829028</v>
+        <v>6828858</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,10 +7117,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755517</v>
+        <v>125755525</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7123,21 +7128,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7147,10 +7152,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483386</v>
+        <v>483442</v>
       </c>
       <c r="R68" t="n">
-        <v>6829003</v>
+        <v>6829028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7209,50 +7214,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755431</v>
+        <v>125755517</v>
       </c>
       <c r="B69" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483099</v>
+        <v>483386</v>
       </c>
       <c r="R69" t="n">
-        <v>6828858</v>
+        <v>6829003</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125748016</v>
+        <v>125755441</v>
       </c>
       <c r="B72" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,39 +7516,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483071</v>
+        <v>483114</v>
       </c>
       <c r="R72" t="n">
-        <v>6828797</v>
+        <v>6828865</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7595,22 +7590,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755472</v>
+        <v>125748016</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7618,34 +7613,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483203</v>
+        <v>483071</v>
       </c>
       <c r="R73" t="n">
-        <v>6829189</v>
+        <v>6828797</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7692,22 +7692,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755412</v>
+        <v>125755424</v>
       </c>
       <c r="B74" t="n">
-        <v>79590</v>
+        <v>79004</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7715,21 +7715,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>482912</v>
+        <v>483162</v>
       </c>
       <c r="R74" t="n">
-        <v>6828922</v>
+        <v>6828879</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755489</v>
+        <v>125755472</v>
       </c>
       <c r="B75" t="n">
         <v>78972</v>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483001</v>
+        <v>483203</v>
       </c>
       <c r="R75" t="n">
-        <v>6828740</v>
+        <v>6829189</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7898,10 +7898,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755451</v>
+        <v>125755412</v>
       </c>
       <c r="B76" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,21 +7909,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483278</v>
+        <v>482912</v>
       </c>
       <c r="R76" t="n">
-        <v>6828932</v>
+        <v>6828922</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7995,10 +7995,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755424</v>
+        <v>125755489</v>
       </c>
       <c r="B77" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483162</v>
+        <v>483001</v>
       </c>
       <c r="R77" t="n">
-        <v>6828879</v>
+        <v>6828740</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8092,10 +8092,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755441</v>
+        <v>125755451</v>
       </c>
       <c r="B78" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8103,21 +8103,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483114</v>
+        <v>483278</v>
       </c>
       <c r="R78" t="n">
-        <v>6828865</v>
+        <v>6828932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755446</v>
+        <v>125755526</v>
       </c>
       <c r="B93" t="n">
-        <v>80075</v>
+        <v>78639</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9558,21 +9558,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>482885</v>
+        <v>483499</v>
       </c>
       <c r="R93" t="n">
-        <v>6828845</v>
+        <v>6829120</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755413</v>
+        <v>125755469</v>
       </c>
       <c r="B94" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>482962</v>
+        <v>483342</v>
       </c>
       <c r="R94" t="n">
-        <v>6828771</v>
+        <v>6829286</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755444</v>
+        <v>125755493</v>
       </c>
       <c r="B95" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9752,21 +9752,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483272</v>
+        <v>483037</v>
       </c>
       <c r="R95" t="n">
-        <v>6829286</v>
+        <v>6828788</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755435</v>
+        <v>125755520</v>
       </c>
       <c r="B96" t="n">
-        <v>58130</v>
+        <v>92522</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103018</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483450</v>
+        <v>483458</v>
       </c>
       <c r="R96" t="n">
-        <v>6829302</v>
+        <v>6829089</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9935,10 +9935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755526</v>
+        <v>125755446</v>
       </c>
       <c r="B97" t="n">
-        <v>78639</v>
+        <v>80075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483499</v>
+        <v>482885</v>
       </c>
       <c r="R97" t="n">
-        <v>6829120</v>
+        <v>6828845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755469</v>
+        <v>125755413</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483342</v>
+        <v>482962</v>
       </c>
       <c r="R98" t="n">
-        <v>6829286</v>
+        <v>6828771</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,10 +10129,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755493</v>
+        <v>125755444</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10140,21 +10140,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483037</v>
+        <v>483272</v>
       </c>
       <c r="R99" t="n">
-        <v>6828788</v>
+        <v>6829286</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10226,32 +10226,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755520</v>
+        <v>125755435</v>
       </c>
       <c r="B100" t="n">
-        <v>92522</v>
+        <v>58130</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>103018</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483458</v>
+        <v>483450</v>
       </c>
       <c r="R100" t="n">
-        <v>6829089</v>
+        <v>6829302</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11492,10 +11492,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755457</v>
+        <v>125755486</v>
       </c>
       <c r="B113" t="n">
-        <v>56834</v>
+        <v>78972</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11503,39 +11503,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483040</v>
+        <v>483015</v>
       </c>
       <c r="R113" t="n">
-        <v>6828774</v>
+        <v>6828711</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11594,7 +11589,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755486</v>
+        <v>125755471</v>
       </c>
       <c r="B114" t="n">
         <v>78972</v>
@@ -11629,10 +11624,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483015</v>
+        <v>483206</v>
       </c>
       <c r="R114" t="n">
-        <v>6828711</v>
+        <v>6829193</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11691,10 +11686,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755471</v>
+        <v>125755457</v>
       </c>
       <c r="B115" t="n">
-        <v>78972</v>
+        <v>56834</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11702,34 +11697,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483206</v>
+        <v>483040</v>
       </c>
       <c r="R115" t="n">
-        <v>6829193</v>
+        <v>6828774</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11788,32 +11788,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755436</v>
+        <v>125755427</v>
       </c>
       <c r="B116" t="n">
-        <v>80104</v>
+        <v>79561</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11823,10 +11823,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483303</v>
+        <v>483472</v>
       </c>
       <c r="R116" t="n">
-        <v>6829290</v>
+        <v>6829305</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11885,32 +11885,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755427</v>
+        <v>125755436</v>
       </c>
       <c r="B117" t="n">
-        <v>79561</v>
+        <v>80104</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11920,10 +11920,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483472</v>
+        <v>483303</v>
       </c>
       <c r="R117" t="n">
-        <v>6829305</v>
+        <v>6829290</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755452</v>
+        <v>125755439</v>
       </c>
       <c r="B12" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483587</v>
+        <v>483586</v>
       </c>
       <c r="R12" t="n">
         <v>6829364</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755439</v>
+        <v>125755452</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483586</v>
+        <v>483587</v>
       </c>
       <c r="R14" t="n">
         <v>6829364</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125746064</v>
+        <v>125755416</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,34 +1957,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483474</v>
+        <v>483454</v>
       </c>
       <c r="R15" t="n">
-        <v>6829119</v>
+        <v>6829082</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,19 +2031,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125746931</v>
+        <v>125755488</v>
       </c>
       <c r="B16" t="n">
         <v>78972</v>
@@ -2074,14 +2074,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483156</v>
+        <v>483019</v>
       </c>
       <c r="R16" t="n">
-        <v>6828728</v>
+        <v>6828737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,11 +2116,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2133,19 +2128,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755488</v>
+        <v>125755475</v>
       </c>
       <c r="B17" t="n">
         <v>78972</v>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483019</v>
+        <v>483169</v>
       </c>
       <c r="R17" t="n">
-        <v>6828737</v>
+        <v>6829132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755475</v>
+        <v>125746064</v>
       </c>
       <c r="B18" t="n">
         <v>78972</v>
@@ -2273,14 +2268,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483169</v>
+        <v>483474</v>
       </c>
       <c r="R18" t="n">
-        <v>6829132</v>
+        <v>6829119</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,22 +2322,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755416</v>
+        <v>125746931</v>
       </c>
       <c r="B19" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,34 +2345,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483454</v>
+        <v>483156</v>
       </c>
       <c r="R19" t="n">
-        <v>6829082</v>
+        <v>6828728</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2412,6 +2407,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2424,22 +2424,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755440</v>
+        <v>125755445</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482960</v>
+        <v>482900</v>
       </c>
       <c r="R20" t="n">
-        <v>6828991</v>
+        <v>6828861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755506</v>
+        <v>125755421</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483162</v>
+        <v>483044</v>
       </c>
       <c r="R21" t="n">
-        <v>6828887</v>
+        <v>6828792</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755480</v>
+        <v>125755506</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482885</v>
+        <v>483162</v>
       </c>
       <c r="R22" t="n">
-        <v>6828897</v>
+        <v>6828887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755494</v>
+        <v>125755480</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483047</v>
+        <v>482885</v>
       </c>
       <c r="R23" t="n">
-        <v>6828790</v>
+        <v>6828897</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755445</v>
+        <v>125755494</v>
       </c>
       <c r="B24" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482900</v>
+        <v>483047</v>
       </c>
       <c r="R24" t="n">
-        <v>6828861</v>
+        <v>6828790</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755421</v>
+        <v>125745798</v>
       </c>
       <c r="B25" t="n">
-        <v>79004</v>
+        <v>79590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483044</v>
+        <v>483474</v>
       </c>
       <c r="R25" t="n">
-        <v>6828792</v>
+        <v>6829119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,22 +3006,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125745798</v>
+        <v>125755440</v>
       </c>
       <c r="B26" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483474</v>
+        <v>482960</v>
       </c>
       <c r="R26" t="n">
-        <v>6829119</v>
+        <v>6828991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3103,12 +3103,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755516</v>
+        <v>125755428</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483291</v>
+        <v>483280</v>
       </c>
       <c r="R30" t="n">
-        <v>6828969</v>
+        <v>6828942</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755481</v>
+        <v>125755516</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>482929</v>
+        <v>483291</v>
       </c>
       <c r="R31" t="n">
-        <v>6828797</v>
+        <v>6828969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755428</v>
+        <v>125755481</v>
       </c>
       <c r="B32" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483280</v>
+        <v>482929</v>
       </c>
       <c r="R32" t="n">
-        <v>6828942</v>
+        <v>6828797</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755460</v>
+        <v>125755411</v>
       </c>
       <c r="B33" t="n">
-        <v>91393</v>
+        <v>79590</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>482913</v>
+        <v>482945</v>
       </c>
       <c r="R33" t="n">
-        <v>6829095</v>
+        <v>6829125</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,32 +3988,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755478</v>
+        <v>125755460</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483147</v>
+        <v>482913</v>
       </c>
       <c r="R36" t="n">
         <v>6829095</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755411</v>
+        <v>125755478</v>
       </c>
       <c r="B37" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>482945</v>
+        <v>483147</v>
       </c>
       <c r="R37" t="n">
-        <v>6829125</v>
+        <v>6829095</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125747249</v>
+        <v>125755501</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4310,14 +4310,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R39" t="n">
-        <v>6828658</v>
+        <v>6828833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4352,11 +4352,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4369,19 +4364,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125746848</v>
+        <v>125755464</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4412,14 +4407,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483247</v>
+        <v>483423</v>
       </c>
       <c r="R40" t="n">
-        <v>6828848</v>
+        <v>6829325</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,22 +4461,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125748935</v>
+        <v>125755508</v>
       </c>
       <c r="B41" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483071</v>
+        <v>483189</v>
       </c>
       <c r="R41" t="n">
-        <v>6828797</v>
+        <v>6828911</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4563,19 +4558,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125747099</v>
+        <v>125755482</v>
       </c>
       <c r="B42" t="n">
         <v>78972</v>
@@ -4606,14 +4601,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483090</v>
+        <v>482960</v>
       </c>
       <c r="R42" t="n">
-        <v>6828658</v>
+        <v>6828769</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4660,19 +4655,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755501</v>
+        <v>125747099</v>
       </c>
       <c r="B43" t="n">
         <v>78972</v>
@@ -4703,14 +4698,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483071</v>
+        <v>483090</v>
       </c>
       <c r="R43" t="n">
-        <v>6828833</v>
+        <v>6828658</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4757,19 +4752,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755508</v>
+        <v>125747249</v>
       </c>
       <c r="B44" t="n">
         <v>78972</v>
@@ -4800,14 +4795,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483189</v>
+        <v>483032</v>
       </c>
       <c r="R44" t="n">
-        <v>6828911</v>
+        <v>6828658</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4842,6 +4837,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -4854,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755464</v>
+        <v>125748935</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,34 +4877,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483423</v>
+        <v>483071</v>
       </c>
       <c r="R45" t="n">
-        <v>6829325</v>
+        <v>6828797</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4951,19 +4951,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755482</v>
+        <v>125746416</v>
       </c>
       <c r="B46" t="n">
         <v>78972</v>
@@ -4994,14 +4994,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>482960</v>
+        <v>483247</v>
       </c>
       <c r="R46" t="n">
-        <v>6828769</v>
+        <v>6828848</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5048,22 +5048,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755466</v>
+        <v>125755453</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483400</v>
+        <v>482979</v>
       </c>
       <c r="R47" t="n">
-        <v>6829318</v>
+        <v>6829140</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755510</v>
+        <v>125755456</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483191</v>
+        <v>483114</v>
       </c>
       <c r="R48" t="n">
-        <v>6828929</v>
+        <v>6828865</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755456</v>
+        <v>125755536</v>
       </c>
       <c r="B49" t="n">
-        <v>78730</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483114</v>
+        <v>483037</v>
       </c>
       <c r="R49" t="n">
-        <v>6828865</v>
+        <v>6828775</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5325,6 +5330,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5351,10 +5361,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755453</v>
+        <v>125755466</v>
       </c>
       <c r="B50" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5372,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>482979</v>
+        <v>483400</v>
       </c>
       <c r="R50" t="n">
-        <v>6829140</v>
+        <v>6829318</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,7 +5458,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755500</v>
+        <v>125755510</v>
       </c>
       <c r="B51" t="n">
         <v>78972</v>
@@ -5483,10 +5493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483068</v>
+        <v>483191</v>
       </c>
       <c r="R51" t="n">
-        <v>6828819</v>
+        <v>6828929</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5545,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755536</v>
+        <v>125755500</v>
       </c>
       <c r="B52" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,39 +5566,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483037</v>
+        <v>483068</v>
       </c>
       <c r="R52" t="n">
-        <v>6828775</v>
+        <v>6828819</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5621,11 +5626,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5652,45 +5652,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125746158</v>
+        <v>125755458</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>58326</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483342</v>
+        <v>483319</v>
       </c>
       <c r="R53" t="n">
-        <v>6828971</v>
+        <v>6829293</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5737,57 +5737,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755458</v>
+        <v>125746158</v>
       </c>
       <c r="B54" t="n">
-        <v>58326</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483319</v>
+        <v>483342</v>
       </c>
       <c r="R54" t="n">
-        <v>6829293</v>
+        <v>6828971</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5834,22 +5834,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755442</v>
+        <v>125755483</v>
       </c>
       <c r="B55" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483201</v>
+        <v>482971</v>
       </c>
       <c r="R55" t="n">
-        <v>6828916</v>
+        <v>6828738</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755491</v>
+        <v>125755437</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5954,21 +5954,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483015</v>
+        <v>483307</v>
       </c>
       <c r="R56" t="n">
-        <v>6828753</v>
+        <v>6829287</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755437</v>
+        <v>125755491</v>
       </c>
       <c r="B57" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6051,21 +6051,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483307</v>
+        <v>483015</v>
       </c>
       <c r="R57" t="n">
-        <v>6829287</v>
+        <v>6828753</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755483</v>
+        <v>125755442</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>482971</v>
+        <v>483201</v>
       </c>
       <c r="R58" t="n">
-        <v>6828738</v>
+        <v>6828916</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755463</v>
+        <v>125755496</v>
       </c>
       <c r="B64" t="n">
         <v>78972</v>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483450</v>
+        <v>483054</v>
       </c>
       <c r="R64" t="n">
-        <v>6829306</v>
+        <v>6828788</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6918,7 +6918,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755496</v>
+        <v>125755463</v>
       </c>
       <c r="B66" t="n">
         <v>78972</v>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483054</v>
+        <v>483450</v>
       </c>
       <c r="R66" t="n">
-        <v>6828788</v>
+        <v>6829306</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7015,50 +7015,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755431</v>
+        <v>125755533</v>
       </c>
       <c r="B67" t="n">
-        <v>56843</v>
+        <v>78378</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483099</v>
+        <v>483472</v>
       </c>
       <c r="R67" t="n">
-        <v>6828858</v>
+        <v>6829305</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7311,45 +7306,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755533</v>
+        <v>125755431</v>
       </c>
       <c r="B70" t="n">
-        <v>78378</v>
+        <v>56843</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483472</v>
+        <v>483099</v>
       </c>
       <c r="R70" t="n">
-        <v>6829305</v>
+        <v>6828858</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755441</v>
+        <v>125755424</v>
       </c>
       <c r="B72" t="n">
-        <v>78731</v>
+        <v>79004</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,21 +7516,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483114</v>
+        <v>483162</v>
       </c>
       <c r="R72" t="n">
-        <v>6828865</v>
+        <v>6828879</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125748016</v>
+        <v>125755472</v>
       </c>
       <c r="B73" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7613,39 +7613,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483071</v>
+        <v>483203</v>
       </c>
       <c r="R73" t="n">
-        <v>6828797</v>
+        <v>6829189</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7692,22 +7687,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755424</v>
+        <v>125755489</v>
       </c>
       <c r="B74" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7715,21 +7710,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7739,10 +7734,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483162</v>
+        <v>483001</v>
       </c>
       <c r="R74" t="n">
-        <v>6828879</v>
+        <v>6828740</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7801,10 +7796,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755472</v>
+        <v>125755441</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7812,21 +7807,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7836,10 +7831,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483203</v>
+        <v>483114</v>
       </c>
       <c r="R75" t="n">
-        <v>6829189</v>
+        <v>6828865</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7898,10 +7893,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755412</v>
+        <v>125755451</v>
       </c>
       <c r="B76" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,21 +7904,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7933,10 +7928,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>482912</v>
+        <v>483278</v>
       </c>
       <c r="R76" t="n">
-        <v>6828922</v>
+        <v>6828932</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7995,10 +7990,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755489</v>
+        <v>125755412</v>
       </c>
       <c r="B77" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8006,21 +8001,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8030,10 +8025,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483001</v>
+        <v>482912</v>
       </c>
       <c r="R77" t="n">
-        <v>6828740</v>
+        <v>6828922</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8092,10 +8087,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755451</v>
+        <v>125748016</v>
       </c>
       <c r="B78" t="n">
-        <v>78730</v>
+        <v>57651</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8103,34 +8098,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483278</v>
+        <v>483071</v>
       </c>
       <c r="R78" t="n">
-        <v>6828932</v>
+        <v>6828797</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8177,12 +8177,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8868,10 +8868,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125747880</v>
+        <v>125755418</v>
       </c>
       <c r="B86" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8879,34 +8879,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483012</v>
+        <v>482886</v>
       </c>
       <c r="R86" t="n">
-        <v>6828723</v>
+        <v>6828895</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8953,22 +8953,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755418</v>
+        <v>125755511</v>
       </c>
       <c r="B87" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8976,21 +8976,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>482886</v>
+        <v>483188</v>
       </c>
       <c r="R87" t="n">
-        <v>6828895</v>
+        <v>6828936</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9062,7 +9062,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755511</v>
+        <v>125755504</v>
       </c>
       <c r="B88" t="n">
         <v>78972</v>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483188</v>
+        <v>483117</v>
       </c>
       <c r="R88" t="n">
-        <v>6828936</v>
+        <v>6828857</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,7 +9159,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755504</v>
+        <v>125755484</v>
       </c>
       <c r="B89" t="n">
         <v>78972</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483117</v>
+        <v>482976</v>
       </c>
       <c r="R89" t="n">
-        <v>6828857</v>
+        <v>6828720</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9256,7 +9256,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755484</v>
+        <v>125755479</v>
       </c>
       <c r="B90" t="n">
         <v>78972</v>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482976</v>
+        <v>482918</v>
       </c>
       <c r="R90" t="n">
-        <v>6828720</v>
+        <v>6828932</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755479</v>
+        <v>125755512</v>
       </c>
       <c r="B91" t="n">
         <v>78972</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>482918</v>
+        <v>483190</v>
       </c>
       <c r="R91" t="n">
-        <v>6828932</v>
+        <v>6828942</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755512</v>
+        <v>125747880</v>
       </c>
       <c r="B92" t="n">
         <v>78972</v>
@@ -9481,14 +9481,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483190</v>
+        <v>483012</v>
       </c>
       <c r="R92" t="n">
-        <v>6828942</v>
+        <v>6828723</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9535,12 +9535,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755469</v>
+        <v>125755435</v>
       </c>
       <c r="B94" t="n">
-        <v>78972</v>
+        <v>58130</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483342</v>
+        <v>483450</v>
       </c>
       <c r="R94" t="n">
-        <v>6829286</v>
+        <v>6829302</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755493</v>
+        <v>125755413</v>
       </c>
       <c r="B95" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9752,21 +9752,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483037</v>
+        <v>482962</v>
       </c>
       <c r="R95" t="n">
-        <v>6828788</v>
+        <v>6828771</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755520</v>
+        <v>125755444</v>
       </c>
       <c r="B96" t="n">
-        <v>92522</v>
+        <v>80075</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483458</v>
+        <v>483272</v>
       </c>
       <c r="R96" t="n">
-        <v>6829089</v>
+        <v>6829286</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755413</v>
+        <v>125755469</v>
       </c>
       <c r="B98" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>482962</v>
+        <v>483342</v>
       </c>
       <c r="R98" t="n">
-        <v>6828771</v>
+        <v>6829286</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,10 +10129,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755444</v>
+        <v>125755493</v>
       </c>
       <c r="B99" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10140,21 +10140,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483272</v>
+        <v>483037</v>
       </c>
       <c r="R99" t="n">
-        <v>6829286</v>
+        <v>6828788</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10226,32 +10226,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755435</v>
+        <v>125755520</v>
       </c>
       <c r="B100" t="n">
-        <v>58130</v>
+        <v>92522</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103018</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483450</v>
+        <v>483458</v>
       </c>
       <c r="R100" t="n">
-        <v>6829302</v>
+        <v>6829089</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755422</v>
+        <v>125755415</v>
       </c>
       <c r="B101" t="n">
-        <v>79004</v>
+        <v>79590</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483099</v>
+        <v>483456</v>
       </c>
       <c r="R101" t="n">
-        <v>6828854</v>
+        <v>6829062</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755507</v>
+        <v>125755422</v>
       </c>
       <c r="B102" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483178</v>
+        <v>483099</v>
       </c>
       <c r="R102" t="n">
-        <v>6828902</v>
+        <v>6828854</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755415</v>
+        <v>125755507</v>
       </c>
       <c r="B103" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483456</v>
+        <v>483178</v>
       </c>
       <c r="R103" t="n">
-        <v>6829062</v>
+        <v>6828902</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755497</v>
+        <v>125746359</v>
       </c>
       <c r="B104" t="n">
         <v>78972</v>
@@ -10645,14 +10645,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483063</v>
+        <v>483265</v>
       </c>
       <c r="R104" t="n">
-        <v>6828803</v>
+        <v>6828852</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10699,19 +10699,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755490</v>
+        <v>125755497</v>
       </c>
       <c r="B105" t="n">
         <v>78972</v>
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483007</v>
+        <v>483063</v>
       </c>
       <c r="R105" t="n">
-        <v>6828754</v>
+        <v>6828803</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10808,7 +10808,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755485</v>
+        <v>125755490</v>
       </c>
       <c r="B106" t="n">
         <v>78972</v>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483002</v>
+        <v>483007</v>
       </c>
       <c r="R106" t="n">
-        <v>6828695</v>
+        <v>6828754</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125746359</v>
+        <v>125755485</v>
       </c>
       <c r="B107" t="n">
         <v>78972</v>
@@ -10936,14 +10936,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483265</v>
+        <v>483002</v>
       </c>
       <c r="R107" t="n">
-        <v>6828852</v>
+        <v>6828695</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10990,22 +10990,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125746396</v>
+        <v>125755455</v>
       </c>
       <c r="B108" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,34 +11013,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483265</v>
+        <v>482942</v>
       </c>
       <c r="R108" t="n">
-        <v>6828852</v>
+        <v>6828979</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11087,62 +11087,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125747874</v>
+        <v>125755532</v>
       </c>
       <c r="B109" t="n">
-        <v>57651</v>
+        <v>80110</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483012</v>
+        <v>483294</v>
       </c>
       <c r="R109" t="n">
-        <v>6828723</v>
+        <v>6829294</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11189,22 +11184,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755455</v>
+        <v>125755523</v>
       </c>
       <c r="B110" t="n">
-        <v>78730</v>
+        <v>78639</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11212,21 +11207,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11236,10 +11231,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>482942</v>
+        <v>483313</v>
       </c>
       <c r="R110" t="n">
-        <v>6828979</v>
+        <v>6829017</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11298,45 +11293,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755532</v>
+        <v>125746396</v>
       </c>
       <c r="B111" t="n">
-        <v>80110</v>
+        <v>78731</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483294</v>
+        <v>483265</v>
       </c>
       <c r="R111" t="n">
-        <v>6829294</v>
+        <v>6828852</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11383,22 +11378,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755523</v>
+        <v>125747874</v>
       </c>
       <c r="B112" t="n">
-        <v>78639</v>
+        <v>57651</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11406,34 +11401,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483313</v>
+        <v>483012</v>
       </c>
       <c r="R112" t="n">
-        <v>6829017</v>
+        <v>6828723</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11480,12 +11480,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755506</v>
+        <v>125755440</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483162</v>
+        <v>482960</v>
       </c>
       <c r="R22" t="n">
-        <v>6828887</v>
+        <v>6828991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755480</v>
+        <v>125755506</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482885</v>
+        <v>483162</v>
       </c>
       <c r="R23" t="n">
-        <v>6828897</v>
+        <v>6828887</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755494</v>
+        <v>125755480</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483047</v>
+        <v>482885</v>
       </c>
       <c r="R24" t="n">
-        <v>6828790</v>
+        <v>6828897</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125745798</v>
+        <v>125755494</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483474</v>
+        <v>483047</v>
       </c>
       <c r="R25" t="n">
-        <v>6829119</v>
+        <v>6828790</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,22 +3006,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755440</v>
+        <v>125745798</v>
       </c>
       <c r="B26" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482960</v>
+        <v>483474</v>
       </c>
       <c r="R26" t="n">
-        <v>6828991</v>
+        <v>6829119</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3103,12 +3103,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755428</v>
+        <v>125755516</v>
       </c>
       <c r="B30" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483280</v>
+        <v>483291</v>
       </c>
       <c r="R30" t="n">
-        <v>6828942</v>
+        <v>6828969</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755516</v>
+        <v>125755481</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483291</v>
+        <v>482929</v>
       </c>
       <c r="R31" t="n">
-        <v>6828969</v>
+        <v>6828797</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755481</v>
+        <v>125755428</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>482929</v>
+        <v>483280</v>
       </c>
       <c r="R32" t="n">
-        <v>6828797</v>
+        <v>6828942</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755533</v>
+        <v>125755525</v>
       </c>
       <c r="B67" t="n">
-        <v>78378</v>
+        <v>78639</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483472</v>
+        <v>483442</v>
       </c>
       <c r="R67" t="n">
-        <v>6829305</v>
+        <v>6829028</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,45 +7112,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755525</v>
+        <v>125755431</v>
       </c>
       <c r="B68" t="n">
-        <v>78639</v>
+        <v>56843</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483442</v>
+        <v>483099</v>
       </c>
       <c r="R68" t="n">
-        <v>6829028</v>
+        <v>6828858</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7209,10 +7214,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755517</v>
+        <v>125755433</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7220,21 +7225,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7244,10 +7249,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483386</v>
+        <v>483307</v>
       </c>
       <c r="R69" t="n">
-        <v>6829003</v>
+        <v>6829287</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7306,50 +7311,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755431</v>
+        <v>125755533</v>
       </c>
       <c r="B70" t="n">
-        <v>56843</v>
+        <v>78378</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483099</v>
+        <v>483472</v>
       </c>
       <c r="R70" t="n">
-        <v>6828858</v>
+        <v>6829305</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755433</v>
+        <v>125755517</v>
       </c>
       <c r="B71" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483307</v>
+        <v>483386</v>
       </c>
       <c r="R71" t="n">
-        <v>6829287</v>
+        <v>6829003</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755528</v>
+        <v>125755409</v>
       </c>
       <c r="B9" t="n">
-        <v>78639</v>
+        <v>79590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483525</v>
+        <v>483587</v>
       </c>
       <c r="R9" t="n">
-        <v>6829111</v>
+        <v>6829364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755409</v>
+        <v>125755528</v>
       </c>
       <c r="B10" t="n">
-        <v>79590</v>
+        <v>78639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483587</v>
+        <v>483525</v>
       </c>
       <c r="R10" t="n">
-        <v>6829364</v>
+        <v>6829111</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755440</v>
+        <v>125755506</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482960</v>
+        <v>483162</v>
       </c>
       <c r="R22" t="n">
-        <v>6828991</v>
+        <v>6828887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755506</v>
+        <v>125755480</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483162</v>
+        <v>482885</v>
       </c>
       <c r="R23" t="n">
-        <v>6828887</v>
+        <v>6828897</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755480</v>
+        <v>125755494</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482885</v>
+        <v>483047</v>
       </c>
       <c r="R24" t="n">
-        <v>6828897</v>
+        <v>6828790</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755494</v>
+        <v>125745798</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483047</v>
+        <v>483474</v>
       </c>
       <c r="R25" t="n">
-        <v>6828790</v>
+        <v>6829119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,22 +3006,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125745798</v>
+        <v>125755440</v>
       </c>
       <c r="B26" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483474</v>
+        <v>482960</v>
       </c>
       <c r="R26" t="n">
-        <v>6829119</v>
+        <v>6828991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3103,39 +3103,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755513</v>
+        <v>125755530</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>80110</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R27" t="n">
-        <v>6828917</v>
+        <v>6829288</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3212,27 +3212,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755530</v>
+        <v>125755513</v>
       </c>
       <c r="B28" t="n">
-        <v>80110</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R28" t="n">
-        <v>6829288</v>
+        <v>6828917</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755516</v>
+        <v>125755428</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483291</v>
+        <v>483280</v>
       </c>
       <c r="R30" t="n">
-        <v>6828969</v>
+        <v>6828942</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755481</v>
+        <v>125755516</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>482929</v>
+        <v>483291</v>
       </c>
       <c r="R31" t="n">
-        <v>6828797</v>
+        <v>6828969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755428</v>
+        <v>125755481</v>
       </c>
       <c r="B32" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483280</v>
+        <v>482929</v>
       </c>
       <c r="R32" t="n">
-        <v>6828942</v>
+        <v>6828797</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755411</v>
+        <v>125755502</v>
       </c>
       <c r="B33" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>482945</v>
+        <v>483078</v>
       </c>
       <c r="R33" t="n">
-        <v>6829125</v>
+        <v>6828839</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755502</v>
+        <v>125755473</v>
       </c>
       <c r="B34" t="n">
         <v>78972</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483078</v>
+        <v>483182</v>
       </c>
       <c r="R34" t="n">
-        <v>6828839</v>
+        <v>6829175</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,32 +3891,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755473</v>
+        <v>125755460</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483182</v>
+        <v>482913</v>
       </c>
       <c r="R35" t="n">
-        <v>6829175</v>
+        <v>6829095</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,32 +3988,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755460</v>
+        <v>125755478</v>
       </c>
       <c r="B36" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>482913</v>
+        <v>483147</v>
       </c>
       <c r="R36" t="n">
         <v>6829095</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755478</v>
+        <v>125755411</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483147</v>
+        <v>482945</v>
       </c>
       <c r="R37" t="n">
-        <v>6829095</v>
+        <v>6829125</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755525</v>
+        <v>125755533</v>
       </c>
       <c r="B67" t="n">
-        <v>78639</v>
+        <v>78378</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483442</v>
+        <v>483472</v>
       </c>
       <c r="R67" t="n">
-        <v>6829028</v>
+        <v>6829305</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,50 +7112,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755431</v>
+        <v>125755517</v>
       </c>
       <c r="B68" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483099</v>
+        <v>483386</v>
       </c>
       <c r="R68" t="n">
-        <v>6828858</v>
+        <v>6829003</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7214,10 +7209,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755433</v>
+        <v>125755525</v>
       </c>
       <c r="B69" t="n">
-        <v>57811</v>
+        <v>78639</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7225,21 +7220,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7249,10 +7244,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483307</v>
+        <v>483442</v>
       </c>
       <c r="R69" t="n">
-        <v>6829287</v>
+        <v>6829028</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7311,45 +7306,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755533</v>
+        <v>125755431</v>
       </c>
       <c r="B70" t="n">
-        <v>78378</v>
+        <v>56843</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483472</v>
+        <v>483099</v>
       </c>
       <c r="R70" t="n">
-        <v>6829305</v>
+        <v>6828858</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755517</v>
+        <v>125755433</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483386</v>
+        <v>483307</v>
       </c>
       <c r="R71" t="n">
-        <v>6829003</v>
+        <v>6829287</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755424</v>
+        <v>125755441</v>
       </c>
       <c r="B72" t="n">
-        <v>79004</v>
+        <v>78731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,21 +7516,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483162</v>
+        <v>483114</v>
       </c>
       <c r="R72" t="n">
-        <v>6828879</v>
+        <v>6828865</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755472</v>
+        <v>125755451</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7613,21 +7613,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483203</v>
+        <v>483278</v>
       </c>
       <c r="R73" t="n">
-        <v>6829189</v>
+        <v>6828932</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755489</v>
+        <v>125755412</v>
       </c>
       <c r="B74" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7710,21 +7710,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7734,10 +7734,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483001</v>
+        <v>482912</v>
       </c>
       <c r="R74" t="n">
-        <v>6828740</v>
+        <v>6828922</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7796,10 +7796,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755441</v>
+        <v>125755424</v>
       </c>
       <c r="B75" t="n">
-        <v>78731</v>
+        <v>79004</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,21 +7807,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483114</v>
+        <v>483162</v>
       </c>
       <c r="R75" t="n">
-        <v>6828865</v>
+        <v>6828879</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7893,10 +7893,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755451</v>
+        <v>125755472</v>
       </c>
       <c r="B76" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7904,21 +7904,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483278</v>
+        <v>483203</v>
       </c>
       <c r="R76" t="n">
-        <v>6828932</v>
+        <v>6829189</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7990,10 +7990,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755412</v>
+        <v>125755489</v>
       </c>
       <c r="B77" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8001,21 +8001,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>482912</v>
+        <v>483001</v>
       </c>
       <c r="R77" t="n">
-        <v>6828922</v>
+        <v>6828740</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8771,10 +8771,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755414</v>
+        <v>125747880</v>
       </c>
       <c r="B85" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8782,34 +8782,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483240</v>
+        <v>483012</v>
       </c>
       <c r="R85" t="n">
-        <v>6828921</v>
+        <v>6828723</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8856,22 +8856,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755418</v>
+        <v>125755414</v>
       </c>
       <c r="B86" t="n">
-        <v>79004</v>
+        <v>79590</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8879,21 +8879,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>482886</v>
+        <v>483240</v>
       </c>
       <c r="R86" t="n">
-        <v>6828895</v>
+        <v>6828921</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8965,10 +8965,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755511</v>
+        <v>125755418</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8976,21 +8976,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483188</v>
+        <v>482886</v>
       </c>
       <c r="R87" t="n">
-        <v>6828936</v>
+        <v>6828895</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9062,7 +9062,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755504</v>
+        <v>125755511</v>
       </c>
       <c r="B88" t="n">
         <v>78972</v>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483117</v>
+        <v>483188</v>
       </c>
       <c r="R88" t="n">
-        <v>6828857</v>
+        <v>6828936</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,7 +9159,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755484</v>
+        <v>125755504</v>
       </c>
       <c r="B89" t="n">
         <v>78972</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>482976</v>
+        <v>483117</v>
       </c>
       <c r="R89" t="n">
-        <v>6828720</v>
+        <v>6828857</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9256,7 +9256,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755479</v>
+        <v>125755484</v>
       </c>
       <c r="B90" t="n">
         <v>78972</v>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482918</v>
+        <v>482976</v>
       </c>
       <c r="R90" t="n">
-        <v>6828932</v>
+        <v>6828720</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755512</v>
+        <v>125755479</v>
       </c>
       <c r="B91" t="n">
         <v>78972</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483190</v>
+        <v>482918</v>
       </c>
       <c r="R91" t="n">
-        <v>6828942</v>
+        <v>6828932</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125747880</v>
+        <v>125755512</v>
       </c>
       <c r="B92" t="n">
         <v>78972</v>
@@ -9481,14 +9481,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483012</v>
+        <v>483190</v>
       </c>
       <c r="R92" t="n">
-        <v>6828723</v>
+        <v>6828942</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9535,22 +9535,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755526</v>
+        <v>125755435</v>
       </c>
       <c r="B93" t="n">
-        <v>78639</v>
+        <v>58130</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9558,21 +9558,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>103018</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483499</v>
+        <v>483450</v>
       </c>
       <c r="R93" t="n">
-        <v>6829120</v>
+        <v>6829302</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755435</v>
+        <v>125755526</v>
       </c>
       <c r="B94" t="n">
-        <v>58130</v>
+        <v>78639</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9655,21 +9655,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103018</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483450</v>
+        <v>483499</v>
       </c>
       <c r="R94" t="n">
-        <v>6829302</v>
+        <v>6829120</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755413</v>
+        <v>125755469</v>
       </c>
       <c r="B95" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9752,21 +9752,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>482962</v>
+        <v>483342</v>
       </c>
       <c r="R95" t="n">
-        <v>6828771</v>
+        <v>6829286</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755444</v>
+        <v>125755493</v>
       </c>
       <c r="B96" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9849,21 +9849,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483272</v>
+        <v>483037</v>
       </c>
       <c r="R96" t="n">
-        <v>6829286</v>
+        <v>6828788</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9935,10 +9935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755446</v>
+        <v>125755413</v>
       </c>
       <c r="B97" t="n">
-        <v>80075</v>
+        <v>79590</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>482885</v>
+        <v>482962</v>
       </c>
       <c r="R97" t="n">
-        <v>6828845</v>
+        <v>6828771</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755469</v>
+        <v>125755444</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483342</v>
+        <v>483272</v>
       </c>
       <c r="R98" t="n">
         <v>6829286</v>
@@ -10129,10 +10129,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755493</v>
+        <v>125755446</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10140,21 +10140,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483037</v>
+        <v>482885</v>
       </c>
       <c r="R99" t="n">
-        <v>6828788</v>
+        <v>6828845</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11686,50 +11686,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755457</v>
+        <v>125755436</v>
       </c>
       <c r="B115" t="n">
-        <v>56834</v>
+        <v>80104</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483040</v>
+        <v>483303</v>
       </c>
       <c r="R115" t="n">
-        <v>6828774</v>
+        <v>6829290</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11788,10 +11783,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755427</v>
+        <v>125755457</v>
       </c>
       <c r="B116" t="n">
-        <v>79561</v>
+        <v>56834</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11799,34 +11794,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>102612</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483472</v>
+        <v>483040</v>
       </c>
       <c r="R116" t="n">
-        <v>6829305</v>
+        <v>6828774</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11885,32 +11885,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755436</v>
+        <v>125755427</v>
       </c>
       <c r="B117" t="n">
-        <v>80104</v>
+        <v>79561</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11920,10 +11920,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483303</v>
+        <v>483472</v>
       </c>
       <c r="R117" t="n">
-        <v>6829290</v>
+        <v>6829305</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125755443</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125755429</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125755426</v>
       </c>
       <c r="B4" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125744833</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125755529</v>
       </c>
       <c r="B6" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125755447</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125755430</v>
       </c>
       <c r="B8" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125755409</v>
       </c>
       <c r="B9" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125755528</v>
       </c>
       <c r="B10" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125755448</v>
       </c>
       <c r="B11" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755439</v>
+        <v>125755452</v>
       </c>
       <c r="B12" t="n">
         <v>78731</v>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483586</v>
+        <v>483587</v>
       </c>
       <c r="R12" t="n">
         <v>6829364</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755438</v>
+        <v>125755439</v>
       </c>
       <c r="B13" t="n">
-        <v>78996</v>
+        <v>78732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483600</v>
+        <v>483586</v>
       </c>
       <c r="R13" t="n">
-        <v>6829152</v>
+        <v>6829364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755452</v>
+        <v>125755438</v>
       </c>
       <c r="B14" t="n">
-        <v>78730</v>
+        <v>78997</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483587</v>
+        <v>483600</v>
       </c>
       <c r="R14" t="n">
-        <v>6829364</v>
+        <v>6829152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
         <v>125755416</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>125755488</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>125755475</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>125746064</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>125746931</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755445</v>
+        <v>125755506</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482900</v>
+        <v>483162</v>
       </c>
       <c r="R20" t="n">
-        <v>6828861</v>
+        <v>6828887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755421</v>
+        <v>125755480</v>
       </c>
       <c r="B21" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483044</v>
+        <v>482885</v>
       </c>
       <c r="R21" t="n">
-        <v>6828792</v>
+        <v>6828897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755506</v>
+        <v>125755494</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483162</v>
+        <v>483047</v>
       </c>
       <c r="R22" t="n">
-        <v>6828887</v>
+        <v>6828790</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755480</v>
+        <v>125755421</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,21 +2738,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482885</v>
+        <v>483044</v>
       </c>
       <c r="R23" t="n">
-        <v>6828897</v>
+        <v>6828792</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755494</v>
+        <v>125755445</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483047</v>
+        <v>482900</v>
       </c>
       <c r="R24" t="n">
-        <v>6828790</v>
+        <v>6828861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,7 +2924,7 @@
         <v>125745798</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>125755440</v>
       </c>
       <c r="B26" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3115,27 +3115,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755530</v>
+        <v>125755513</v>
       </c>
       <c r="B27" t="n">
-        <v>80110</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R27" t="n">
-        <v>6829288</v>
+        <v>6828917</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3212,27 +3212,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755513</v>
+        <v>125755530</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R28" t="n">
-        <v>6828917</v>
+        <v>6829288</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3312,7 +3312,7 @@
         <v>125747349</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755428</v>
+        <v>125755516</v>
       </c>
       <c r="B30" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483280</v>
+        <v>483291</v>
       </c>
       <c r="R30" t="n">
-        <v>6828942</v>
+        <v>6828969</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755516</v>
+        <v>125755481</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483291</v>
+        <v>482929</v>
       </c>
       <c r="R31" t="n">
-        <v>6828969</v>
+        <v>6828797</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755481</v>
+        <v>125755428</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>79562</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>482929</v>
+        <v>483280</v>
       </c>
       <c r="R32" t="n">
-        <v>6828797</v>
+        <v>6828942</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3700,7 +3700,7 @@
         <v>125755502</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>125755473</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>125755460</v>
       </c>
       <c r="B35" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>125755478</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>125755411</v>
       </c>
       <c r="B37" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>125755417</v>
       </c>
       <c r="B38" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755501</v>
+        <v>125746848</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,14 +4310,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483071</v>
+        <v>483247</v>
       </c>
       <c r="R39" t="n">
-        <v>6828833</v>
+        <v>6828848</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4364,22 +4364,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755464</v>
+        <v>125755501</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483423</v>
+        <v>483071</v>
       </c>
       <c r="R40" t="n">
-        <v>6829325</v>
+        <v>6828833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755508</v>
+        <v>125755464</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483189</v>
+        <v>483423</v>
       </c>
       <c r="R41" t="n">
-        <v>6828911</v>
+        <v>6829325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755482</v>
+        <v>125755508</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>482960</v>
+        <v>483189</v>
       </c>
       <c r="R42" t="n">
-        <v>6828769</v>
+        <v>6828911</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125747099</v>
+        <v>125755482</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4698,14 +4698,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483090</v>
+        <v>482960</v>
       </c>
       <c r="R43" t="n">
-        <v>6828658</v>
+        <v>6828769</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4752,22 +4752,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125747249</v>
+        <v>125748935</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4775,21 +4775,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R44" t="n">
-        <v>6828658</v>
+        <v>6828797</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4835,11 +4835,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125748935</v>
+        <v>125747249</v>
       </c>
       <c r="B45" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R45" t="n">
-        <v>6828797</v>
+        <v>6828658</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4937,6 +4932,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125746416</v>
+        <v>125747099</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483247</v>
+        <v>483090</v>
       </c>
       <c r="R46" t="n">
-        <v>6828848</v>
+        <v>6828658</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755453</v>
+        <v>125755466</v>
       </c>
       <c r="B47" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>482979</v>
+        <v>483400</v>
       </c>
       <c r="R47" t="n">
-        <v>6829140</v>
+        <v>6829318</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5160,7 +5160,7 @@
         <v>125755456</v>
       </c>
       <c r="B48" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755536</v>
+        <v>125755510</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,39 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483037</v>
+        <v>483191</v>
       </c>
       <c r="R49" t="n">
-        <v>6828775</v>
+        <v>6828929</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5330,11 +5325,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5361,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755466</v>
+        <v>125755453</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5372,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5396,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483400</v>
+        <v>482979</v>
       </c>
       <c r="R50" t="n">
-        <v>6829318</v>
+        <v>6829140</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5458,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755510</v>
+        <v>125755500</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5493,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483191</v>
+        <v>483068</v>
       </c>
       <c r="R51" t="n">
-        <v>6828929</v>
+        <v>6828819</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5555,10 +5545,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755500</v>
+        <v>125755536</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,34 +5556,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483068</v>
+        <v>483037</v>
       </c>
       <c r="R52" t="n">
-        <v>6828819</v>
+        <v>6828775</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5626,6 +5621,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5652,45 +5652,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755458</v>
+        <v>125746158</v>
       </c>
       <c r="B53" t="n">
-        <v>58326</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483319</v>
+        <v>483342</v>
       </c>
       <c r="R53" t="n">
-        <v>6829293</v>
+        <v>6828971</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5737,22 +5737,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125746158</v>
+        <v>125755483</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5780,14 +5780,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483342</v>
+        <v>482971</v>
       </c>
       <c r="R54" t="n">
-        <v>6828971</v>
+        <v>6828738</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5834,22 +5834,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755483</v>
+        <v>125755437</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>80077</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>482971</v>
+        <v>483307</v>
       </c>
       <c r="R55" t="n">
-        <v>6828738</v>
+        <v>6829287</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755437</v>
+        <v>125755491</v>
       </c>
       <c r="B56" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5954,21 +5954,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483307</v>
+        <v>483015</v>
       </c>
       <c r="R56" t="n">
-        <v>6829287</v>
+        <v>6828753</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6040,32 +6040,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755491</v>
+        <v>125755458</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>58327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483015</v>
+        <v>483319</v>
       </c>
       <c r="R57" t="n">
-        <v>6828753</v>
+        <v>6829293</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6140,7 +6140,7 @@
         <v>125755442</v>
       </c>
       <c r="B58" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6234,45 +6234,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755492</v>
+        <v>125755432</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>56844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483032</v>
+        <v>483446</v>
       </c>
       <c r="R59" t="n">
-        <v>6828773</v>
+        <v>6829026</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,10 +6336,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755498</v>
+        <v>125755492</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6366,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R60" t="n">
-        <v>6828809</v>
+        <v>6828773</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,10 +6433,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755468</v>
+        <v>125755498</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6463,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483391</v>
+        <v>483071</v>
       </c>
       <c r="R61" t="n">
-        <v>6829308</v>
+        <v>6828809</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6525,50 +6530,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755432</v>
+        <v>125755468</v>
       </c>
       <c r="B62" t="n">
-        <v>56843</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483446</v>
+        <v>483391</v>
       </c>
       <c r="R62" t="n">
-        <v>6829026</v>
+        <v>6829308</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755419</v>
+        <v>125755463</v>
       </c>
       <c r="B63" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483005</v>
+        <v>483450</v>
       </c>
       <c r="R63" t="n">
-        <v>6828754</v>
+        <v>6829306</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
         <v>125755496</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>125755459</v>
       </c>
       <c r="B65" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755463</v>
+        <v>125755419</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6929,21 +6929,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483450</v>
+        <v>483005</v>
       </c>
       <c r="R66" t="n">
-        <v>6829306</v>
+        <v>6828754</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7018,7 +7018,7 @@
         <v>125755533</v>
       </c>
       <c r="B67" t="n">
-        <v>78378</v>
+        <v>78379</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>125755517</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>125755525</v>
       </c>
       <c r="B69" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>125755431</v>
       </c>
       <c r="B70" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>125755433</v>
       </c>
       <c r="B71" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755441</v>
+        <v>125755472</v>
       </c>
       <c r="B72" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,21 +7516,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483114</v>
+        <v>483203</v>
       </c>
       <c r="R72" t="n">
-        <v>6828865</v>
+        <v>6829189</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755451</v>
+        <v>125755489</v>
       </c>
       <c r="B73" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7613,21 +7613,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483278</v>
+        <v>483001</v>
       </c>
       <c r="R73" t="n">
-        <v>6828932</v>
+        <v>6828740</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755412</v>
+        <v>125755451</v>
       </c>
       <c r="B74" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7710,21 +7710,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7734,10 +7734,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>482912</v>
+        <v>483278</v>
       </c>
       <c r="R74" t="n">
-        <v>6828922</v>
+        <v>6828932</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7799,7 +7799,7 @@
         <v>125755424</v>
       </c>
       <c r="B75" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7893,10 +7893,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755472</v>
+        <v>125755412</v>
       </c>
       <c r="B76" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7904,21 +7904,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483203</v>
+        <v>482912</v>
       </c>
       <c r="R76" t="n">
-        <v>6829189</v>
+        <v>6828922</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7990,10 +7990,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755489</v>
+        <v>125748016</v>
       </c>
       <c r="B77" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8001,34 +8001,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483001</v>
+        <v>483071</v>
       </c>
       <c r="R77" t="n">
-        <v>6828740</v>
+        <v>6828797</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8075,22 +8080,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125748016</v>
+        <v>125755441</v>
       </c>
       <c r="B78" t="n">
-        <v>57651</v>
+        <v>78732</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8098,39 +8103,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483071</v>
+        <v>483114</v>
       </c>
       <c r="R78" t="n">
-        <v>6828797</v>
+        <v>6828865</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8177,22 +8177,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755522</v>
+        <v>125755515</v>
       </c>
       <c r="B79" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8200,21 +8200,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483303</v>
+        <v>483280</v>
       </c>
       <c r="R79" t="n">
-        <v>6829017</v>
+        <v>6828952</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,10 +8286,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755515</v>
+        <v>125755514</v>
       </c>
       <c r="B80" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483280</v>
+        <v>483220</v>
       </c>
       <c r="R80" t="n">
-        <v>6828952</v>
+        <v>6828907</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755514</v>
+        <v>125755518</v>
       </c>
       <c r="B81" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483220</v>
+        <v>483467</v>
       </c>
       <c r="R81" t="n">
-        <v>6828907</v>
+        <v>6829027</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8480,10 +8480,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755518</v>
+        <v>125755503</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483467</v>
+        <v>483095</v>
       </c>
       <c r="R82" t="n">
-        <v>6829027</v>
+        <v>6828845</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,10 +8577,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755503</v>
+        <v>125755474</v>
       </c>
       <c r="B83" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483095</v>
+        <v>483188</v>
       </c>
       <c r="R83" t="n">
-        <v>6828845</v>
+        <v>6829143</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8674,10 +8674,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755474</v>
+        <v>125755522</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8685,21 +8685,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483188</v>
+        <v>483303</v>
       </c>
       <c r="R84" t="n">
-        <v>6829143</v>
+        <v>6829017</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8771,10 +8771,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125747880</v>
+        <v>125755418</v>
       </c>
       <c r="B85" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8782,34 +8782,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483012</v>
+        <v>482886</v>
       </c>
       <c r="R85" t="n">
-        <v>6828723</v>
+        <v>6828895</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8856,12 +8856,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -8871,7 +8871,7 @@
         <v>125755414</v>
       </c>
       <c r="B86" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8965,10 +8965,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755418</v>
+        <v>125747880</v>
       </c>
       <c r="B87" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8976,34 +8976,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>482886</v>
+        <v>483012</v>
       </c>
       <c r="R87" t="n">
-        <v>6828895</v>
+        <v>6828723</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9050,12 +9050,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9065,7 +9065,7 @@
         <v>125755511</v>
       </c>
       <c r="B88" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>125755504</v>
       </c>
       <c r="B89" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>125755484</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>125755479</v>
       </c>
       <c r="B91" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>125755512</v>
       </c>
       <c r="B92" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755435</v>
+        <v>125755493</v>
       </c>
       <c r="B93" t="n">
-        <v>58130</v>
+        <v>78973</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9558,21 +9558,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483450</v>
+        <v>483037</v>
       </c>
       <c r="R93" t="n">
-        <v>6829302</v>
+        <v>6828788</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,32 +9644,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755526</v>
+        <v>125755520</v>
       </c>
       <c r="B94" t="n">
-        <v>78639</v>
+        <v>92524</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483499</v>
+        <v>483458</v>
       </c>
       <c r="R94" t="n">
-        <v>6829120</v>
+        <v>6829089</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9744,7 +9744,7 @@
         <v>125755469</v>
       </c>
       <c r="B95" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755493</v>
+        <v>125755526</v>
       </c>
       <c r="B96" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9849,21 +9849,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483037</v>
+        <v>483499</v>
       </c>
       <c r="R96" t="n">
-        <v>6828788</v>
+        <v>6829120</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9938,7 +9938,7 @@
         <v>125755413</v>
       </c>
       <c r="B97" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>125755444</v>
       </c>
       <c r="B98" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>125755446</v>
       </c>
       <c r="B99" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10226,32 +10226,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755520</v>
+        <v>125755435</v>
       </c>
       <c r="B100" t="n">
-        <v>92522</v>
+        <v>58131</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>103018</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483458</v>
+        <v>483450</v>
       </c>
       <c r="R100" t="n">
-        <v>6829089</v>
+        <v>6829302</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755415</v>
+        <v>125755507</v>
       </c>
       <c r="B101" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483456</v>
+        <v>483178</v>
       </c>
       <c r="R101" t="n">
-        <v>6829062</v>
+        <v>6828902</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10423,7 +10423,7 @@
         <v>125755422</v>
       </c>
       <c r="B102" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755507</v>
+        <v>125755415</v>
       </c>
       <c r="B103" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483178</v>
+        <v>483456</v>
       </c>
       <c r="R103" t="n">
-        <v>6828902</v>
+        <v>6829062</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10614,10 +10614,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125746359</v>
+        <v>125755497</v>
       </c>
       <c r="B104" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10645,14 +10645,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483265</v>
+        <v>483063</v>
       </c>
       <c r="R104" t="n">
-        <v>6828852</v>
+        <v>6828803</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10699,22 +10699,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755497</v>
+        <v>125755490</v>
       </c>
       <c r="B105" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483063</v>
+        <v>483007</v>
       </c>
       <c r="R105" t="n">
-        <v>6828803</v>
+        <v>6828754</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755490</v>
+        <v>125755485</v>
       </c>
       <c r="B106" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483007</v>
+        <v>483002</v>
       </c>
       <c r="R106" t="n">
-        <v>6828754</v>
+        <v>6828695</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10905,10 +10905,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755485</v>
+        <v>125746359</v>
       </c>
       <c r="B107" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10936,14 +10936,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483002</v>
+        <v>483265</v>
       </c>
       <c r="R107" t="n">
-        <v>6828695</v>
+        <v>6828852</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10990,12 +10990,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11005,7 +11005,7 @@
         <v>125755455</v>
       </c>
       <c r="B108" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11099,32 +11099,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755532</v>
+        <v>125755523</v>
       </c>
       <c r="B109" t="n">
-        <v>80110</v>
+        <v>78640</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483294</v>
+        <v>483313</v>
       </c>
       <c r="R109" t="n">
-        <v>6829294</v>
+        <v>6829017</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11196,32 +11196,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755523</v>
+        <v>125755532</v>
       </c>
       <c r="B110" t="n">
-        <v>78639</v>
+        <v>80111</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483313</v>
+        <v>483294</v>
       </c>
       <c r="R110" t="n">
-        <v>6829017</v>
+        <v>6829294</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11293,10 +11293,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125746396</v>
+        <v>125747874</v>
       </c>
       <c r="B111" t="n">
-        <v>78731</v>
+        <v>57652</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11304,34 +11304,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483265</v>
+        <v>483012</v>
       </c>
       <c r="R111" t="n">
-        <v>6828852</v>
+        <v>6828723</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11390,10 +11395,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125747874</v>
+        <v>125746396</v>
       </c>
       <c r="B112" t="n">
-        <v>57651</v>
+        <v>78732</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11401,39 +11406,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483012</v>
+        <v>483265</v>
       </c>
       <c r="R112" t="n">
-        <v>6828723</v>
+        <v>6828852</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11495,7 +11495,7 @@
         <v>125755486</v>
       </c>
       <c r="B113" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11589,32 +11589,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755471</v>
+        <v>125755436</v>
       </c>
       <c r="B114" t="n">
-        <v>78972</v>
+        <v>80105</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R114" t="n">
-        <v>6829193</v>
+        <v>6829290</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11686,45 +11686,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755436</v>
+        <v>125755457</v>
       </c>
       <c r="B115" t="n">
-        <v>80104</v>
+        <v>56835</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483303</v>
+        <v>483040</v>
       </c>
       <c r="R115" t="n">
-        <v>6829290</v>
+        <v>6828774</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11783,10 +11788,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755457</v>
+        <v>125755471</v>
       </c>
       <c r="B116" t="n">
-        <v>56834</v>
+        <v>78973</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11794,39 +11799,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483040</v>
+        <v>483206</v>
       </c>
       <c r="R116" t="n">
-        <v>6828774</v>
+        <v>6829193</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11888,7 +11888,7 @@
         <v>125755427</v>
       </c>
       <c r="B117" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>125755462</v>
       </c>
       <c r="B118" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>125691576</v>
       </c>
       <c r="B119" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755452</v>
+        <v>125755439</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483587</v>
+        <v>483586</v>
       </c>
       <c r="R12" t="n">
         <v>6829364</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755439</v>
+        <v>125755452</v>
       </c>
       <c r="B13" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483586</v>
+        <v>483587</v>
       </c>
       <c r="R13" t="n">
         <v>6829364</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125746848</v>
+        <v>125755501</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4310,14 +4310,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483247</v>
+        <v>483071</v>
       </c>
       <c r="R39" t="n">
-        <v>6828848</v>
+        <v>6828833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4364,19 +4364,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755501</v>
+        <v>125755464</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483071</v>
+        <v>483423</v>
       </c>
       <c r="R40" t="n">
-        <v>6828833</v>
+        <v>6829325</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755464</v>
+        <v>125755508</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483423</v>
+        <v>483189</v>
       </c>
       <c r="R41" t="n">
-        <v>6829325</v>
+        <v>6828911</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755508</v>
+        <v>125755482</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483189</v>
+        <v>482960</v>
       </c>
       <c r="R42" t="n">
-        <v>6828911</v>
+        <v>6828769</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755482</v>
+        <v>125748935</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,34 +4678,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>482960</v>
+        <v>483071</v>
       </c>
       <c r="R43" t="n">
-        <v>6828769</v>
+        <v>6828797</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4752,22 +4752,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125748935</v>
+        <v>125746848</v>
       </c>
       <c r="B44" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4775,21 +4775,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483071</v>
+        <v>483247</v>
       </c>
       <c r="R44" t="n">
-        <v>6828797</v>
+        <v>6828848</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755463</v>
+        <v>125755496</v>
       </c>
       <c r="B63" t="n">
         <v>78973</v>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483450</v>
+        <v>483054</v>
       </c>
       <c r="R63" t="n">
-        <v>6829306</v>
+        <v>6828788</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755496</v>
+        <v>125755459</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>91248</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6735,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483054</v>
+        <v>483398</v>
       </c>
       <c r="R64" t="n">
-        <v>6828788</v>
+        <v>6829316</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755459</v>
+        <v>125755463</v>
       </c>
       <c r="B65" t="n">
-        <v>91248</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483398</v>
+        <v>483450</v>
       </c>
       <c r="R65" t="n">
-        <v>6829316</v>
+        <v>6829306</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8771,10 +8771,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755418</v>
+        <v>125755511</v>
       </c>
       <c r="B85" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8782,21 +8782,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>482886</v>
+        <v>483188</v>
       </c>
       <c r="R85" t="n">
-        <v>6828895</v>
+        <v>6828936</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8868,10 +8868,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755414</v>
+        <v>125755504</v>
       </c>
       <c r="B86" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8879,21 +8879,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483240</v>
+        <v>483117</v>
       </c>
       <c r="R86" t="n">
-        <v>6828921</v>
+        <v>6828857</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125747880</v>
+        <v>125755484</v>
       </c>
       <c r="B87" t="n">
         <v>78973</v>
@@ -8996,14 +8996,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483012</v>
+        <v>482976</v>
       </c>
       <c r="R87" t="n">
-        <v>6828723</v>
+        <v>6828720</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9050,19 +9050,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755511</v>
+        <v>125755479</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483188</v>
+        <v>482918</v>
       </c>
       <c r="R88" t="n">
-        <v>6828936</v>
+        <v>6828932</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,7 +9159,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755504</v>
+        <v>125755512</v>
       </c>
       <c r="B89" t="n">
         <v>78973</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483117</v>
+        <v>483190</v>
       </c>
       <c r="R89" t="n">
-        <v>6828857</v>
+        <v>6828942</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755484</v>
+        <v>125755418</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9267,21 +9267,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482976</v>
+        <v>482886</v>
       </c>
       <c r="R90" t="n">
-        <v>6828720</v>
+        <v>6828895</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755479</v>
+        <v>125755414</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>482918</v>
+        <v>483240</v>
       </c>
       <c r="R91" t="n">
-        <v>6828932</v>
+        <v>6828921</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755512</v>
+        <v>125747880</v>
       </c>
       <c r="B92" t="n">
         <v>78973</v>
@@ -9481,14 +9481,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483190</v>
+        <v>483012</v>
       </c>
       <c r="R92" t="n">
-        <v>6828942</v>
+        <v>6828723</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9535,12 +9535,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755497</v>
+        <v>125746359</v>
       </c>
       <c r="B104" t="n">
         <v>78973</v>
@@ -10645,14 +10645,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483063</v>
+        <v>483265</v>
       </c>
       <c r="R104" t="n">
-        <v>6828803</v>
+        <v>6828852</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10699,19 +10699,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755490</v>
+        <v>125755497</v>
       </c>
       <c r="B105" t="n">
         <v>78973</v>
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483007</v>
+        <v>483063</v>
       </c>
       <c r="R105" t="n">
-        <v>6828754</v>
+        <v>6828803</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10808,7 +10808,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755485</v>
+        <v>125755490</v>
       </c>
       <c r="B106" t="n">
         <v>78973</v>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483002</v>
+        <v>483007</v>
       </c>
       <c r="R106" t="n">
-        <v>6828695</v>
+        <v>6828754</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125746359</v>
+        <v>125755485</v>
       </c>
       <c r="B107" t="n">
         <v>78973</v>
@@ -10936,14 +10936,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483265</v>
+        <v>483002</v>
       </c>
       <c r="R107" t="n">
-        <v>6828852</v>
+        <v>6828695</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10990,22 +10990,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755455</v>
+        <v>125755523</v>
       </c>
       <c r="B108" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,21 +11013,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11037,10 +11037,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>482942</v>
+        <v>483313</v>
       </c>
       <c r="R108" t="n">
-        <v>6828979</v>
+        <v>6829017</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11099,32 +11099,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755523</v>
+        <v>125755532</v>
       </c>
       <c r="B109" t="n">
-        <v>78640</v>
+        <v>80111</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483313</v>
+        <v>483294</v>
       </c>
       <c r="R109" t="n">
-        <v>6829017</v>
+        <v>6829294</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11196,45 +11196,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755532</v>
+        <v>125747874</v>
       </c>
       <c r="B110" t="n">
-        <v>80111</v>
+        <v>57652</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483294</v>
+        <v>483012</v>
       </c>
       <c r="R110" t="n">
-        <v>6829294</v>
+        <v>6828723</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11281,22 +11286,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125747874</v>
+        <v>125755455</v>
       </c>
       <c r="B111" t="n">
-        <v>57652</v>
+        <v>78731</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11304,39 +11309,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483012</v>
+        <v>482942</v>
       </c>
       <c r="R111" t="n">
-        <v>6828723</v>
+        <v>6828979</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11383,12 +11383,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125755426</v>
       </c>
       <c r="B4" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125755430</v>
       </c>
       <c r="B8" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755409</v>
+        <v>125755528</v>
       </c>
       <c r="B9" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483587</v>
+        <v>483525</v>
       </c>
       <c r="R9" t="n">
-        <v>6829364</v>
+        <v>6829111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755528</v>
+        <v>125755409</v>
       </c>
       <c r="B10" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483525</v>
+        <v>483587</v>
       </c>
       <c r="R10" t="n">
-        <v>6829111</v>
+        <v>6829364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755439</v>
+        <v>125755452</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483586</v>
+        <v>483587</v>
       </c>
       <c r="R12" t="n">
         <v>6829364</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755452</v>
+        <v>125755438</v>
       </c>
       <c r="B13" t="n">
-        <v>78731</v>
+        <v>78997</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483587</v>
+        <v>483600</v>
       </c>
       <c r="R13" t="n">
-        <v>6829364</v>
+        <v>6829152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755438</v>
+        <v>125755439</v>
       </c>
       <c r="B14" t="n">
-        <v>78997</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483600</v>
+        <v>483586</v>
       </c>
       <c r="R14" t="n">
-        <v>6829152</v>
+        <v>6829364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755416</v>
+        <v>125746064</v>
       </c>
       <c r="B15" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,34 +1957,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483454</v>
+        <v>483474</v>
       </c>
       <c r="R15" t="n">
-        <v>6829082</v>
+        <v>6829119</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,19 +2031,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755488</v>
+        <v>125746931</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2074,14 +2074,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483019</v>
+        <v>483156</v>
       </c>
       <c r="R16" t="n">
-        <v>6828737</v>
+        <v>6828728</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,6 +2116,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2128,22 +2133,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755475</v>
+        <v>125755416</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483169</v>
+        <v>483454</v>
       </c>
       <c r="R17" t="n">
-        <v>6829132</v>
+        <v>6829082</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125746064</v>
+        <v>125755488</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2268,14 +2273,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483474</v>
+        <v>483019</v>
       </c>
       <c r="R18" t="n">
-        <v>6829119</v>
+        <v>6828737</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2322,19 +2327,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125746931</v>
+        <v>125755475</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2365,14 +2370,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483156</v>
+        <v>483169</v>
       </c>
       <c r="R19" t="n">
-        <v>6828728</v>
+        <v>6829132</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2407,11 +2412,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2424,22 +2424,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755506</v>
+        <v>125745798</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483162</v>
+        <v>483474</v>
       </c>
       <c r="R20" t="n">
-        <v>6828887</v>
+        <v>6829119</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,22 +2521,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755480</v>
+        <v>125755440</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482885</v>
+        <v>482960</v>
       </c>
       <c r="R21" t="n">
-        <v>6828897</v>
+        <v>6828991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755494</v>
+        <v>125755506</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483047</v>
+        <v>483162</v>
       </c>
       <c r="R22" t="n">
-        <v>6828790</v>
+        <v>6828887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755421</v>
+        <v>125755494</v>
       </c>
       <c r="B23" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,21 +2738,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483044</v>
+        <v>483047</v>
       </c>
       <c r="R23" t="n">
-        <v>6828792</v>
+        <v>6828790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755445</v>
+        <v>125755421</v>
       </c>
       <c r="B24" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482900</v>
+        <v>483044</v>
       </c>
       <c r="R24" t="n">
-        <v>6828861</v>
+        <v>6828792</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125745798</v>
+        <v>125755480</v>
       </c>
       <c r="B25" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483474</v>
+        <v>482885</v>
       </c>
       <c r="R25" t="n">
-        <v>6829119</v>
+        <v>6828897</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,22 +3006,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755440</v>
+        <v>125755445</v>
       </c>
       <c r="B26" t="n">
-        <v>78732</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482960</v>
+        <v>482900</v>
       </c>
       <c r="R26" t="n">
-        <v>6828991</v>
+        <v>6828861</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755513</v>
+        <v>125747349</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3146,14 +3146,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483206</v>
+        <v>482981</v>
       </c>
       <c r="R27" t="n">
-        <v>6828917</v>
+        <v>6828687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3200,12 +3200,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125747349</v>
+        <v>125755513</v>
       </c>
       <c r="B29" t="n">
         <v>78973</v>
@@ -3340,14 +3340,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482981</v>
+        <v>483206</v>
       </c>
       <c r="R29" t="n">
-        <v>6828687</v>
+        <v>6828917</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3394,12 +3394,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755502</v>
+        <v>125755460</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>91397</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483078</v>
+        <v>482913</v>
       </c>
       <c r="R33" t="n">
-        <v>6828839</v>
+        <v>6829095</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755473</v>
+        <v>125755478</v>
       </c>
       <c r="B34" t="n">
         <v>78973</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483182</v>
+        <v>483147</v>
       </c>
       <c r="R34" t="n">
-        <v>6829175</v>
+        <v>6829095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,32 +3891,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755460</v>
+        <v>125755502</v>
       </c>
       <c r="B35" t="n">
-        <v>91395</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>482913</v>
+        <v>483078</v>
       </c>
       <c r="R35" t="n">
-        <v>6829095</v>
+        <v>6828839</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755478</v>
+        <v>125755473</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483147</v>
+        <v>483182</v>
       </c>
       <c r="R36" t="n">
-        <v>6829095</v>
+        <v>6829175</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755501</v>
+        <v>125746848</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4310,14 +4310,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483071</v>
+        <v>483247</v>
       </c>
       <c r="R39" t="n">
-        <v>6828833</v>
+        <v>6828848</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4364,19 +4364,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755464</v>
+        <v>125747249</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4407,14 +4407,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483423</v>
+        <v>483032</v>
       </c>
       <c r="R40" t="n">
-        <v>6829325</v>
+        <v>6828658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4449,6 +4449,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4461,19 +4466,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755508</v>
+        <v>125747099</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4504,14 +4509,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483189</v>
+        <v>483090</v>
       </c>
       <c r="R41" t="n">
-        <v>6828911</v>
+        <v>6828658</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4558,22 +4563,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755482</v>
+        <v>125748935</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4586,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>482960</v>
+        <v>483071</v>
       </c>
       <c r="R42" t="n">
-        <v>6828769</v>
+        <v>6828797</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4655,22 +4660,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125748935</v>
+        <v>125755501</v>
       </c>
       <c r="B43" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,34 +4683,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
         <v>483071</v>
       </c>
       <c r="R43" t="n">
-        <v>6828797</v>
+        <v>6828833</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4752,19 +4757,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125746848</v>
+        <v>125755464</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4795,14 +4800,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483247</v>
+        <v>483423</v>
       </c>
       <c r="R44" t="n">
-        <v>6828848</v>
+        <v>6829325</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4849,19 +4854,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125747249</v>
+        <v>125755508</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4892,14 +4897,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483032</v>
+        <v>483189</v>
       </c>
       <c r="R45" t="n">
-        <v>6828658</v>
+        <v>6828911</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4934,11 +4939,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -4951,19 +4951,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125747099</v>
+        <v>125755482</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -4994,14 +4994,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483090</v>
+        <v>482960</v>
       </c>
       <c r="R46" t="n">
-        <v>6828658</v>
+        <v>6828769</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755483</v>
+        <v>125755437</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>482971</v>
+        <v>483307</v>
       </c>
       <c r="R54" t="n">
-        <v>6828738</v>
+        <v>6829287</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755437</v>
+        <v>125755483</v>
       </c>
       <c r="B55" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483307</v>
+        <v>482971</v>
       </c>
       <c r="R55" t="n">
-        <v>6829287</v>
+        <v>6828738</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6234,50 +6234,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755432</v>
+        <v>125755492</v>
       </c>
       <c r="B59" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483446</v>
+        <v>483032</v>
       </c>
       <c r="R59" t="n">
-        <v>6829026</v>
+        <v>6828773</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,7 +6331,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755492</v>
+        <v>125755468</v>
       </c>
       <c r="B60" t="n">
         <v>78973</v>
@@ -6371,10 +6366,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483032</v>
+        <v>483391</v>
       </c>
       <c r="R60" t="n">
-        <v>6828773</v>
+        <v>6829308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,45 +6428,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755498</v>
+        <v>125755432</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483071</v>
+        <v>483446</v>
       </c>
       <c r="R61" t="n">
-        <v>6828809</v>
+        <v>6829026</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755468</v>
+        <v>125755498</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483391</v>
+        <v>483071</v>
       </c>
       <c r="R62" t="n">
-        <v>6829308</v>
+        <v>6828809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755496</v>
+        <v>125755459</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>91250</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483054</v>
+        <v>483398</v>
       </c>
       <c r="R63" t="n">
-        <v>6828788</v>
+        <v>6829316</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755459</v>
+        <v>125755419</v>
       </c>
       <c r="B64" t="n">
-        <v>91248</v>
+        <v>79005</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6735,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483398</v>
+        <v>483005</v>
       </c>
       <c r="R64" t="n">
-        <v>6829316</v>
+        <v>6828754</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755463</v>
+        <v>125755496</v>
       </c>
       <c r="B65" t="n">
         <v>78973</v>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483450</v>
+        <v>483054</v>
       </c>
       <c r="R65" t="n">
-        <v>6829306</v>
+        <v>6828788</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755419</v>
+        <v>125755463</v>
       </c>
       <c r="B66" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6929,21 +6929,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483005</v>
+        <v>483450</v>
       </c>
       <c r="R66" t="n">
-        <v>6828754</v>
+        <v>6829306</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755533</v>
+        <v>125755525</v>
       </c>
       <c r="B67" t="n">
-        <v>78379</v>
+        <v>78640</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483472</v>
+        <v>483442</v>
       </c>
       <c r="R67" t="n">
-        <v>6829305</v>
+        <v>6829028</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755517</v>
+        <v>125755533</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>78379</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483386</v>
+        <v>483472</v>
       </c>
       <c r="R68" t="n">
-        <v>6829003</v>
+        <v>6829305</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755525</v>
+        <v>125755517</v>
       </c>
       <c r="B69" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483442</v>
+        <v>483386</v>
       </c>
       <c r="R69" t="n">
-        <v>6829028</v>
+        <v>6829003</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755472</v>
+        <v>125755441</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,21 +7516,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483203</v>
+        <v>483114</v>
       </c>
       <c r="R72" t="n">
-        <v>6829189</v>
+        <v>6828865</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755489</v>
+        <v>125748016</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7613,34 +7613,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483001</v>
+        <v>483071</v>
       </c>
       <c r="R73" t="n">
-        <v>6828740</v>
+        <v>6828797</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7687,22 +7692,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755451</v>
+        <v>125755424</v>
       </c>
       <c r="B74" t="n">
-        <v>78731</v>
+        <v>79005</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7710,21 +7715,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7734,10 +7739,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483278</v>
+        <v>483162</v>
       </c>
       <c r="R74" t="n">
-        <v>6828932</v>
+        <v>6828879</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7796,10 +7801,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755424</v>
+        <v>125755412</v>
       </c>
       <c r="B75" t="n">
-        <v>79005</v>
+        <v>79591</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,21 +7812,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7831,10 +7836,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483162</v>
+        <v>482912</v>
       </c>
       <c r="R75" t="n">
-        <v>6828879</v>
+        <v>6828922</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7893,10 +7898,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755412</v>
+        <v>125755472</v>
       </c>
       <c r="B76" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7904,21 +7909,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7928,10 +7933,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>482912</v>
+        <v>483203</v>
       </c>
       <c r="R76" t="n">
-        <v>6828922</v>
+        <v>6829189</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7990,10 +7995,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125748016</v>
+        <v>125755489</v>
       </c>
       <c r="B77" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8001,39 +8006,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483071</v>
+        <v>483001</v>
       </c>
       <c r="R77" t="n">
-        <v>6828797</v>
+        <v>6828740</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8080,22 +8080,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755441</v>
+        <v>125755451</v>
       </c>
       <c r="B78" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8103,21 +8103,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483114</v>
+        <v>483278</v>
       </c>
       <c r="R78" t="n">
-        <v>6828865</v>
+        <v>6828932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8189,7 +8189,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755515</v>
+        <v>125755474</v>
       </c>
       <c r="B79" t="n">
         <v>78973</v>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483280</v>
+        <v>483188</v>
       </c>
       <c r="R79" t="n">
-        <v>6828952</v>
+        <v>6829143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,7 +8286,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755514</v>
+        <v>125755515</v>
       </c>
       <c r="B80" t="n">
         <v>78973</v>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483220</v>
+        <v>483280</v>
       </c>
       <c r="R80" t="n">
-        <v>6828907</v>
+        <v>6828952</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755518</v>
+        <v>125755522</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8394,21 +8394,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483467</v>
+        <v>483303</v>
       </c>
       <c r="R81" t="n">
-        <v>6829027</v>
+        <v>6829017</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755503</v>
+        <v>125755514</v>
       </c>
       <c r="B82" t="n">
         <v>78973</v>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483095</v>
+        <v>483220</v>
       </c>
       <c r="R82" t="n">
-        <v>6828845</v>
+        <v>6828907</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,7 +8577,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755474</v>
+        <v>125755518</v>
       </c>
       <c r="B83" t="n">
         <v>78973</v>
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483188</v>
+        <v>483467</v>
       </c>
       <c r="R83" t="n">
-        <v>6829143</v>
+        <v>6829027</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8674,10 +8674,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755522</v>
+        <v>125755503</v>
       </c>
       <c r="B84" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8685,21 +8685,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483303</v>
+        <v>483095</v>
       </c>
       <c r="R84" t="n">
-        <v>6829017</v>
+        <v>6828845</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8771,7 +8771,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755511</v>
+        <v>125755504</v>
       </c>
       <c r="B85" t="n">
         <v>78973</v>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483188</v>
+        <v>483117</v>
       </c>
       <c r="R85" t="n">
-        <v>6828936</v>
+        <v>6828857</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8868,10 +8868,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755504</v>
+        <v>125755418</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8879,21 +8879,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483117</v>
+        <v>482886</v>
       </c>
       <c r="R86" t="n">
-        <v>6828857</v>
+        <v>6828895</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755484</v>
+        <v>125755512</v>
       </c>
       <c r="B87" t="n">
         <v>78973</v>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>482976</v>
+        <v>483190</v>
       </c>
       <c r="R87" t="n">
-        <v>6828720</v>
+        <v>6828942</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9062,7 +9062,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755479</v>
+        <v>125755511</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482918</v>
+        <v>483188</v>
       </c>
       <c r="R88" t="n">
-        <v>6828932</v>
+        <v>6828936</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,7 +9159,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755512</v>
+        <v>125755484</v>
       </c>
       <c r="B89" t="n">
         <v>78973</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483190</v>
+        <v>482976</v>
       </c>
       <c r="R89" t="n">
-        <v>6828942</v>
+        <v>6828720</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755418</v>
+        <v>125755414</v>
       </c>
       <c r="B90" t="n">
-        <v>79005</v>
+        <v>79591</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9267,21 +9267,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482886</v>
+        <v>483240</v>
       </c>
       <c r="R90" t="n">
-        <v>6828895</v>
+        <v>6828921</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755414</v>
+        <v>125755479</v>
       </c>
       <c r="B91" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483240</v>
+        <v>482918</v>
       </c>
       <c r="R91" t="n">
-        <v>6828921</v>
+        <v>6828932</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755493</v>
+        <v>125755446</v>
       </c>
       <c r="B93" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9558,21 +9558,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483037</v>
+        <v>482885</v>
       </c>
       <c r="R93" t="n">
-        <v>6828788</v>
+        <v>6828845</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,32 +9644,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755520</v>
+        <v>125755413</v>
       </c>
       <c r="B94" t="n">
-        <v>92524</v>
+        <v>79591</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483458</v>
+        <v>482962</v>
       </c>
       <c r="R94" t="n">
-        <v>6829089</v>
+        <v>6828771</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755469</v>
+        <v>125755444</v>
       </c>
       <c r="B95" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9752,21 +9752,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483342</v>
+        <v>483272</v>
       </c>
       <c r="R95" t="n">
         <v>6829286</v>
@@ -9935,10 +9935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755413</v>
+        <v>125755469</v>
       </c>
       <c r="B97" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>482962</v>
+        <v>483342</v>
       </c>
       <c r="R97" t="n">
-        <v>6828771</v>
+        <v>6829286</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755444</v>
+        <v>125755493</v>
       </c>
       <c r="B98" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483272</v>
+        <v>483037</v>
       </c>
       <c r="R98" t="n">
-        <v>6829286</v>
+        <v>6828788</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,32 +10129,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755446</v>
+        <v>125755520</v>
       </c>
       <c r="B99" t="n">
-        <v>80076</v>
+        <v>92526</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>482885</v>
+        <v>483458</v>
       </c>
       <c r="R99" t="n">
-        <v>6828845</v>
+        <v>6829089</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755507</v>
+        <v>125755422</v>
       </c>
       <c r="B101" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483178</v>
+        <v>483099</v>
       </c>
       <c r="R101" t="n">
-        <v>6828902</v>
+        <v>6828854</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755422</v>
+        <v>125755415</v>
       </c>
       <c r="B102" t="n">
-        <v>79005</v>
+        <v>79591</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483099</v>
+        <v>483456</v>
       </c>
       <c r="R102" t="n">
-        <v>6828854</v>
+        <v>6829062</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755415</v>
+        <v>125755507</v>
       </c>
       <c r="B103" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483456</v>
+        <v>483178</v>
       </c>
       <c r="R103" t="n">
-        <v>6829062</v>
+        <v>6828902</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125746359</v>
+        <v>125755497</v>
       </c>
       <c r="B104" t="n">
         <v>78973</v>
@@ -10645,14 +10645,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483265</v>
+        <v>483063</v>
       </c>
       <c r="R104" t="n">
-        <v>6828852</v>
+        <v>6828803</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10699,19 +10699,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755497</v>
+        <v>125746359</v>
       </c>
       <c r="B105" t="n">
         <v>78973</v>
@@ -10742,14 +10742,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483063</v>
+        <v>483265</v>
       </c>
       <c r="R105" t="n">
-        <v>6828803</v>
+        <v>6828852</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10796,12 +10796,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11002,10 +11002,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755523</v>
+        <v>125747874</v>
       </c>
       <c r="B108" t="n">
-        <v>78640</v>
+        <v>57652</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,34 +11013,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483313</v>
+        <v>483012</v>
       </c>
       <c r="R108" t="n">
-        <v>6829017</v>
+        <v>6828723</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11087,57 +11092,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755532</v>
+        <v>125746396</v>
       </c>
       <c r="B109" t="n">
-        <v>80111</v>
+        <v>78732</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483294</v>
+        <v>483265</v>
       </c>
       <c r="R109" t="n">
-        <v>6829294</v>
+        <v>6828852</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11184,22 +11189,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125747874</v>
+        <v>125755523</v>
       </c>
       <c r="B110" t="n">
-        <v>57652</v>
+        <v>78640</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11207,39 +11212,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483012</v>
+        <v>483313</v>
       </c>
       <c r="R110" t="n">
-        <v>6828723</v>
+        <v>6829017</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11286,12 +11286,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11395,45 +11395,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125746396</v>
+        <v>125755532</v>
       </c>
       <c r="B112" t="n">
-        <v>78732</v>
+        <v>80111</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483265</v>
+        <v>483294</v>
       </c>
       <c r="R112" t="n">
-        <v>6828852</v>
+        <v>6829294</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11480,44 +11480,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755486</v>
+        <v>125755436</v>
       </c>
       <c r="B113" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483015</v>
+        <v>483303</v>
       </c>
       <c r="R113" t="n">
-        <v>6828711</v>
+        <v>6829290</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11589,32 +11589,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755436</v>
+        <v>125755486</v>
       </c>
       <c r="B114" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483303</v>
+        <v>483015</v>
       </c>
       <c r="R114" t="n">
-        <v>6829290</v>
+        <v>6828711</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11686,10 +11686,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755457</v>
+        <v>125755471</v>
       </c>
       <c r="B115" t="n">
-        <v>56835</v>
+        <v>78973</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11697,39 +11697,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483040</v>
+        <v>483206</v>
       </c>
       <c r="R115" t="n">
-        <v>6828774</v>
+        <v>6829193</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11788,10 +11783,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755471</v>
+        <v>125755457</v>
       </c>
       <c r="B116" t="n">
-        <v>78973</v>
+        <v>56835</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11799,34 +11794,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483206</v>
+        <v>483040</v>
       </c>
       <c r="R116" t="n">
-        <v>6829193</v>
+        <v>6828774</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125746848</v>
+        <v>125747249</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483247</v>
+        <v>483032</v>
       </c>
       <c r="R39" t="n">
-        <v>6828848</v>
+        <v>6828658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4350,6 +4350,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4376,7 +4381,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125747249</v>
+        <v>125747099</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4411,7 +4416,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483032</v>
+        <v>483090</v>
       </c>
       <c r="R40" t="n">
         <v>6828658</v>
@@ -4447,11 +4452,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125747099</v>
+        <v>125748935</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483090</v>
+        <v>483071</v>
       </c>
       <c r="R41" t="n">
-        <v>6828658</v>
+        <v>6828797</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125748935</v>
+        <v>125755501</v>
       </c>
       <c r="B42" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,34 +4586,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>483071</v>
       </c>
       <c r="R42" t="n">
-        <v>6828797</v>
+        <v>6828833</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4660,19 +4660,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755501</v>
+        <v>125755464</v>
       </c>
       <c r="B43" t="n">
         <v>78973</v>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483071</v>
+        <v>483423</v>
       </c>
       <c r="R43" t="n">
-        <v>6828833</v>
+        <v>6829325</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755464</v>
+        <v>125755508</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483423</v>
+        <v>483189</v>
       </c>
       <c r="R44" t="n">
-        <v>6829325</v>
+        <v>6828911</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755508</v>
+        <v>125755482</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483189</v>
+        <v>482960</v>
       </c>
       <c r="R45" t="n">
-        <v>6828911</v>
+        <v>6828769</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755482</v>
+        <v>125746848</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -4994,14 +4994,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>482960</v>
+        <v>483247</v>
       </c>
       <c r="R46" t="n">
-        <v>6828769</v>
+        <v>6828848</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755533</v>
+        <v>125755433</v>
       </c>
       <c r="B68" t="n">
-        <v>78379</v>
+        <v>57812</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483472</v>
+        <v>483307</v>
       </c>
       <c r="R68" t="n">
-        <v>6829305</v>
+        <v>6829287</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755517</v>
+        <v>125755533</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>78379</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483386</v>
+        <v>483472</v>
       </c>
       <c r="R69" t="n">
-        <v>6829003</v>
+        <v>6829305</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7306,50 +7306,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755431</v>
+        <v>125755517</v>
       </c>
       <c r="B70" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483099</v>
+        <v>483386</v>
       </c>
       <c r="R70" t="n">
-        <v>6828858</v>
+        <v>6829003</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7408,45 +7403,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755433</v>
+        <v>125755431</v>
       </c>
       <c r="B71" t="n">
-        <v>57812</v>
+        <v>56844</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483307</v>
+        <v>483099</v>
       </c>
       <c r="R71" t="n">
-        <v>6829287</v>
+        <v>6828858</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8189,7 +8189,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755474</v>
+        <v>125755515</v>
       </c>
       <c r="B79" t="n">
         <v>78973</v>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483188</v>
+        <v>483280</v>
       </c>
       <c r="R79" t="n">
-        <v>6829143</v>
+        <v>6828952</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,7 +8286,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755515</v>
+        <v>125755474</v>
       </c>
       <c r="B80" t="n">
         <v>78973</v>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483280</v>
+        <v>483188</v>
       </c>
       <c r="R80" t="n">
-        <v>6828952</v>
+        <v>6829143</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755422</v>
+        <v>125755507</v>
       </c>
       <c r="B101" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483099</v>
+        <v>483178</v>
       </c>
       <c r="R101" t="n">
-        <v>6828854</v>
+        <v>6828902</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755415</v>
+        <v>125755422</v>
       </c>
       <c r="B102" t="n">
-        <v>79591</v>
+        <v>79005</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483456</v>
+        <v>483099</v>
       </c>
       <c r="R102" t="n">
-        <v>6829062</v>
+        <v>6828854</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755507</v>
+        <v>125755415</v>
       </c>
       <c r="B103" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483178</v>
+        <v>483456</v>
       </c>
       <c r="R103" t="n">
-        <v>6828902</v>
+        <v>6829062</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125755426</v>
       </c>
       <c r="B4" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125755430</v>
       </c>
       <c r="B8" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125746064</v>
+        <v>125755488</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1977,14 +1977,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483474</v>
+        <v>483019</v>
       </c>
       <c r="R15" t="n">
-        <v>6829119</v>
+        <v>6828737</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,19 +2031,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125746931</v>
+        <v>125755475</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2074,14 +2074,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483156</v>
+        <v>483169</v>
       </c>
       <c r="R16" t="n">
-        <v>6828728</v>
+        <v>6829132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,11 +2116,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2133,22 +2128,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755416</v>
+        <v>125746931</v>
       </c>
       <c r="B17" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,34 +2151,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483454</v>
+        <v>483156</v>
       </c>
       <c r="R17" t="n">
-        <v>6829082</v>
+        <v>6828728</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2218,6 +2213,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2230,19 +2230,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755488</v>
+        <v>125746064</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2273,14 +2273,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483019</v>
+        <v>483474</v>
       </c>
       <c r="R18" t="n">
-        <v>6828737</v>
+        <v>6829119</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,22 +2327,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755475</v>
+        <v>125755416</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483169</v>
+        <v>483454</v>
       </c>
       <c r="R19" t="n">
-        <v>6829132</v>
+        <v>6829082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125745798</v>
+        <v>125755421</v>
       </c>
       <c r="B20" t="n">
-        <v>79591</v>
+        <v>79005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483474</v>
+        <v>483044</v>
       </c>
       <c r="R20" t="n">
-        <v>6829119</v>
+        <v>6828792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,22 +2521,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755440</v>
+        <v>125755506</v>
       </c>
       <c r="B21" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482960</v>
+        <v>483162</v>
       </c>
       <c r="R21" t="n">
-        <v>6828991</v>
+        <v>6828887</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755506</v>
+        <v>125745798</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,34 +2641,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483162</v>
+        <v>483474</v>
       </c>
       <c r="R22" t="n">
-        <v>6828887</v>
+        <v>6829119</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2715,22 +2715,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755494</v>
+        <v>125755440</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,21 +2738,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483047</v>
+        <v>482960</v>
       </c>
       <c r="R23" t="n">
-        <v>6828790</v>
+        <v>6828991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755421</v>
+        <v>125755480</v>
       </c>
       <c r="B24" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483044</v>
+        <v>482885</v>
       </c>
       <c r="R24" t="n">
-        <v>6828792</v>
+        <v>6828897</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755480</v>
+        <v>125755494</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>482885</v>
+        <v>483047</v>
       </c>
       <c r="R25" t="n">
-        <v>6828897</v>
+        <v>6828790</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125747349</v>
+        <v>125755513</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3146,14 +3146,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482981</v>
+        <v>483206</v>
       </c>
       <c r="R27" t="n">
-        <v>6828687</v>
+        <v>6828917</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3200,12 +3200,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755513</v>
+        <v>125747349</v>
       </c>
       <c r="B29" t="n">
         <v>78973</v>
@@ -3340,14 +3340,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483206</v>
+        <v>482981</v>
       </c>
       <c r="R29" t="n">
-        <v>6828917</v>
+        <v>6828687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3394,22 +3394,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755516</v>
+        <v>125755428</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483291</v>
+        <v>483280</v>
       </c>
       <c r="R30" t="n">
-        <v>6828969</v>
+        <v>6828942</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755428</v>
+        <v>125755516</v>
       </c>
       <c r="B32" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483280</v>
+        <v>483291</v>
       </c>
       <c r="R32" t="n">
-        <v>6828942</v>
+        <v>6828969</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3700,7 +3700,7 @@
         <v>125755460</v>
       </c>
       <c r="B33" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755478</v>
+        <v>125755502</v>
       </c>
       <c r="B34" t="n">
         <v>78973</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483147</v>
+        <v>483078</v>
       </c>
       <c r="R34" t="n">
-        <v>6829095</v>
+        <v>6828839</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755502</v>
+        <v>125755478</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483078</v>
+        <v>483147</v>
       </c>
       <c r="R35" t="n">
-        <v>6828839</v>
+        <v>6829095</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125747249</v>
+        <v>125755501</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4310,14 +4310,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R39" t="n">
-        <v>6828658</v>
+        <v>6828833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4352,11 +4352,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4369,19 +4364,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125747099</v>
+        <v>125755508</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4412,14 +4407,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483090</v>
+        <v>483189</v>
       </c>
       <c r="R40" t="n">
-        <v>6828658</v>
+        <v>6828911</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,22 +4461,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125748935</v>
+        <v>125755464</v>
       </c>
       <c r="B41" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483071</v>
+        <v>483423</v>
       </c>
       <c r="R41" t="n">
-        <v>6828797</v>
+        <v>6829325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4563,19 +4558,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755501</v>
+        <v>125746848</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4606,14 +4601,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483071</v>
+        <v>483247</v>
       </c>
       <c r="R42" t="n">
-        <v>6828833</v>
+        <v>6828848</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4660,19 +4655,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755464</v>
+        <v>125747099</v>
       </c>
       <c r="B43" t="n">
         <v>78973</v>
@@ -4703,14 +4698,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483423</v>
+        <v>483090</v>
       </c>
       <c r="R43" t="n">
-        <v>6829325</v>
+        <v>6828658</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4757,19 +4752,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755508</v>
+        <v>125755482</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4804,10 +4799,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483189</v>
+        <v>482960</v>
       </c>
       <c r="R44" t="n">
-        <v>6828911</v>
+        <v>6828769</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,7 +4861,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755482</v>
+        <v>125747249</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4897,14 +4892,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>482960</v>
+        <v>483032</v>
       </c>
       <c r="R45" t="n">
-        <v>6828769</v>
+        <v>6828658</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4939,6 +4934,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -4951,22 +4951,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125746848</v>
+        <v>125748935</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483247</v>
+        <v>483071</v>
       </c>
       <c r="R46" t="n">
-        <v>6828848</v>
+        <v>6828797</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755466</v>
+        <v>125755500</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483400</v>
+        <v>483068</v>
       </c>
       <c r="R47" t="n">
-        <v>6829318</v>
+        <v>6828819</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755456</v>
+        <v>125755466</v>
       </c>
       <c r="B48" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483114</v>
+        <v>483400</v>
       </c>
       <c r="R48" t="n">
-        <v>6828865</v>
+        <v>6829318</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755510</v>
+        <v>125755456</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483191</v>
+        <v>483114</v>
       </c>
       <c r="R49" t="n">
-        <v>6828929</v>
+        <v>6828865</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755453</v>
+        <v>125755510</v>
       </c>
       <c r="B50" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>482979</v>
+        <v>483191</v>
       </c>
       <c r="R50" t="n">
-        <v>6829140</v>
+        <v>6828929</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755500</v>
+        <v>125755453</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483068</v>
+        <v>482979</v>
       </c>
       <c r="R51" t="n">
-        <v>6828819</v>
+        <v>6829140</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125746158</v>
+        <v>125755483</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5683,14 +5683,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483342</v>
+        <v>482971</v>
       </c>
       <c r="R53" t="n">
-        <v>6828971</v>
+        <v>6828738</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5737,22 +5737,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755437</v>
+        <v>125755491</v>
       </c>
       <c r="B54" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483307</v>
+        <v>483015</v>
       </c>
       <c r="R54" t="n">
-        <v>6829287</v>
+        <v>6828753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755483</v>
+        <v>125755437</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>482971</v>
+        <v>483307</v>
       </c>
       <c r="R55" t="n">
-        <v>6828738</v>
+        <v>6829287</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755491</v>
+        <v>125746158</v>
       </c>
       <c r="B56" t="n">
         <v>78973</v>
@@ -5974,14 +5974,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483015</v>
+        <v>483342</v>
       </c>
       <c r="R56" t="n">
-        <v>6828753</v>
+        <v>6828971</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,12 +6028,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6234,7 +6234,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755492</v>
+        <v>125755468</v>
       </c>
       <c r="B59" t="n">
         <v>78973</v>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483032</v>
+        <v>483391</v>
       </c>
       <c r="R59" t="n">
-        <v>6828773</v>
+        <v>6829308</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,45 +6331,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755468</v>
+        <v>125755432</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483391</v>
+        <v>483446</v>
       </c>
       <c r="R60" t="n">
-        <v>6829308</v>
+        <v>6829026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,50 +6433,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755432</v>
+        <v>125755498</v>
       </c>
       <c r="B61" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483446</v>
+        <v>483071</v>
       </c>
       <c r="R61" t="n">
-        <v>6829026</v>
+        <v>6828809</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755498</v>
+        <v>125755492</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R62" t="n">
-        <v>6828809</v>
+        <v>6828773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
         <v>125755459</v>
       </c>
       <c r="B63" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755496</v>
+        <v>125755463</v>
       </c>
       <c r="B65" t="n">
         <v>78973</v>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483054</v>
+        <v>483450</v>
       </c>
       <c r="R65" t="n">
-        <v>6828788</v>
+        <v>6829306</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6918,7 +6918,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755463</v>
+        <v>125755496</v>
       </c>
       <c r="B66" t="n">
         <v>78973</v>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483450</v>
+        <v>483054</v>
       </c>
       <c r="R66" t="n">
-        <v>6829306</v>
+        <v>6828788</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755441</v>
+        <v>125755424</v>
       </c>
       <c r="B72" t="n">
-        <v>78732</v>
+        <v>79005</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,21 +7516,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483114</v>
+        <v>483162</v>
       </c>
       <c r="R72" t="n">
-        <v>6828865</v>
+        <v>6828879</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125748016</v>
+        <v>125755489</v>
       </c>
       <c r="B73" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7613,39 +7613,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483071</v>
+        <v>483001</v>
       </c>
       <c r="R73" t="n">
-        <v>6828797</v>
+        <v>6828740</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7692,22 +7687,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755424</v>
+        <v>125755472</v>
       </c>
       <c r="B74" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7715,21 +7710,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7739,10 +7734,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483162</v>
+        <v>483203</v>
       </c>
       <c r="R74" t="n">
-        <v>6828879</v>
+        <v>6829189</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7801,10 +7796,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755412</v>
+        <v>125755451</v>
       </c>
       <c r="B75" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7812,21 +7807,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7836,10 +7831,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>482912</v>
+        <v>483278</v>
       </c>
       <c r="R75" t="n">
-        <v>6828922</v>
+        <v>6828932</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7898,10 +7893,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755472</v>
+        <v>125755412</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7909,21 +7904,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7933,10 +7928,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483203</v>
+        <v>482912</v>
       </c>
       <c r="R76" t="n">
-        <v>6829189</v>
+        <v>6828922</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7995,10 +7990,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755489</v>
+        <v>125755441</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8006,21 +8001,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8030,10 +8025,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483001</v>
+        <v>483114</v>
       </c>
       <c r="R77" t="n">
-        <v>6828740</v>
+        <v>6828865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8092,10 +8087,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755451</v>
+        <v>125748016</v>
       </c>
       <c r="B78" t="n">
-        <v>78731</v>
+        <v>57652</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8103,34 +8098,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483278</v>
+        <v>483071</v>
       </c>
       <c r="R78" t="n">
-        <v>6828932</v>
+        <v>6828797</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8177,22 +8177,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755515</v>
+        <v>125755522</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8200,21 +8200,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483280</v>
+        <v>483303</v>
       </c>
       <c r="R79" t="n">
-        <v>6828952</v>
+        <v>6829017</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,7 +8286,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755474</v>
+        <v>125755515</v>
       </c>
       <c r="B80" t="n">
         <v>78973</v>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483188</v>
+        <v>483280</v>
       </c>
       <c r="R80" t="n">
-        <v>6829143</v>
+        <v>6828952</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755522</v>
+        <v>125755474</v>
       </c>
       <c r="B81" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8394,21 +8394,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483303</v>
+        <v>483188</v>
       </c>
       <c r="R81" t="n">
-        <v>6829017</v>
+        <v>6829143</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8771,10 +8771,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755504</v>
+        <v>125755418</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8782,21 +8782,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483117</v>
+        <v>482886</v>
       </c>
       <c r="R85" t="n">
-        <v>6828857</v>
+        <v>6828895</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8868,10 +8868,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755418</v>
+        <v>125755512</v>
       </c>
       <c r="B86" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8879,21 +8879,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>482886</v>
+        <v>483190</v>
       </c>
       <c r="R86" t="n">
-        <v>6828895</v>
+        <v>6828942</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755512</v>
+        <v>125755504</v>
       </c>
       <c r="B87" t="n">
         <v>78973</v>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483190</v>
+        <v>483117</v>
       </c>
       <c r="R87" t="n">
-        <v>6828942</v>
+        <v>6828857</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9062,7 +9062,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755511</v>
+        <v>125755479</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483188</v>
+        <v>482918</v>
       </c>
       <c r="R88" t="n">
-        <v>6828936</v>
+        <v>6828932</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,7 +9159,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755484</v>
+        <v>125755511</v>
       </c>
       <c r="B89" t="n">
         <v>78973</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>482976</v>
+        <v>483188</v>
       </c>
       <c r="R89" t="n">
-        <v>6828720</v>
+        <v>6828936</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755414</v>
+        <v>125755484</v>
       </c>
       <c r="B90" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9267,21 +9267,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483240</v>
+        <v>482976</v>
       </c>
       <c r="R90" t="n">
-        <v>6828921</v>
+        <v>6828720</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755479</v>
+        <v>125755414</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>482918</v>
+        <v>483240</v>
       </c>
       <c r="R91" t="n">
-        <v>6828932</v>
+        <v>6828921</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9547,32 +9547,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755446</v>
+        <v>125755520</v>
       </c>
       <c r="B93" t="n">
-        <v>80076</v>
+        <v>92528</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>482885</v>
+        <v>483458</v>
       </c>
       <c r="R93" t="n">
-        <v>6828845</v>
+        <v>6829089</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755526</v>
+        <v>125755446</v>
       </c>
       <c r="B96" t="n">
-        <v>78640</v>
+        <v>80076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9849,21 +9849,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483499</v>
+        <v>482885</v>
       </c>
       <c r="R96" t="n">
-        <v>6829120</v>
+        <v>6828845</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9935,10 +9935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755469</v>
+        <v>125755435</v>
       </c>
       <c r="B97" t="n">
-        <v>78973</v>
+        <v>58131</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483342</v>
+        <v>483450</v>
       </c>
       <c r="R97" t="n">
-        <v>6829286</v>
+        <v>6829302</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755493</v>
+        <v>125755526</v>
       </c>
       <c r="B98" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483037</v>
+        <v>483499</v>
       </c>
       <c r="R98" t="n">
-        <v>6828788</v>
+        <v>6829120</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,32 +10129,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755520</v>
+        <v>125755469</v>
       </c>
       <c r="B99" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483458</v>
+        <v>483342</v>
       </c>
       <c r="R99" t="n">
-        <v>6829089</v>
+        <v>6829286</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755435</v>
+        <v>125755493</v>
       </c>
       <c r="B100" t="n">
-        <v>58131</v>
+        <v>78973</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483450</v>
+        <v>483037</v>
       </c>
       <c r="R100" t="n">
-        <v>6829302</v>
+        <v>6828788</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755507</v>
+        <v>125755422</v>
       </c>
       <c r="B101" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10334,21 +10334,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483178</v>
+        <v>483099</v>
       </c>
       <c r="R101" t="n">
-        <v>6828902</v>
+        <v>6828854</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755422</v>
+        <v>125755507</v>
       </c>
       <c r="B102" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483099</v>
+        <v>483178</v>
       </c>
       <c r="R102" t="n">
-        <v>6828854</v>
+        <v>6828902</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755497</v>
+        <v>125755485</v>
       </c>
       <c r="B104" t="n">
         <v>78973</v>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483063</v>
+        <v>483002</v>
       </c>
       <c r="R104" t="n">
-        <v>6828803</v>
+        <v>6828695</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10711,7 +10711,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125746359</v>
+        <v>125755490</v>
       </c>
       <c r="B105" t="n">
         <v>78973</v>
@@ -10742,14 +10742,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483265</v>
+        <v>483007</v>
       </c>
       <c r="R105" t="n">
-        <v>6828852</v>
+        <v>6828754</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10796,19 +10796,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755490</v>
+        <v>125755497</v>
       </c>
       <c r="B106" t="n">
         <v>78973</v>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483007</v>
+        <v>483063</v>
       </c>
       <c r="R106" t="n">
-        <v>6828754</v>
+        <v>6828803</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755485</v>
+        <v>125746359</v>
       </c>
       <c r="B107" t="n">
         <v>78973</v>
@@ -10936,14 +10936,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483002</v>
+        <v>483265</v>
       </c>
       <c r="R107" t="n">
-        <v>6828695</v>
+        <v>6828852</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10990,22 +10990,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125747874</v>
+        <v>125746396</v>
       </c>
       <c r="B108" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,39 +11013,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483012</v>
+        <v>483265</v>
       </c>
       <c r="R108" t="n">
-        <v>6828723</v>
+        <v>6828852</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11104,10 +11099,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125746396</v>
+        <v>125755523</v>
       </c>
       <c r="B109" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11115,34 +11110,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483265</v>
+        <v>483313</v>
       </c>
       <c r="R109" t="n">
-        <v>6828852</v>
+        <v>6829017</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11189,22 +11184,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755523</v>
+        <v>125755455</v>
       </c>
       <c r="B110" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11212,21 +11207,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11236,10 +11231,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483313</v>
+        <v>482942</v>
       </c>
       <c r="R110" t="n">
-        <v>6829017</v>
+        <v>6828979</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11298,32 +11293,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755455</v>
+        <v>125755532</v>
       </c>
       <c r="B111" t="n">
-        <v>78731</v>
+        <v>80111</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11333,10 +11328,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>482942</v>
+        <v>483294</v>
       </c>
       <c r="R111" t="n">
-        <v>6828979</v>
+        <v>6829294</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11395,45 +11390,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755532</v>
+        <v>125747874</v>
       </c>
       <c r="B112" t="n">
-        <v>80111</v>
+        <v>57652</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483294</v>
+        <v>483012</v>
       </c>
       <c r="R112" t="n">
-        <v>6829294</v>
+        <v>6828723</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11480,44 +11480,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755436</v>
+        <v>125755471</v>
       </c>
       <c r="B113" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R113" t="n">
-        <v>6829290</v>
+        <v>6829193</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11686,32 +11686,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755471</v>
+        <v>125755436</v>
       </c>
       <c r="B115" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R115" t="n">
-        <v>6829193</v>
+        <v>6829290</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY119"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125744833</v>
+        <v>125755529</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483642</v>
+        <v>483526</v>
       </c>
       <c r="R5" t="n">
-        <v>6829342</v>
+        <v>6829108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755529</v>
+        <v>125755447</v>
       </c>
       <c r="B6" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483526</v>
+        <v>483591</v>
       </c>
       <c r="R6" t="n">
-        <v>6829108</v>
+        <v>6829246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755447</v>
+        <v>125755430</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,39 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483591</v>
+        <v>483636</v>
       </c>
       <c r="R7" t="n">
-        <v>6829246</v>
+        <v>6829343</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755430</v>
+        <v>125755528</v>
       </c>
       <c r="B8" t="n">
-        <v>91238</v>
+        <v>78640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483636</v>
+        <v>483525</v>
       </c>
       <c r="R8" t="n">
-        <v>6829343</v>
+        <v>6829111</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755528</v>
+        <v>125755409</v>
       </c>
       <c r="B9" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483525</v>
+        <v>483587</v>
       </c>
       <c r="R9" t="n">
-        <v>6829111</v>
+        <v>6829364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755409</v>
+        <v>125755448</v>
       </c>
       <c r="B10" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,34 +1467,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483587</v>
+        <v>483529</v>
       </c>
       <c r="R10" t="n">
-        <v>6829364</v>
+        <v>6829109</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,7 +1558,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755448</v>
+        <v>125755452</v>
       </c>
       <c r="B11" t="n">
         <v>78731</v>
@@ -1582,21 +1587,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483529</v>
+        <v>483587</v>
       </c>
       <c r="R11" t="n">
-        <v>6829109</v>
+        <v>6829364</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755452</v>
+        <v>125755438</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78997</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483587</v>
+        <v>483600</v>
       </c>
       <c r="R12" t="n">
-        <v>6829364</v>
+        <v>6829152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755438</v>
+        <v>125755439</v>
       </c>
       <c r="B13" t="n">
-        <v>78997</v>
+        <v>78732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483600</v>
+        <v>483586</v>
       </c>
       <c r="R13" t="n">
-        <v>6829152</v>
+        <v>6829364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755439</v>
+        <v>125744833</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483586</v>
+        <v>483642</v>
       </c>
       <c r="R14" t="n">
-        <v>6829364</v>
+        <v>6829342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1934,12 +1934,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125746931</v>
+        <v>125755416</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,34 +2151,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483156</v>
+        <v>483454</v>
       </c>
       <c r="R17" t="n">
-        <v>6828728</v>
+        <v>6829082</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2213,11 +2213,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2230,22 +2225,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125746064</v>
+        <v>125755421</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,34 +2248,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483474</v>
+        <v>483044</v>
       </c>
       <c r="R18" t="n">
-        <v>6829119</v>
+        <v>6828792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,22 +2322,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755416</v>
+        <v>125755506</v>
       </c>
       <c r="B19" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483454</v>
+        <v>483162</v>
       </c>
       <c r="R19" t="n">
-        <v>6829082</v>
+        <v>6828887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755421</v>
+        <v>125755440</v>
       </c>
       <c r="B20" t="n">
-        <v>79005</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483044</v>
+        <v>482960</v>
       </c>
       <c r="R20" t="n">
-        <v>6828792</v>
+        <v>6828991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,7 +2528,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755506</v>
+        <v>125755480</v>
       </c>
       <c r="B21" t="n">
         <v>78973</v>
@@ -2568,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483162</v>
+        <v>482885</v>
       </c>
       <c r="R21" t="n">
-        <v>6828887</v>
+        <v>6828897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125745798</v>
+        <v>125755494</v>
       </c>
       <c r="B22" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,34 +2636,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483474</v>
+        <v>483047</v>
       </c>
       <c r="R22" t="n">
-        <v>6829119</v>
+        <v>6828790</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2715,22 +2710,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755440</v>
+        <v>125755445</v>
       </c>
       <c r="B23" t="n">
-        <v>78732</v>
+        <v>80076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482960</v>
+        <v>482900</v>
       </c>
       <c r="R23" t="n">
-        <v>6828991</v>
+        <v>6828861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,27 +2819,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755480</v>
+        <v>125755530</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>80111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2859,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482885</v>
+        <v>483303</v>
       </c>
       <c r="R24" t="n">
-        <v>6828897</v>
+        <v>6829288</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755494</v>
+        <v>125755513</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2956,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483047</v>
+        <v>483206</v>
       </c>
       <c r="R25" t="n">
-        <v>6828790</v>
+        <v>6828917</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3018,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755445</v>
+        <v>125755428</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>79562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3029,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3053,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482900</v>
+        <v>483280</v>
       </c>
       <c r="R26" t="n">
-        <v>6828861</v>
+        <v>6828942</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3115,7 +3110,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755513</v>
+        <v>125755481</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3150,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483206</v>
+        <v>482929</v>
       </c>
       <c r="R27" t="n">
-        <v>6828917</v>
+        <v>6828797</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3212,27 +3207,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755530</v>
+        <v>125755516</v>
       </c>
       <c r="B28" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3247,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483303</v>
+        <v>483291</v>
       </c>
       <c r="R28" t="n">
-        <v>6829288</v>
+        <v>6828969</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3309,45 +3304,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125747349</v>
+        <v>125755460</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>91399</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482981</v>
+        <v>482913</v>
       </c>
       <c r="R29" t="n">
-        <v>6828687</v>
+        <v>6829095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3394,22 +3389,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755428</v>
+        <v>125755502</v>
       </c>
       <c r="B30" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3412,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483280</v>
+        <v>483078</v>
       </c>
       <c r="R30" t="n">
-        <v>6828942</v>
+        <v>6828839</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,7 +3498,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755481</v>
+        <v>125755478</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3538,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>482929</v>
+        <v>483147</v>
       </c>
       <c r="R31" t="n">
-        <v>6828797</v>
+        <v>6829095</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,7 +3595,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755516</v>
+        <v>125755473</v>
       </c>
       <c r="B32" t="n">
         <v>78973</v>
@@ -3635,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483291</v>
+        <v>483182</v>
       </c>
       <c r="R32" t="n">
-        <v>6828969</v>
+        <v>6829175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,32 +3692,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755460</v>
+        <v>125755411</v>
       </c>
       <c r="B33" t="n">
-        <v>91399</v>
+        <v>79591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>482913</v>
+        <v>482945</v>
       </c>
       <c r="R33" t="n">
-        <v>6829095</v>
+        <v>6829125</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3789,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755502</v>
+        <v>125755417</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3800,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3824,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483078</v>
+        <v>482974</v>
       </c>
       <c r="R34" t="n">
-        <v>6828839</v>
+        <v>6829143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3886,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755478</v>
+        <v>125755482</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483147</v>
+        <v>482960</v>
       </c>
       <c r="R35" t="n">
-        <v>6829095</v>
+        <v>6828769</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,7 +3983,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755473</v>
+        <v>125755501</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4023,10 +4018,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483182</v>
+        <v>483071</v>
       </c>
       <c r="R36" t="n">
-        <v>6829175</v>
+        <v>6828833</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4080,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755411</v>
+        <v>125755508</v>
       </c>
       <c r="B37" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4091,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>482945</v>
+        <v>483189</v>
       </c>
       <c r="R37" t="n">
-        <v>6829125</v>
+        <v>6828911</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4177,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755417</v>
+        <v>125755464</v>
       </c>
       <c r="B38" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4188,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4212,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>482974</v>
+        <v>483423</v>
       </c>
       <c r="R38" t="n">
-        <v>6829143</v>
+        <v>6829325</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,7 +4274,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755501</v>
+        <v>125755500</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483071</v>
+        <v>483068</v>
       </c>
       <c r="R39" t="n">
-        <v>6828833</v>
+        <v>6828819</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4376,7 +4371,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755508</v>
+        <v>125755466</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4411,10 +4406,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483189</v>
+        <v>483400</v>
       </c>
       <c r="R40" t="n">
-        <v>6828911</v>
+        <v>6829318</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,10 +4468,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755464</v>
+        <v>125755456</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4479,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4503,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483423</v>
+        <v>483114</v>
       </c>
       <c r="R41" t="n">
-        <v>6829325</v>
+        <v>6828865</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,7 +4565,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125746848</v>
+        <v>125755510</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4601,14 +4596,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483247</v>
+        <v>483191</v>
       </c>
       <c r="R42" t="n">
-        <v>6828848</v>
+        <v>6828929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4655,22 +4650,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125747099</v>
+        <v>125755453</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,34 +4673,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483090</v>
+        <v>482979</v>
       </c>
       <c r="R43" t="n">
-        <v>6828658</v>
+        <v>6829140</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4752,22 +4747,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755482</v>
+        <v>125755536</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4775,34 +4770,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>482960</v>
+        <v>483037</v>
       </c>
       <c r="R44" t="n">
-        <v>6828769</v>
+        <v>6828775</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4835,6 +4835,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4861,7 +4866,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125747249</v>
+        <v>125755483</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4892,14 +4897,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483032</v>
+        <v>482971</v>
       </c>
       <c r="R45" t="n">
-        <v>6828658</v>
+        <v>6828738</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4934,11 +4939,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -4951,22 +4951,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125748935</v>
+        <v>125755491</v>
       </c>
       <c r="B46" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,34 +4974,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483071</v>
+        <v>483015</v>
       </c>
       <c r="R46" t="n">
-        <v>6828797</v>
+        <v>6828753</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5048,22 +5048,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755500</v>
+        <v>125755437</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483068</v>
+        <v>483307</v>
       </c>
       <c r="R47" t="n">
-        <v>6828819</v>
+        <v>6829287</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,32 +5157,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755466</v>
+        <v>125755458</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>58327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483400</v>
+        <v>483319</v>
       </c>
       <c r="R48" t="n">
-        <v>6829318</v>
+        <v>6829293</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755456</v>
+        <v>125755442</v>
       </c>
       <c r="B49" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483114</v>
+        <v>483201</v>
       </c>
       <c r="R49" t="n">
-        <v>6828865</v>
+        <v>6828916</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755510</v>
+        <v>125755468</v>
       </c>
       <c r="B50" t="n">
         <v>78973</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483191</v>
+        <v>483391</v>
       </c>
       <c r="R50" t="n">
-        <v>6828929</v>
+        <v>6829308</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,45 +5448,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755453</v>
+        <v>125755432</v>
       </c>
       <c r="B51" t="n">
-        <v>78731</v>
+        <v>56844</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>482979</v>
+        <v>483446</v>
       </c>
       <c r="R51" t="n">
-        <v>6829140</v>
+        <v>6829026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5545,10 +5550,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755536</v>
+        <v>125755498</v>
       </c>
       <c r="B52" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,39 +5561,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483037</v>
+        <v>483071</v>
       </c>
       <c r="R52" t="n">
-        <v>6828775</v>
+        <v>6828809</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5621,11 +5621,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5652,7 +5647,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755483</v>
+        <v>125755492</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5687,10 +5682,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>482971</v>
+        <v>483032</v>
       </c>
       <c r="R53" t="n">
-        <v>6828738</v>
+        <v>6828773</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5749,10 +5744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755491</v>
+        <v>125755459</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>91252</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,21 +5755,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483015</v>
+        <v>483398</v>
       </c>
       <c r="R54" t="n">
-        <v>6828753</v>
+        <v>6829316</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,10 +5841,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755437</v>
+        <v>125755419</v>
       </c>
       <c r="B55" t="n">
-        <v>80077</v>
+        <v>79005</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5852,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5876,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483307</v>
+        <v>483005</v>
       </c>
       <c r="R55" t="n">
-        <v>6829287</v>
+        <v>6828754</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,7 +5938,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125746158</v>
+        <v>125755463</v>
       </c>
       <c r="B56" t="n">
         <v>78973</v>
@@ -5974,14 +5969,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483342</v>
+        <v>483450</v>
       </c>
       <c r="R56" t="n">
-        <v>6828971</v>
+        <v>6829306</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,44 +6023,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755458</v>
+        <v>125755496</v>
       </c>
       <c r="B57" t="n">
-        <v>58327</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483319</v>
+        <v>483054</v>
       </c>
       <c r="R57" t="n">
-        <v>6829293</v>
+        <v>6828788</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6137,10 +6132,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755442</v>
+        <v>125755533</v>
       </c>
       <c r="B58" t="n">
-        <v>78732</v>
+        <v>78379</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6148,21 +6143,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6172,10 +6167,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483201</v>
+        <v>483472</v>
       </c>
       <c r="R58" t="n">
-        <v>6828916</v>
+        <v>6829305</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6234,7 +6229,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755468</v>
+        <v>125755517</v>
       </c>
       <c r="B59" t="n">
         <v>78973</v>
@@ -6269,10 +6264,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483391</v>
+        <v>483386</v>
       </c>
       <c r="R59" t="n">
-        <v>6829308</v>
+        <v>6829003</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,7 +6326,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755432</v>
+        <v>125755431</v>
       </c>
       <c r="B60" t="n">
         <v>56844</v>
@@ -6362,7 +6357,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6371,10 +6366,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483446</v>
+        <v>483099</v>
       </c>
       <c r="R60" t="n">
-        <v>6829026</v>
+        <v>6828858</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,10 +6428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755498</v>
+        <v>125755525</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6444,21 +6439,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6468,10 +6463,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483071</v>
+        <v>483442</v>
       </c>
       <c r="R61" t="n">
-        <v>6828809</v>
+        <v>6829028</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,10 +6525,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755492</v>
+        <v>125755433</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6536,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6560,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483032</v>
+        <v>483307</v>
       </c>
       <c r="R62" t="n">
-        <v>6828773</v>
+        <v>6829287</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6622,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755459</v>
+        <v>125755441</v>
       </c>
       <c r="B63" t="n">
-        <v>91252</v>
+        <v>78732</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6633,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6657,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483398</v>
+        <v>483114</v>
       </c>
       <c r="R63" t="n">
-        <v>6829316</v>
+        <v>6828865</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755419</v>
+        <v>125755489</v>
       </c>
       <c r="B64" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6730,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6754,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483005</v>
+        <v>483001</v>
       </c>
       <c r="R64" t="n">
-        <v>6828754</v>
+        <v>6828740</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6821,7 +6816,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755463</v>
+        <v>125755472</v>
       </c>
       <c r="B65" t="n">
         <v>78973</v>
@@ -6856,10 +6851,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483450</v>
+        <v>483203</v>
       </c>
       <c r="R65" t="n">
-        <v>6829306</v>
+        <v>6829189</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6918,10 +6913,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755496</v>
+        <v>125755451</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6929,21 +6924,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6953,10 +6948,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483054</v>
+        <v>483278</v>
       </c>
       <c r="R66" t="n">
-        <v>6828788</v>
+        <v>6828932</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7015,10 +7010,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755525</v>
+        <v>125755424</v>
       </c>
       <c r="B67" t="n">
-        <v>78640</v>
+        <v>79005</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7026,21 +7021,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7050,10 +7045,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483442</v>
+        <v>483162</v>
       </c>
       <c r="R67" t="n">
-        <v>6829028</v>
+        <v>6828879</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7112,10 +7107,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755433</v>
+        <v>125755412</v>
       </c>
       <c r="B68" t="n">
-        <v>57812</v>
+        <v>79591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7123,21 +7118,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7147,10 +7142,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483307</v>
+        <v>482912</v>
       </c>
       <c r="R68" t="n">
-        <v>6829287</v>
+        <v>6828922</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7209,10 +7204,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755533</v>
+        <v>125755522</v>
       </c>
       <c r="B69" t="n">
-        <v>78379</v>
+        <v>78640</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7220,21 +7215,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7244,10 +7239,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483472</v>
+        <v>483303</v>
       </c>
       <c r="R69" t="n">
-        <v>6829305</v>
+        <v>6829017</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7306,7 +7301,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755517</v>
+        <v>125755515</v>
       </c>
       <c r="B70" t="n">
         <v>78973</v>
@@ -7341,10 +7336,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483386</v>
+        <v>483280</v>
       </c>
       <c r="R70" t="n">
-        <v>6829003</v>
+        <v>6828952</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7403,50 +7398,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755431</v>
+        <v>125755474</v>
       </c>
       <c r="B71" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483099</v>
+        <v>483188</v>
       </c>
       <c r="R71" t="n">
-        <v>6828858</v>
+        <v>6829143</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7505,10 +7495,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755424</v>
+        <v>125755514</v>
       </c>
       <c r="B72" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7516,21 +7506,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7540,10 +7530,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483162</v>
+        <v>483220</v>
       </c>
       <c r="R72" t="n">
-        <v>6828879</v>
+        <v>6828907</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7602,7 +7592,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755489</v>
+        <v>125755518</v>
       </c>
       <c r="B73" t="n">
         <v>78973</v>
@@ -7637,10 +7627,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483001</v>
+        <v>483467</v>
       </c>
       <c r="R73" t="n">
-        <v>6828740</v>
+        <v>6829027</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7699,7 +7689,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755472</v>
+        <v>125755503</v>
       </c>
       <c r="B74" t="n">
         <v>78973</v>
@@ -7734,10 +7724,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483203</v>
+        <v>483095</v>
       </c>
       <c r="R74" t="n">
-        <v>6829189</v>
+        <v>6828845</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7796,10 +7786,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755451</v>
+        <v>125755418</v>
       </c>
       <c r="B75" t="n">
-        <v>78731</v>
+        <v>79005</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,21 +7797,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7831,10 +7821,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483278</v>
+        <v>482886</v>
       </c>
       <c r="R75" t="n">
-        <v>6828932</v>
+        <v>6828895</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7893,10 +7883,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755412</v>
+        <v>125755512</v>
       </c>
       <c r="B76" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7904,21 +7894,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7928,10 +7918,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>482912</v>
+        <v>483190</v>
       </c>
       <c r="R76" t="n">
-        <v>6828922</v>
+        <v>6828942</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7990,10 +7980,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755441</v>
+        <v>125755504</v>
       </c>
       <c r="B77" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8001,21 +7991,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8025,10 +8015,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483114</v>
+        <v>483117</v>
       </c>
       <c r="R77" t="n">
-        <v>6828865</v>
+        <v>6828857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8087,10 +8077,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125748016</v>
+        <v>125755479</v>
       </c>
       <c r="B78" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8098,39 +8088,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483071</v>
+        <v>482918</v>
       </c>
       <c r="R78" t="n">
-        <v>6828797</v>
+        <v>6828932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8177,22 +8162,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755522</v>
+        <v>125755511</v>
       </c>
       <c r="B79" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8200,21 +8185,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8224,10 +8209,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483303</v>
+        <v>483188</v>
       </c>
       <c r="R79" t="n">
-        <v>6829017</v>
+        <v>6828936</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,7 +8271,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755515</v>
+        <v>125755484</v>
       </c>
       <c r="B80" t="n">
         <v>78973</v>
@@ -8321,10 +8306,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483280</v>
+        <v>482976</v>
       </c>
       <c r="R80" t="n">
-        <v>6828952</v>
+        <v>6828720</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8383,10 +8368,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755474</v>
+        <v>125755414</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8394,21 +8379,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8418,10 +8403,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483188</v>
+        <v>483240</v>
       </c>
       <c r="R81" t="n">
-        <v>6829143</v>
+        <v>6828921</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8480,32 +8465,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755514</v>
+        <v>125755520</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8515,10 +8500,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483220</v>
+        <v>483458</v>
       </c>
       <c r="R82" t="n">
-        <v>6828907</v>
+        <v>6829089</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,10 +8562,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755518</v>
+        <v>125755526</v>
       </c>
       <c r="B83" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8588,21 +8573,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8612,10 +8597,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483467</v>
+        <v>483499</v>
       </c>
       <c r="R83" t="n">
-        <v>6829027</v>
+        <v>6829120</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8674,7 +8659,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755503</v>
+        <v>125755469</v>
       </c>
       <c r="B84" t="n">
         <v>78973</v>
@@ -8709,10 +8694,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483095</v>
+        <v>483342</v>
       </c>
       <c r="R84" t="n">
-        <v>6828845</v>
+        <v>6829286</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8771,10 +8756,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755418</v>
+        <v>125755493</v>
       </c>
       <c r="B85" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8782,21 +8767,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8806,10 +8791,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>482886</v>
+        <v>483037</v>
       </c>
       <c r="R85" t="n">
-        <v>6828895</v>
+        <v>6828788</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8868,10 +8853,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755512</v>
+        <v>125755413</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8879,21 +8864,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8903,10 +8888,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483190</v>
+        <v>482962</v>
       </c>
       <c r="R86" t="n">
-        <v>6828942</v>
+        <v>6828771</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8965,10 +8950,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755504</v>
+        <v>125755444</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8976,21 +8961,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9000,10 +8985,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483117</v>
+        <v>483272</v>
       </c>
       <c r="R87" t="n">
-        <v>6828857</v>
+        <v>6829286</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9062,10 +9047,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755479</v>
+        <v>125755446</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9073,21 +9058,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9097,10 +9082,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482918</v>
+        <v>482885</v>
       </c>
       <c r="R88" t="n">
-        <v>6828932</v>
+        <v>6828845</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,10 +9144,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755511</v>
+        <v>125755435</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>58131</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9170,21 +9155,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9194,10 +9179,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483188</v>
+        <v>483450</v>
       </c>
       <c r="R89" t="n">
-        <v>6828936</v>
+        <v>6829302</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9256,10 +9241,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755484</v>
+        <v>125755422</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9267,21 +9252,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9291,10 +9276,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482976</v>
+        <v>483099</v>
       </c>
       <c r="R90" t="n">
-        <v>6828720</v>
+        <v>6828854</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9353,10 +9338,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755414</v>
+        <v>125755507</v>
       </c>
       <c r="B91" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9364,21 +9349,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9388,10 +9373,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483240</v>
+        <v>483178</v>
       </c>
       <c r="R91" t="n">
-        <v>6828921</v>
+        <v>6828902</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9450,10 +9435,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125747880</v>
+        <v>125755415</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9461,34 +9446,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483012</v>
+        <v>483456</v>
       </c>
       <c r="R92" t="n">
-        <v>6828723</v>
+        <v>6829062</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9535,44 +9520,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755520</v>
+        <v>125755485</v>
       </c>
       <c r="B93" t="n">
-        <v>92528</v>
+        <v>78973</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9582,10 +9567,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483458</v>
+        <v>483002</v>
       </c>
       <c r="R93" t="n">
-        <v>6829089</v>
+        <v>6828695</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9644,10 +9629,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755413</v>
+        <v>125755490</v>
       </c>
       <c r="B94" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9655,21 +9640,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9679,10 +9664,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>482962</v>
+        <v>483007</v>
       </c>
       <c r="R94" t="n">
-        <v>6828771</v>
+        <v>6828754</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9741,10 +9726,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755444</v>
+        <v>125755497</v>
       </c>
       <c r="B95" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9752,21 +9737,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9776,10 +9761,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483272</v>
+        <v>483063</v>
       </c>
       <c r="R95" t="n">
-        <v>6829286</v>
+        <v>6828803</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9838,10 +9823,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755446</v>
+        <v>125755523</v>
       </c>
       <c r="B96" t="n">
-        <v>80076</v>
+        <v>78640</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9849,21 +9834,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9873,10 +9858,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>482885</v>
+        <v>483313</v>
       </c>
       <c r="R96" t="n">
-        <v>6828845</v>
+        <v>6829017</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9935,10 +9920,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755435</v>
+        <v>125755455</v>
       </c>
       <c r="B97" t="n">
-        <v>58131</v>
+        <v>78731</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9946,21 +9931,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103018</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9970,10 +9955,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483450</v>
+        <v>482942</v>
       </c>
       <c r="R97" t="n">
-        <v>6829302</v>
+        <v>6828979</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10032,32 +10017,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755526</v>
+        <v>125755532</v>
       </c>
       <c r="B98" t="n">
-        <v>78640</v>
+        <v>80111</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10067,10 +10052,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483499</v>
+        <v>483294</v>
       </c>
       <c r="R98" t="n">
-        <v>6829120</v>
+        <v>6829294</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10129,7 +10114,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755469</v>
+        <v>125755471</v>
       </c>
       <c r="B99" t="n">
         <v>78973</v>
@@ -10164,10 +10149,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483342</v>
+        <v>483206</v>
       </c>
       <c r="R99" t="n">
-        <v>6829286</v>
+        <v>6829193</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10226,7 +10211,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755493</v>
+        <v>125755486</v>
       </c>
       <c r="B100" t="n">
         <v>78973</v>
@@ -10261,10 +10246,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483037</v>
+        <v>483015</v>
       </c>
       <c r="R100" t="n">
-        <v>6828788</v>
+        <v>6828711</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10323,32 +10308,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755422</v>
+        <v>125755436</v>
       </c>
       <c r="B101" t="n">
-        <v>79005</v>
+        <v>80105</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10358,10 +10343,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483099</v>
+        <v>483303</v>
       </c>
       <c r="R101" t="n">
-        <v>6828854</v>
+        <v>6829290</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10420,10 +10405,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755507</v>
+        <v>125755457</v>
       </c>
       <c r="B102" t="n">
-        <v>78973</v>
+        <v>56835</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10431,34 +10416,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483178</v>
+        <v>483040</v>
       </c>
       <c r="R102" t="n">
-        <v>6828902</v>
+        <v>6828774</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10517,10 +10507,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755415</v>
+        <v>125755427</v>
       </c>
       <c r="B103" t="n">
-        <v>79591</v>
+        <v>79562</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10528,21 +10518,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10552,10 +10542,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483456</v>
+        <v>483472</v>
       </c>
       <c r="R103" t="n">
-        <v>6829062</v>
+        <v>6829305</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10614,7 +10604,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755485</v>
+        <v>125755462</v>
       </c>
       <c r="B104" t="n">
         <v>78973</v>
@@ -10649,10 +10639,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483002</v>
+        <v>483199</v>
       </c>
       <c r="R104" t="n">
-        <v>6828695</v>
+        <v>6828937</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10685,6 +10675,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>150 cm långt i område mycket rikt på hänglavar och keloved. Saknar hänsynsband.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10711,10 +10706,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755490</v>
+        <v>125691576</v>
       </c>
       <c r="B105" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10722,34 +10717,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483007</v>
+        <v>483361</v>
       </c>
       <c r="R105" t="n">
-        <v>6828754</v>
+        <v>6829179</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10776,12 +10774,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10790,28 +10793,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755497</v>
+        <v>125745158</v>
       </c>
       <c r="B106" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10819,37 +10823,45 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483063</v>
+        <v>483359</v>
       </c>
       <c r="R106" t="n">
-        <v>6828803</v>
+        <v>6829093</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10893,19 +10905,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125746359</v>
+        <v>125746931</v>
       </c>
       <c r="B107" t="n">
         <v>78973</v>
@@ -10940,10 +10952,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483265</v>
+        <v>483156</v>
       </c>
       <c r="R107" t="n">
-        <v>6828852</v>
+        <v>6828728</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10976,6 +10988,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11002,10 +11019,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125746396</v>
+        <v>125746064</v>
       </c>
       <c r="B108" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11013,34 +11030,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483265</v>
+        <v>483474</v>
       </c>
       <c r="R108" t="n">
-        <v>6828852</v>
+        <v>6829119</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11099,10 +11116,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755523</v>
+        <v>125745798</v>
       </c>
       <c r="B109" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11110,34 +11127,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483313</v>
+        <v>483474</v>
       </c>
       <c r="R109" t="n">
-        <v>6829017</v>
+        <v>6829119</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11184,22 +11201,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755455</v>
+        <v>125747349</v>
       </c>
       <c r="B110" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11207,34 +11224,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>482942</v>
+        <v>482981</v>
       </c>
       <c r="R110" t="n">
-        <v>6828979</v>
+        <v>6828687</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11281,60 +11298,63 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755532</v>
+        <v>125745325</v>
       </c>
       <c r="B111" t="n">
-        <v>80111</v>
+        <v>91399</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6463</v>
+        <v>1503</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483294</v>
+        <v>483279</v>
       </c>
       <c r="R111" t="n">
-        <v>6829294</v>
+        <v>6829148</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11372,28 +11392,29 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125747874</v>
+        <v>125744923</v>
       </c>
       <c r="B112" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11401,42 +11422,40 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483012</v>
+        <v>483126</v>
       </c>
       <c r="R112" t="n">
-        <v>6828723</v>
+        <v>6829064</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11474,6 +11493,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11492,7 +11512,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755471</v>
+        <v>125746848</v>
       </c>
       <c r="B113" t="n">
         <v>78973</v>
@@ -11523,14 +11543,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483206</v>
+        <v>483247</v>
       </c>
       <c r="R113" t="n">
-        <v>6829193</v>
+        <v>6828848</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11577,22 +11597,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755486</v>
+        <v>125748935</v>
       </c>
       <c r="B114" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11600,34 +11620,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483015</v>
+        <v>483071</v>
       </c>
       <c r="R114" t="n">
-        <v>6828711</v>
+        <v>6828797</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11674,57 +11694,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755436</v>
+        <v>125747249</v>
       </c>
       <c r="B115" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483303</v>
+        <v>483032</v>
       </c>
       <c r="R115" t="n">
-        <v>6829290</v>
+        <v>6828658</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11759,6 +11779,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -11771,22 +11796,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755457</v>
+        <v>125747099</v>
       </c>
       <c r="B116" t="n">
-        <v>56835</v>
+        <v>78973</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11794,39 +11819,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483040</v>
+        <v>483090</v>
       </c>
       <c r="R116" t="n">
-        <v>6828774</v>
+        <v>6828658</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11873,22 +11893,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755427</v>
+        <v>125746158</v>
       </c>
       <c r="B117" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11896,34 +11916,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483472</v>
+        <v>483342</v>
       </c>
       <c r="R117" t="n">
-        <v>6829305</v>
+        <v>6828971</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11970,22 +11990,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755462</v>
+        <v>125748016</v>
       </c>
       <c r="B118" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11993,34 +12013,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483199</v>
+        <v>483071</v>
       </c>
       <c r="R118" t="n">
-        <v>6828937</v>
+        <v>6828797</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12055,11 +12080,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>150 cm långt i område mycket rikt på hänglavar och keloved. Saknar hänsynsband.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12072,22 +12092,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125691576</v>
+        <v>125747880</v>
       </c>
       <c r="B119" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12095,37 +12115,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483361</v>
+        <v>483012</v>
       </c>
       <c r="R119" t="n">
-        <v>6829179</v>
+        <v>6828723</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12152,17 +12169,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12171,7 +12183,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12187,6 +12198,302 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>125746359</v>
+      </c>
+      <c r="B120" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Abborrsjöbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>483265</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6828852</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>125746396</v>
+      </c>
+      <c r="B121" t="n">
+        <v>78732</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Abborrsjöbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>483265</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6828852</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>125747874</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Abborrsjöbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>483012</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6828723</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125755443</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125755429</v>
       </c>
       <c r="B3" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125755426</v>
       </c>
       <c r="B4" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125755529</v>
       </c>
       <c r="B5" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125755447</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125755430</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125755528</v>
       </c>
       <c r="B8" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125755409</v>
       </c>
       <c r="B9" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125755448</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755452</v>
+        <v>125755438</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>79001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483587</v>
+        <v>483600</v>
       </c>
       <c r="R11" t="n">
-        <v>6829364</v>
+        <v>6829152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755438</v>
+        <v>125755452</v>
       </c>
       <c r="B12" t="n">
-        <v>78997</v>
+        <v>78735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483600</v>
+        <v>483587</v>
       </c>
       <c r="R12" t="n">
-        <v>6829152</v>
+        <v>6829364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
         <v>125755439</v>
       </c>
       <c r="B13" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>125744833</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>125755488</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>125755475</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>125755416</v>
       </c>
       <c r="B17" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>125755421</v>
       </c>
       <c r="B18" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>125755506</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755440</v>
+        <v>125755480</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482960</v>
+        <v>482885</v>
       </c>
       <c r="R20" t="n">
-        <v>6828991</v>
+        <v>6828897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755480</v>
+        <v>125755445</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482885</v>
+        <v>482900</v>
       </c>
       <c r="R21" t="n">
-        <v>6828897</v>
+        <v>6828861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
         <v>125755494</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755445</v>
+        <v>125755440</v>
       </c>
       <c r="B23" t="n">
-        <v>80076</v>
+        <v>78736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482900</v>
+        <v>482960</v>
       </c>
       <c r="R23" t="n">
-        <v>6828861</v>
+        <v>6828991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2822,7 +2822,7 @@
         <v>125755530</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>125755513</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755428</v>
+        <v>125755516</v>
       </c>
       <c r="B26" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483280</v>
+        <v>483291</v>
       </c>
       <c r="R26" t="n">
-        <v>6828942</v>
+        <v>6828969</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
         <v>125755481</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755516</v>
+        <v>125755428</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483291</v>
+        <v>483280</v>
       </c>
       <c r="R28" t="n">
-        <v>6828969</v>
+        <v>6828942</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,32 +3304,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755460</v>
+        <v>125755502</v>
       </c>
       <c r="B29" t="n">
-        <v>91399</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482913</v>
+        <v>483078</v>
       </c>
       <c r="R29" t="n">
-        <v>6829095</v>
+        <v>6828839</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755502</v>
+        <v>125755473</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483078</v>
+        <v>483182</v>
       </c>
       <c r="R30" t="n">
-        <v>6828839</v>
+        <v>6829175</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3501,7 +3501,7 @@
         <v>125755478</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3595,32 +3595,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755473</v>
+        <v>125755460</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>91403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483182</v>
+        <v>482913</v>
       </c>
       <c r="R32" t="n">
-        <v>6829175</v>
+        <v>6829095</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3695,7 +3695,7 @@
         <v>125755411</v>
       </c>
       <c r="B33" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>125755417</v>
       </c>
       <c r="B34" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755482</v>
+        <v>125755501</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>482960</v>
+        <v>483071</v>
       </c>
       <c r="R35" t="n">
-        <v>6828769</v>
+        <v>6828833</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755501</v>
+        <v>125755464</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483071</v>
+        <v>483423</v>
       </c>
       <c r="R36" t="n">
-        <v>6828833</v>
+        <v>6829325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4083,7 +4083,7 @@
         <v>125755508</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4177,10 +4177,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755464</v>
+        <v>125755482</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483423</v>
+        <v>482960</v>
       </c>
       <c r="R38" t="n">
-        <v>6829325</v>
+        <v>6828769</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755500</v>
+        <v>125755456</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4285,21 +4285,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483068</v>
+        <v>483114</v>
       </c>
       <c r="R39" t="n">
-        <v>6828819</v>
+        <v>6828865</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755466</v>
+        <v>125755453</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483400</v>
+        <v>482979</v>
       </c>
       <c r="R40" t="n">
-        <v>6829318</v>
+        <v>6829140</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755456</v>
+        <v>125755536</v>
       </c>
       <c r="B41" t="n">
-        <v>78731</v>
+        <v>57656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,34 +4479,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483114</v>
+        <v>483037</v>
       </c>
       <c r="R41" t="n">
-        <v>6828865</v>
+        <v>6828775</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4539,6 +4544,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4565,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755510</v>
+        <v>125755466</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4600,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483191</v>
+        <v>483400</v>
       </c>
       <c r="R42" t="n">
-        <v>6828929</v>
+        <v>6829318</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4662,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755453</v>
+        <v>125755510</v>
       </c>
       <c r="B43" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4673,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4697,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>482979</v>
+        <v>483191</v>
       </c>
       <c r="R43" t="n">
-        <v>6829140</v>
+        <v>6828929</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4759,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755536</v>
+        <v>125755500</v>
       </c>
       <c r="B44" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4770,39 +4780,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483037</v>
+        <v>483068</v>
       </c>
       <c r="R44" t="n">
-        <v>6828775</v>
+        <v>6828819</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4835,11 +4840,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755483</v>
+        <v>125755442</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>482971</v>
+        <v>483201</v>
       </c>
       <c r="R45" t="n">
-        <v>6828738</v>
+        <v>6828916</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755491</v>
+        <v>125755437</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>80081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483015</v>
+        <v>483307</v>
       </c>
       <c r="R46" t="n">
-        <v>6828753</v>
+        <v>6829287</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755437</v>
+        <v>125755483</v>
       </c>
       <c r="B47" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483307</v>
+        <v>482971</v>
       </c>
       <c r="R47" t="n">
-        <v>6829287</v>
+        <v>6828738</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,32 +5157,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755458</v>
+        <v>125755491</v>
       </c>
       <c r="B48" t="n">
-        <v>58327</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483319</v>
+        <v>483015</v>
       </c>
       <c r="R48" t="n">
-        <v>6829293</v>
+        <v>6828753</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,32 +5254,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755442</v>
+        <v>125755458</v>
       </c>
       <c r="B49" t="n">
-        <v>78732</v>
+        <v>58331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>103044</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483201</v>
+        <v>483319</v>
       </c>
       <c r="R49" t="n">
-        <v>6828916</v>
+        <v>6829293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,45 +5351,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755468</v>
+        <v>125755432</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>56848</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483391</v>
+        <v>483446</v>
       </c>
       <c r="R50" t="n">
-        <v>6829308</v>
+        <v>6829026</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,50 +5453,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755432</v>
+        <v>125755498</v>
       </c>
       <c r="B51" t="n">
-        <v>56844</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483446</v>
+        <v>483071</v>
       </c>
       <c r="R51" t="n">
-        <v>6829026</v>
+        <v>6828809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755498</v>
+        <v>125755492</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R52" t="n">
-        <v>6828809</v>
+        <v>6828773</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755492</v>
+        <v>125755468</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483032</v>
+        <v>483391</v>
       </c>
       <c r="R53" t="n">
-        <v>6828773</v>
+        <v>6829308</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5747,7 +5747,7 @@
         <v>125755459</v>
       </c>
       <c r="B54" t="n">
-        <v>91252</v>
+        <v>91256</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>125755419</v>
       </c>
       <c r="B55" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755463</v>
+        <v>125755496</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483450</v>
+        <v>483054</v>
       </c>
       <c r="R56" t="n">
-        <v>6829306</v>
+        <v>6828788</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6035,10 +6035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755496</v>
+        <v>125755463</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483054</v>
+        <v>483450</v>
       </c>
       <c r="R57" t="n">
-        <v>6828788</v>
+        <v>6829306</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6132,10 +6132,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755533</v>
+        <v>125755525</v>
       </c>
       <c r="B58" t="n">
-        <v>78379</v>
+        <v>78644</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483472</v>
+        <v>483442</v>
       </c>
       <c r="R58" t="n">
-        <v>6829305</v>
+        <v>6829028</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6229,45 +6229,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755517</v>
+        <v>125755431</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>56848</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483386</v>
+        <v>483099</v>
       </c>
       <c r="R59" t="n">
-        <v>6829003</v>
+        <v>6828858</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6326,50 +6331,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755431</v>
+        <v>125755433</v>
       </c>
       <c r="B60" t="n">
-        <v>56844</v>
+        <v>57816</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483099</v>
+        <v>483307</v>
       </c>
       <c r="R60" t="n">
-        <v>6828858</v>
+        <v>6829287</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,10 +6428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755525</v>
+        <v>125755533</v>
       </c>
       <c r="B61" t="n">
-        <v>78640</v>
+        <v>78383</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6439,21 +6439,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483442</v>
+        <v>483472</v>
       </c>
       <c r="R61" t="n">
-        <v>6829028</v>
+        <v>6829305</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6525,10 +6525,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755433</v>
+        <v>125755517</v>
       </c>
       <c r="B62" t="n">
-        <v>57812</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6536,21 +6536,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6560,10 +6560,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483307</v>
+        <v>483386</v>
       </c>
       <c r="R62" t="n">
-        <v>6829287</v>
+        <v>6829003</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6625,7 +6625,7 @@
         <v>125755441</v>
       </c>
       <c r="B63" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6719,10 +6719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755489</v>
+        <v>125755424</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6730,21 +6730,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483001</v>
+        <v>483162</v>
       </c>
       <c r="R64" t="n">
-        <v>6828740</v>
+        <v>6828879</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6819,7 +6819,7 @@
         <v>125755472</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>125755451</v>
       </c>
       <c r="B66" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7010,10 +7010,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755424</v>
+        <v>125755412</v>
       </c>
       <c r="B67" t="n">
-        <v>79005</v>
+        <v>79595</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7021,21 +7021,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483162</v>
+        <v>482912</v>
       </c>
       <c r="R67" t="n">
-        <v>6828879</v>
+        <v>6828922</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755412</v>
+        <v>125755489</v>
       </c>
       <c r="B68" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7118,21 +7118,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>482912</v>
+        <v>483001</v>
       </c>
       <c r="R68" t="n">
-        <v>6828922</v>
+        <v>6828740</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7207,7 +7207,7 @@
         <v>125755522</v>
       </c>
       <c r="B69" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>125755515</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755474</v>
+        <v>125755514</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483188</v>
+        <v>483220</v>
       </c>
       <c r="R71" t="n">
-        <v>6829143</v>
+        <v>6828907</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7495,10 +7495,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755514</v>
+        <v>125755518</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483220</v>
+        <v>483467</v>
       </c>
       <c r="R72" t="n">
-        <v>6828907</v>
+        <v>6829027</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7592,10 +7592,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755518</v>
+        <v>125755503</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483467</v>
+        <v>483095</v>
       </c>
       <c r="R73" t="n">
-        <v>6829027</v>
+        <v>6828845</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755503</v>
+        <v>125755474</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483095</v>
+        <v>483188</v>
       </c>
       <c r="R74" t="n">
-        <v>6828845</v>
+        <v>6829143</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7789,7 +7789,7 @@
         <v>125755418</v>
       </c>
       <c r="B75" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755512</v>
+        <v>125755414</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7894,21 +7894,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483190</v>
+        <v>483240</v>
       </c>
       <c r="R76" t="n">
-        <v>6828942</v>
+        <v>6828921</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7983,7 +7983,7 @@
         <v>125755504</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8077,10 +8077,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755479</v>
+        <v>125755512</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>482918</v>
+        <v>483190</v>
       </c>
       <c r="R78" t="n">
-        <v>6828932</v>
+        <v>6828942</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8177,7 +8177,7 @@
         <v>125755511</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>125755484</v>
       </c>
       <c r="B80" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8368,10 +8368,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755414</v>
+        <v>125755479</v>
       </c>
       <c r="B81" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8379,21 +8379,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483240</v>
+        <v>482918</v>
       </c>
       <c r="R81" t="n">
-        <v>6828921</v>
+        <v>6828932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8465,32 +8465,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755520</v>
+        <v>125755526</v>
       </c>
       <c r="B82" t="n">
-        <v>92528</v>
+        <v>78644</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483458</v>
+        <v>483499</v>
       </c>
       <c r="R82" t="n">
-        <v>6829089</v>
+        <v>6829120</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8562,10 +8562,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755526</v>
+        <v>125755493</v>
       </c>
       <c r="B83" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8573,21 +8573,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483499</v>
+        <v>483037</v>
       </c>
       <c r="R83" t="n">
-        <v>6829120</v>
+        <v>6828788</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8659,10 +8659,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755469</v>
+        <v>125755446</v>
       </c>
       <c r="B84" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8670,21 +8670,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483342</v>
+        <v>482885</v>
       </c>
       <c r="R84" t="n">
-        <v>6829286</v>
+        <v>6828845</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8756,10 +8756,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755493</v>
+        <v>125755413</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8767,21 +8767,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483037</v>
+        <v>482962</v>
       </c>
       <c r="R85" t="n">
-        <v>6828788</v>
+        <v>6828771</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8853,10 +8853,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755413</v>
+        <v>125755444</v>
       </c>
       <c r="B86" t="n">
-        <v>79591</v>
+        <v>80080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8864,21 +8864,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>482962</v>
+        <v>483272</v>
       </c>
       <c r="R86" t="n">
-        <v>6828771</v>
+        <v>6829286</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8950,10 +8950,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755444</v>
+        <v>125755469</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8961,21 +8961,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483272</v>
+        <v>483342</v>
       </c>
       <c r="R87" t="n">
         <v>6829286</v>
@@ -9047,32 +9047,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755446</v>
+        <v>125755520</v>
       </c>
       <c r="B88" t="n">
-        <v>80076</v>
+        <v>92532</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9082,10 +9082,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482885</v>
+        <v>483458</v>
       </c>
       <c r="R88" t="n">
-        <v>6828845</v>
+        <v>6829089</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9147,7 +9147,7 @@
         <v>125755435</v>
       </c>
       <c r="B89" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>125755422</v>
       </c>
       <c r="B90" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>125755507</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>125755415</v>
       </c>
       <c r="B92" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9532,10 +9532,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755485</v>
+        <v>125755497</v>
       </c>
       <c r="B93" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483002</v>
+        <v>483063</v>
       </c>
       <c r="R93" t="n">
-        <v>6828695</v>
+        <v>6828803</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9632,7 +9632,7 @@
         <v>125755490</v>
       </c>
       <c r="B94" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9726,10 +9726,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755497</v>
+        <v>125755485</v>
       </c>
       <c r="B95" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483063</v>
+        <v>483002</v>
       </c>
       <c r="R95" t="n">
-        <v>6828803</v>
+        <v>6828695</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9826,7 +9826,7 @@
         <v>125755523</v>
       </c>
       <c r="B96" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>125755455</v>
       </c>
       <c r="B97" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>125755532</v>
       </c>
       <c r="B98" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10114,32 +10114,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755471</v>
+        <v>125755436</v>
       </c>
       <c r="B99" t="n">
-        <v>78973</v>
+        <v>80109</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R99" t="n">
-        <v>6829193</v>
+        <v>6829290</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10214,7 +10214,7 @@
         <v>125755486</v>
       </c>
       <c r="B100" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10308,32 +10308,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755436</v>
+        <v>125755471</v>
       </c>
       <c r="B101" t="n">
-        <v>80105</v>
+        <v>78977</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R101" t="n">
-        <v>6829290</v>
+        <v>6829193</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10408,7 +10408,7 @@
         <v>125755457</v>
       </c>
       <c r="B102" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>125755427</v>
       </c>
       <c r="B103" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>125755462</v>
       </c>
       <c r="B104" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>125691576</v>
       </c>
       <c r="B105" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125745158</v>
+        <v>125746064</v>
       </c>
       <c r="B106" t="n">
-        <v>57649</v>
+        <v>78977</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10823,45 +10823,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483359</v>
+        <v>483474</v>
       </c>
       <c r="R106" t="n">
-        <v>6829093</v>
+        <v>6829119</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10920,7 +10912,7 @@
         <v>125746931</v>
       </c>
       <c r="B107" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11019,10 +11011,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125746064</v>
+        <v>125745158</v>
       </c>
       <c r="B108" t="n">
-        <v>78973</v>
+        <v>57653</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11030,37 +11022,45 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483474</v>
+        <v>483359</v>
       </c>
       <c r="R108" t="n">
-        <v>6829119</v>
+        <v>6829093</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>125745798</v>
       </c>
       <c r="B109" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>125747349</v>
       </c>
       <c r="B110" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>125745325</v>
       </c>
       <c r="B111" t="n">
-        <v>91399</v>
+        <v>91403</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>125744923</v>
       </c>
       <c r="B112" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11512,10 +11512,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125746848</v>
+        <v>125747249</v>
       </c>
       <c r="B113" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483247</v>
+        <v>483032</v>
       </c>
       <c r="R113" t="n">
-        <v>6828848</v>
+        <v>6828658</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11583,6 +11583,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11609,10 +11614,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125748935</v>
+        <v>125747099</v>
       </c>
       <c r="B114" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11620,21 +11625,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11644,10 +11649,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483071</v>
+        <v>483090</v>
       </c>
       <c r="R114" t="n">
-        <v>6828797</v>
+        <v>6828658</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11706,10 +11711,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125747249</v>
+        <v>125746848</v>
       </c>
       <c r="B115" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11741,10 +11746,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483032</v>
+        <v>483247</v>
       </c>
       <c r="R115" t="n">
-        <v>6828658</v>
+        <v>6828848</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11777,11 +11782,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11808,10 +11808,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125747099</v>
+        <v>125748935</v>
       </c>
       <c r="B116" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11819,21 +11819,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11843,10 +11843,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483090</v>
+        <v>483071</v>
       </c>
       <c r="R116" t="n">
-        <v>6828658</v>
+        <v>6828797</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11908,7 +11908,7 @@
         <v>125746158</v>
       </c>
       <c r="B117" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>125748016</v>
       </c>
       <c r="B118" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>125747880</v>
       </c>
       <c r="B119" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>125746359</v>
       </c>
       <c r="B120" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>125746396</v>
       </c>
       <c r="B121" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>125747874</v>
       </c>
       <c r="B122" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755421</v>
+        <v>125755506</v>
       </c>
       <c r="B18" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483044</v>
+        <v>483162</v>
       </c>
       <c r="R18" t="n">
-        <v>6828792</v>
+        <v>6828887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755506</v>
+        <v>125755480</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483162</v>
+        <v>482885</v>
       </c>
       <c r="R19" t="n">
-        <v>6828887</v>
+        <v>6828897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755480</v>
+        <v>125755445</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482885</v>
+        <v>482900</v>
       </c>
       <c r="R20" t="n">
-        <v>6828897</v>
+        <v>6828861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755445</v>
+        <v>125755494</v>
       </c>
       <c r="B21" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482900</v>
+        <v>483047</v>
       </c>
       <c r="R21" t="n">
-        <v>6828861</v>
+        <v>6828790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755494</v>
+        <v>125755421</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483047</v>
+        <v>483044</v>
       </c>
       <c r="R22" t="n">
-        <v>6828790</v>
+        <v>6828792</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755442</v>
+        <v>125755437</v>
       </c>
       <c r="B45" t="n">
-        <v>78736</v>
+        <v>80081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483201</v>
+        <v>483307</v>
       </c>
       <c r="R45" t="n">
-        <v>6828916</v>
+        <v>6829287</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755437</v>
+        <v>125755491</v>
       </c>
       <c r="B46" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483307</v>
+        <v>483015</v>
       </c>
       <c r="R46" t="n">
-        <v>6829287</v>
+        <v>6828753</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5157,32 +5157,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755491</v>
+        <v>125755458</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>58331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483015</v>
+        <v>483319</v>
       </c>
       <c r="R48" t="n">
-        <v>6828753</v>
+        <v>6829293</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,32 +5254,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755458</v>
+        <v>125755442</v>
       </c>
       <c r="B49" t="n">
-        <v>58331</v>
+        <v>78736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103044</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483319</v>
+        <v>483201</v>
       </c>
       <c r="R49" t="n">
-        <v>6829293</v>
+        <v>6828916</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755459</v>
+        <v>125755419</v>
       </c>
       <c r="B54" t="n">
-        <v>91256</v>
+        <v>79009</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5755,21 +5755,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483398</v>
+        <v>483005</v>
       </c>
       <c r="R54" t="n">
-        <v>6829316</v>
+        <v>6828754</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755419</v>
+        <v>125755496</v>
       </c>
       <c r="B55" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483005</v>
+        <v>483054</v>
       </c>
       <c r="R55" t="n">
-        <v>6828754</v>
+        <v>6828788</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5938,7 +5938,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755496</v>
+        <v>125755463</v>
       </c>
       <c r="B56" t="n">
         <v>78977</v>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483054</v>
+        <v>483450</v>
       </c>
       <c r="R56" t="n">
-        <v>6828788</v>
+        <v>6829306</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6035,10 +6035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755463</v>
+        <v>125755459</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>91256</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6046,21 +6046,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483450</v>
+        <v>483398</v>
       </c>
       <c r="R57" t="n">
-        <v>6829306</v>
+        <v>6829316</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6719,10 +6719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755424</v>
+        <v>125755412</v>
       </c>
       <c r="B64" t="n">
-        <v>79009</v>
+        <v>79595</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6730,21 +6730,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483162</v>
+        <v>482912</v>
       </c>
       <c r="R64" t="n">
-        <v>6828879</v>
+        <v>6828922</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6816,10 +6816,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755472</v>
+        <v>125755424</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6827,21 +6827,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483203</v>
+        <v>483162</v>
       </c>
       <c r="R65" t="n">
-        <v>6829189</v>
+        <v>6828879</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6913,10 +6913,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755451</v>
+        <v>125755472</v>
       </c>
       <c r="B66" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483278</v>
+        <v>483203</v>
       </c>
       <c r="R66" t="n">
-        <v>6828932</v>
+        <v>6829189</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7010,10 +7010,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755412</v>
+        <v>125755451</v>
       </c>
       <c r="B67" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7021,21 +7021,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>482912</v>
+        <v>483278</v>
       </c>
       <c r="R67" t="n">
-        <v>6828922</v>
+        <v>6828932</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7786,10 +7786,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755418</v>
+        <v>125755511</v>
       </c>
       <c r="B75" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7797,21 +7797,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>482886</v>
+        <v>483188</v>
       </c>
       <c r="R75" t="n">
-        <v>6828895</v>
+        <v>6828936</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7883,10 +7883,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755414</v>
+        <v>125755484</v>
       </c>
       <c r="B76" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7894,21 +7894,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483240</v>
+        <v>482976</v>
       </c>
       <c r="R76" t="n">
-        <v>6828921</v>
+        <v>6828720</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755504</v>
+        <v>125755479</v>
       </c>
       <c r="B77" t="n">
         <v>78977</v>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483117</v>
+        <v>482918</v>
       </c>
       <c r="R77" t="n">
-        <v>6828857</v>
+        <v>6828932</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8077,10 +8077,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755512</v>
+        <v>125755418</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483190</v>
+        <v>482886</v>
       </c>
       <c r="R78" t="n">
-        <v>6828942</v>
+        <v>6828895</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8174,7 +8174,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755511</v>
+        <v>125755504</v>
       </c>
       <c r="B79" t="n">
         <v>78977</v>
@@ -8209,10 +8209,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483188</v>
+        <v>483117</v>
       </c>
       <c r="R79" t="n">
-        <v>6828936</v>
+        <v>6828857</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8271,10 +8271,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755484</v>
+        <v>125755414</v>
       </c>
       <c r="B80" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8306,10 +8306,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>482976</v>
+        <v>483240</v>
       </c>
       <c r="R80" t="n">
-        <v>6828720</v>
+        <v>6828921</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755479</v>
+        <v>125755512</v>
       </c>
       <c r="B81" t="n">
         <v>78977</v>
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>482918</v>
+        <v>483190</v>
       </c>
       <c r="R81" t="n">
-        <v>6828932</v>
+        <v>6828942</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8562,7 +8562,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755493</v>
+        <v>125755469</v>
       </c>
       <c r="B83" t="n">
         <v>78977</v>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483037</v>
+        <v>483342</v>
       </c>
       <c r="R83" t="n">
-        <v>6828788</v>
+        <v>6829286</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8659,32 +8659,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755446</v>
+        <v>125755520</v>
       </c>
       <c r="B84" t="n">
-        <v>80080</v>
+        <v>92532</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>482885</v>
+        <v>483458</v>
       </c>
       <c r="R84" t="n">
-        <v>6828845</v>
+        <v>6829089</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8756,10 +8756,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755413</v>
+        <v>125755493</v>
       </c>
       <c r="B85" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8767,21 +8767,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>482962</v>
+        <v>483037</v>
       </c>
       <c r="R85" t="n">
-        <v>6828771</v>
+        <v>6828788</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8853,7 +8853,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755444</v>
+        <v>125755446</v>
       </c>
       <c r="B86" t="n">
         <v>80080</v>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483272</v>
+        <v>482885</v>
       </c>
       <c r="R86" t="n">
-        <v>6829286</v>
+        <v>6828845</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8950,10 +8950,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755469</v>
+        <v>125755413</v>
       </c>
       <c r="B87" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8961,21 +8961,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483342</v>
+        <v>482962</v>
       </c>
       <c r="R87" t="n">
-        <v>6829286</v>
+        <v>6828771</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9047,32 +9047,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755520</v>
+        <v>125755444</v>
       </c>
       <c r="B88" t="n">
-        <v>92532</v>
+        <v>80080</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9082,10 +9082,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483458</v>
+        <v>483272</v>
       </c>
       <c r="R88" t="n">
-        <v>6829089</v>
+        <v>6829286</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10114,32 +10114,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755436</v>
+        <v>125755427</v>
       </c>
       <c r="B99" t="n">
-        <v>80109</v>
+        <v>79566</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483303</v>
+        <v>483472</v>
       </c>
       <c r="R99" t="n">
-        <v>6829290</v>
+        <v>6829305</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10211,32 +10211,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755486</v>
+        <v>125755436</v>
       </c>
       <c r="B100" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483015</v>
+        <v>483303</v>
       </c>
       <c r="R100" t="n">
-        <v>6828711</v>
+        <v>6829290</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10308,7 +10308,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755471</v>
+        <v>125755486</v>
       </c>
       <c r="B101" t="n">
         <v>78977</v>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483206</v>
+        <v>483015</v>
       </c>
       <c r="R101" t="n">
-        <v>6829193</v>
+        <v>6828711</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10405,10 +10405,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755457</v>
+        <v>125755471</v>
       </c>
       <c r="B102" t="n">
-        <v>56839</v>
+        <v>78977</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10416,39 +10416,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483040</v>
+        <v>483206</v>
       </c>
       <c r="R102" t="n">
-        <v>6828774</v>
+        <v>6829193</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10507,10 +10502,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755427</v>
+        <v>125755457</v>
       </c>
       <c r="B103" t="n">
-        <v>79566</v>
+        <v>56839</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10518,34 +10513,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483472</v>
+        <v>483040</v>
       </c>
       <c r="R103" t="n">
-        <v>6829305</v>
+        <v>6828774</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11512,10 +11512,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125747249</v>
+        <v>125748935</v>
       </c>
       <c r="B113" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R113" t="n">
-        <v>6828658</v>
+        <v>6828797</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11583,11 +11583,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11614,7 +11609,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125747099</v>
+        <v>125747249</v>
       </c>
       <c r="B114" t="n">
         <v>78977</v>
@@ -11649,7 +11644,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483090</v>
+        <v>483032</v>
       </c>
       <c r="R114" t="n">
         <v>6828658</v>
@@ -11685,6 +11680,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11711,7 +11711,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125746848</v>
+        <v>125747099</v>
       </c>
       <c r="B115" t="n">
         <v>78977</v>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483247</v>
+        <v>483090</v>
       </c>
       <c r="R115" t="n">
-        <v>6828848</v>
+        <v>6828658</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11808,10 +11808,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125748935</v>
+        <v>125746848</v>
       </c>
       <c r="B116" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11819,21 +11819,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11843,10 +11843,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483071</v>
+        <v>483247</v>
       </c>
       <c r="R116" t="n">
-        <v>6828797</v>
+        <v>6828848</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12298,10 +12298,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125746396</v>
+        <v>125747874</v>
       </c>
       <c r="B121" t="n">
-        <v>78736</v>
+        <v>57656</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12309,34 +12309,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>483265</v>
+        <v>483012</v>
       </c>
       <c r="R121" t="n">
-        <v>6828852</v>
+        <v>6828723</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12395,10 +12400,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125747874</v>
+        <v>125746396</v>
       </c>
       <c r="B122" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12406,39 +12411,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>483012</v>
+        <v>483265</v>
       </c>
       <c r="R122" t="n">
-        <v>6828723</v>
+        <v>6828852</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755438</v>
+        <v>125755452</v>
       </c>
       <c r="B11" t="n">
-        <v>79001</v>
+        <v>78735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483600</v>
+        <v>483587</v>
       </c>
       <c r="R11" t="n">
-        <v>6829152</v>
+        <v>6829364</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755452</v>
+        <v>125755438</v>
       </c>
       <c r="B12" t="n">
-        <v>78735</v>
+        <v>79001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483587</v>
+        <v>483600</v>
       </c>
       <c r="R12" t="n">
-        <v>6829364</v>
+        <v>6829152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755506</v>
+        <v>125755445</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483162</v>
+        <v>482900</v>
       </c>
       <c r="R18" t="n">
-        <v>6828887</v>
+        <v>6828861</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755480</v>
+        <v>125755440</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482885</v>
+        <v>482960</v>
       </c>
       <c r="R19" t="n">
-        <v>6828897</v>
+        <v>6828991</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755445</v>
+        <v>125755421</v>
       </c>
       <c r="B20" t="n">
-        <v>80080</v>
+        <v>79009</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482900</v>
+        <v>483044</v>
       </c>
       <c r="R20" t="n">
-        <v>6828861</v>
+        <v>6828792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755494</v>
+        <v>125755506</v>
       </c>
       <c r="B21" t="n">
         <v>78977</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483047</v>
+        <v>483162</v>
       </c>
       <c r="R21" t="n">
-        <v>6828790</v>
+        <v>6828887</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755421</v>
+        <v>125755480</v>
       </c>
       <c r="B22" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483044</v>
+        <v>482885</v>
       </c>
       <c r="R22" t="n">
-        <v>6828792</v>
+        <v>6828897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755440</v>
+        <v>125755494</v>
       </c>
       <c r="B23" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482960</v>
+        <v>483047</v>
       </c>
       <c r="R23" t="n">
-        <v>6828991</v>
+        <v>6828790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,27 +2819,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755530</v>
+        <v>125755513</v>
       </c>
       <c r="B24" t="n">
-        <v>80115</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R24" t="n">
-        <v>6829288</v>
+        <v>6828917</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,27 +2916,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755513</v>
+        <v>125755530</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R25" t="n">
-        <v>6828917</v>
+        <v>6829288</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755516</v>
+        <v>125755428</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483291</v>
+        <v>483280</v>
       </c>
       <c r="R26" t="n">
-        <v>6828969</v>
+        <v>6828942</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755481</v>
+        <v>125755516</v>
       </c>
       <c r="B27" t="n">
         <v>78977</v>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482929</v>
+        <v>483291</v>
       </c>
       <c r="R27" t="n">
-        <v>6828797</v>
+        <v>6828969</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755428</v>
+        <v>125755481</v>
       </c>
       <c r="B28" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483280</v>
+        <v>482929</v>
       </c>
       <c r="R28" t="n">
-        <v>6828942</v>
+        <v>6828797</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3498,32 +3498,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755478</v>
+        <v>125755460</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>91403</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483147</v>
+        <v>482913</v>
       </c>
       <c r="R31" t="n">
         <v>6829095</v>
@@ -3595,32 +3595,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755460</v>
+        <v>125755478</v>
       </c>
       <c r="B32" t="n">
-        <v>91403</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>482913</v>
+        <v>483147</v>
       </c>
       <c r="R32" t="n">
         <v>6829095</v>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755456</v>
+        <v>125755466</v>
       </c>
       <c r="B39" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4285,21 +4285,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483114</v>
+        <v>483400</v>
       </c>
       <c r="R39" t="n">
-        <v>6828865</v>
+        <v>6829318</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755453</v>
+        <v>125755456</v>
       </c>
       <c r="B40" t="n">
         <v>78735</v>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>482979</v>
+        <v>483114</v>
       </c>
       <c r="R40" t="n">
-        <v>6829140</v>
+        <v>6828865</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755536</v>
+        <v>125755510</v>
       </c>
       <c r="B41" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,39 +4479,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483037</v>
+        <v>483191</v>
       </c>
       <c r="R41" t="n">
-        <v>6828775</v>
+        <v>6828929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,11 +4539,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4565,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755466</v>
+        <v>125755453</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4576,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4600,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483400</v>
+        <v>482979</v>
       </c>
       <c r="R42" t="n">
-        <v>6829318</v>
+        <v>6829140</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,7 +4662,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755510</v>
+        <v>125755500</v>
       </c>
       <c r="B43" t="n">
         <v>78977</v>
@@ -4707,10 +4697,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483191</v>
+        <v>483068</v>
       </c>
       <c r="R43" t="n">
-        <v>6828929</v>
+        <v>6828819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,10 +4759,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755500</v>
+        <v>125755536</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,34 +4770,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483068</v>
+        <v>483037</v>
       </c>
       <c r="R44" t="n">
-        <v>6828819</v>
+        <v>6828775</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4840,6 +4835,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755437</v>
+        <v>125755483</v>
       </c>
       <c r="B45" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483307</v>
+        <v>482971</v>
       </c>
       <c r="R45" t="n">
-        <v>6829287</v>
+        <v>6828738</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755491</v>
+        <v>125755437</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483015</v>
+        <v>483307</v>
       </c>
       <c r="R46" t="n">
-        <v>6828753</v>
+        <v>6829287</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755483</v>
+        <v>125755491</v>
       </c>
       <c r="B47" t="n">
         <v>78977</v>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>482971</v>
+        <v>483015</v>
       </c>
       <c r="R47" t="n">
-        <v>6828738</v>
+        <v>6828753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,50 +5351,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755432</v>
+        <v>125755492</v>
       </c>
       <c r="B50" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483446</v>
+        <v>483032</v>
       </c>
       <c r="R50" t="n">
-        <v>6829026</v>
+        <v>6828773</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,7 +5545,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755492</v>
+        <v>125755468</v>
       </c>
       <c r="B52" t="n">
         <v>78977</v>
@@ -5585,10 +5580,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483032</v>
+        <v>483391</v>
       </c>
       <c r="R52" t="n">
-        <v>6828773</v>
+        <v>6829308</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5647,45 +5642,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755468</v>
+        <v>125755432</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483391</v>
+        <v>483446</v>
       </c>
       <c r="R53" t="n">
-        <v>6829308</v>
+        <v>6829026</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755419</v>
+        <v>125755496</v>
       </c>
       <c r="B54" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5755,21 +5755,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483005</v>
+        <v>483054</v>
       </c>
       <c r="R54" t="n">
-        <v>6828754</v>
+        <v>6828788</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755496</v>
+        <v>125755463</v>
       </c>
       <c r="B55" t="n">
         <v>78977</v>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483054</v>
+        <v>483450</v>
       </c>
       <c r="R55" t="n">
-        <v>6828788</v>
+        <v>6829306</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755463</v>
+        <v>125755459</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>91256</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483450</v>
+        <v>483398</v>
       </c>
       <c r="R56" t="n">
-        <v>6829306</v>
+        <v>6829316</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6035,10 +6035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755459</v>
+        <v>125755419</v>
       </c>
       <c r="B57" t="n">
-        <v>91256</v>
+        <v>79009</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6046,21 +6046,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483398</v>
+        <v>483005</v>
       </c>
       <c r="R57" t="n">
-        <v>6829316</v>
+        <v>6828754</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755433</v>
+        <v>125755533</v>
       </c>
       <c r="B60" t="n">
-        <v>57816</v>
+        <v>78383</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483307</v>
+        <v>483472</v>
       </c>
       <c r="R60" t="n">
-        <v>6829287</v>
+        <v>6829305</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,10 +6428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755533</v>
+        <v>125755517</v>
       </c>
       <c r="B61" t="n">
-        <v>78383</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6439,21 +6439,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483472</v>
+        <v>483386</v>
       </c>
       <c r="R61" t="n">
-        <v>6829305</v>
+        <v>6829003</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6525,10 +6525,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755517</v>
+        <v>125755433</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6536,21 +6536,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6560,10 +6560,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483386</v>
+        <v>483307</v>
       </c>
       <c r="R62" t="n">
-        <v>6829003</v>
+        <v>6829287</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6622,10 +6622,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755441</v>
+        <v>125755424</v>
       </c>
       <c r="B63" t="n">
-        <v>78736</v>
+        <v>79009</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6633,21 +6633,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483114</v>
+        <v>483162</v>
       </c>
       <c r="R63" t="n">
-        <v>6828865</v>
+        <v>6828879</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6719,10 +6719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755412</v>
+        <v>125755472</v>
       </c>
       <c r="B64" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6730,21 +6730,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>482912</v>
+        <v>483203</v>
       </c>
       <c r="R64" t="n">
-        <v>6828922</v>
+        <v>6829189</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6816,10 +6816,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755424</v>
+        <v>125755489</v>
       </c>
       <c r="B65" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6827,21 +6827,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483162</v>
+        <v>483001</v>
       </c>
       <c r="R65" t="n">
-        <v>6828879</v>
+        <v>6828740</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6913,10 +6913,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755472</v>
+        <v>125755451</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483203</v>
+        <v>483278</v>
       </c>
       <c r="R66" t="n">
-        <v>6829189</v>
+        <v>6828932</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7010,10 +7010,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755451</v>
+        <v>125755412</v>
       </c>
       <c r="B67" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7021,21 +7021,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483278</v>
+        <v>482912</v>
       </c>
       <c r="R67" t="n">
-        <v>6828932</v>
+        <v>6828922</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755489</v>
+        <v>125755441</v>
       </c>
       <c r="B68" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7118,21 +7118,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483001</v>
+        <v>483114</v>
       </c>
       <c r="R68" t="n">
-        <v>6828740</v>
+        <v>6828865</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7786,10 +7786,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755511</v>
+        <v>125755414</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7797,21 +7797,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483188</v>
+        <v>483240</v>
       </c>
       <c r="R75" t="n">
-        <v>6828936</v>
+        <v>6828921</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7883,10 +7883,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755484</v>
+        <v>125755418</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7894,21 +7894,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>482976</v>
+        <v>482886</v>
       </c>
       <c r="R76" t="n">
-        <v>6828720</v>
+        <v>6828895</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755479</v>
+        <v>125755511</v>
       </c>
       <c r="B77" t="n">
         <v>78977</v>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>482918</v>
+        <v>483188</v>
       </c>
       <c r="R77" t="n">
-        <v>6828932</v>
+        <v>6828936</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8077,10 +8077,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755418</v>
+        <v>125755504</v>
       </c>
       <c r="B78" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>482886</v>
+        <v>483117</v>
       </c>
       <c r="R78" t="n">
-        <v>6828895</v>
+        <v>6828857</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8174,7 +8174,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755504</v>
+        <v>125755484</v>
       </c>
       <c r="B79" t="n">
         <v>78977</v>
@@ -8209,10 +8209,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483117</v>
+        <v>482976</v>
       </c>
       <c r="R79" t="n">
-        <v>6828857</v>
+        <v>6828720</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8271,10 +8271,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755414</v>
+        <v>125755479</v>
       </c>
       <c r="B80" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8306,10 +8306,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483240</v>
+        <v>482918</v>
       </c>
       <c r="R80" t="n">
-        <v>6828921</v>
+        <v>6828932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8465,10 +8465,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755526</v>
+        <v>125755435</v>
       </c>
       <c r="B82" t="n">
-        <v>78644</v>
+        <v>58135</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8476,21 +8476,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>103018</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483499</v>
+        <v>483450</v>
       </c>
       <c r="R82" t="n">
-        <v>6829120</v>
+        <v>6829302</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8562,10 +8562,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755469</v>
+        <v>125755526</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8573,21 +8573,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483342</v>
+        <v>483499</v>
       </c>
       <c r="R83" t="n">
-        <v>6829286</v>
+        <v>6829120</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8659,32 +8659,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755520</v>
+        <v>125755469</v>
       </c>
       <c r="B84" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483458</v>
+        <v>483342</v>
       </c>
       <c r="R84" t="n">
-        <v>6829089</v>
+        <v>6829286</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8853,32 +8853,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755446</v>
+        <v>125755520</v>
       </c>
       <c r="B86" t="n">
-        <v>80080</v>
+        <v>92532</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>482885</v>
+        <v>483458</v>
       </c>
       <c r="R86" t="n">
-        <v>6828845</v>
+        <v>6829089</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8950,10 +8950,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755413</v>
+        <v>125755446</v>
       </c>
       <c r="B87" t="n">
-        <v>79595</v>
+        <v>80080</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8961,21 +8961,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>482962</v>
+        <v>482885</v>
       </c>
       <c r="R87" t="n">
-        <v>6828771</v>
+        <v>6828845</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9047,10 +9047,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755444</v>
+        <v>125755413</v>
       </c>
       <c r="B88" t="n">
-        <v>80080</v>
+        <v>79595</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9058,21 +9058,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9082,10 +9082,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483272</v>
+        <v>482962</v>
       </c>
       <c r="R88" t="n">
-        <v>6829286</v>
+        <v>6828771</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9144,10 +9144,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755435</v>
+        <v>125755444</v>
       </c>
       <c r="B89" t="n">
-        <v>58135</v>
+        <v>80080</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9155,21 +9155,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9179,10 +9179,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483450</v>
+        <v>483272</v>
       </c>
       <c r="R89" t="n">
-        <v>6829302</v>
+        <v>6829286</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755427</v>
+        <v>125755457</v>
       </c>
       <c r="B99" t="n">
-        <v>79566</v>
+        <v>56839</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10125,34 +10125,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>102612</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483472</v>
+        <v>483040</v>
       </c>
       <c r="R99" t="n">
-        <v>6829305</v>
+        <v>6828774</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10211,32 +10216,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755436</v>
+        <v>125755427</v>
       </c>
       <c r="B100" t="n">
-        <v>80109</v>
+        <v>79566</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10246,10 +10251,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483303</v>
+        <v>483472</v>
       </c>
       <c r="R100" t="n">
-        <v>6829290</v>
+        <v>6829305</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10502,50 +10507,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755457</v>
+        <v>125755436</v>
       </c>
       <c r="B103" t="n">
-        <v>56839</v>
+        <v>80109</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483040</v>
+        <v>483303</v>
       </c>
       <c r="R103" t="n">
-        <v>6828774</v>
+        <v>6829290</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10812,10 +10812,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125746064</v>
+        <v>125745158</v>
       </c>
       <c r="B106" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10823,37 +10823,45 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483474</v>
+        <v>483359</v>
       </c>
       <c r="R106" t="n">
-        <v>6829119</v>
+        <v>6829093</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10909,7 +10917,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125746931</v>
+        <v>125746064</v>
       </c>
       <c r="B107" t="n">
         <v>78977</v>
@@ -10940,14 +10948,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483156</v>
+        <v>483474</v>
       </c>
       <c r="R107" t="n">
-        <v>6828728</v>
+        <v>6829119</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10980,11 +10988,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11011,10 +11014,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125745158</v>
+        <v>125746931</v>
       </c>
       <c r="B108" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11022,45 +11025,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483359</v>
+        <v>483156</v>
       </c>
       <c r="R108" t="n">
-        <v>6829093</v>
+        <v>6828728</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11090,6 +11085,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11512,10 +11512,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125748935</v>
+        <v>125747249</v>
       </c>
       <c r="B113" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R113" t="n">
-        <v>6828797</v>
+        <v>6828658</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11583,6 +11583,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11609,7 +11614,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125747249</v>
+        <v>125747099</v>
       </c>
       <c r="B114" t="n">
         <v>78977</v>
@@ -11644,7 +11649,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483032</v>
+        <v>483090</v>
       </c>
       <c r="R114" t="n">
         <v>6828658</v>
@@ -11680,11 +11685,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11711,7 +11711,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125747099</v>
+        <v>125746848</v>
       </c>
       <c r="B115" t="n">
         <v>78977</v>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483090</v>
+        <v>483247</v>
       </c>
       <c r="R115" t="n">
-        <v>6828658</v>
+        <v>6828848</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11808,10 +11808,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125746848</v>
+        <v>125748935</v>
       </c>
       <c r="B116" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11819,21 +11819,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11843,10 +11843,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483247</v>
+        <v>483071</v>
       </c>
       <c r="R116" t="n">
-        <v>6828848</v>
+        <v>6828797</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755445</v>
+        <v>125755506</v>
       </c>
       <c r="B18" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482900</v>
+        <v>483162</v>
       </c>
       <c r="R18" t="n">
-        <v>6828861</v>
+        <v>6828887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755440</v>
+        <v>125755480</v>
       </c>
       <c r="B19" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482960</v>
+        <v>482885</v>
       </c>
       <c r="R19" t="n">
-        <v>6828991</v>
+        <v>6828897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755421</v>
+        <v>125755494</v>
       </c>
       <c r="B20" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483044</v>
+        <v>483047</v>
       </c>
       <c r="R20" t="n">
-        <v>6828792</v>
+        <v>6828790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755506</v>
+        <v>125755445</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483162</v>
+        <v>482900</v>
       </c>
       <c r="R21" t="n">
-        <v>6828887</v>
+        <v>6828861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755480</v>
+        <v>125755421</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482885</v>
+        <v>483044</v>
       </c>
       <c r="R22" t="n">
-        <v>6828897</v>
+        <v>6828792</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755494</v>
+        <v>125755440</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483047</v>
+        <v>482960</v>
       </c>
       <c r="R23" t="n">
-        <v>6828790</v>
+        <v>6828991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,27 +2819,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755513</v>
+        <v>125755530</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483206</v>
+        <v>483303</v>
       </c>
       <c r="R24" t="n">
-        <v>6828917</v>
+        <v>6829288</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,27 +2916,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755530</v>
+        <v>125755513</v>
       </c>
       <c r="B25" t="n">
-        <v>80115</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R25" t="n">
-        <v>6829288</v>
+        <v>6828917</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755428</v>
+        <v>125755516</v>
       </c>
       <c r="B26" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483280</v>
+        <v>483291</v>
       </c>
       <c r="R26" t="n">
-        <v>6828942</v>
+        <v>6828969</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755516</v>
+        <v>125755481</v>
       </c>
       <c r="B27" t="n">
         <v>78977</v>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483291</v>
+        <v>482929</v>
       </c>
       <c r="R27" t="n">
-        <v>6828969</v>
+        <v>6828797</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755481</v>
+        <v>125755428</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482929</v>
+        <v>483280</v>
       </c>
       <c r="R28" t="n">
-        <v>6828797</v>
+        <v>6828942</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4866,32 +4866,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755483</v>
+        <v>125755458</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>58331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>482971</v>
+        <v>483319</v>
       </c>
       <c r="R45" t="n">
-        <v>6828738</v>
+        <v>6829293</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755437</v>
+        <v>125755483</v>
       </c>
       <c r="B46" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483307</v>
+        <v>482971</v>
       </c>
       <c r="R46" t="n">
-        <v>6829287</v>
+        <v>6828738</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755491</v>
+        <v>125755437</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483015</v>
+        <v>483307</v>
       </c>
       <c r="R47" t="n">
-        <v>6828753</v>
+        <v>6829287</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,32 +5157,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755458</v>
+        <v>125755491</v>
       </c>
       <c r="B48" t="n">
-        <v>58331</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483319</v>
+        <v>483015</v>
       </c>
       <c r="R48" t="n">
-        <v>6829293</v>
+        <v>6828753</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755496</v>
+        <v>125755459</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>91256</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5755,21 +5755,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483054</v>
+        <v>483398</v>
       </c>
       <c r="R54" t="n">
-        <v>6828788</v>
+        <v>6829316</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755463</v>
+        <v>125755419</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483450</v>
+        <v>483005</v>
       </c>
       <c r="R55" t="n">
-        <v>6829306</v>
+        <v>6828754</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755459</v>
+        <v>125755496</v>
       </c>
       <c r="B56" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483398</v>
+        <v>483054</v>
       </c>
       <c r="R56" t="n">
-        <v>6829316</v>
+        <v>6828788</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6035,10 +6035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755419</v>
+        <v>125755463</v>
       </c>
       <c r="B57" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6046,21 +6046,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483005</v>
+        <v>483450</v>
       </c>
       <c r="R57" t="n">
-        <v>6828754</v>
+        <v>6829306</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8562,10 +8562,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755526</v>
+        <v>125755469</v>
       </c>
       <c r="B83" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8573,21 +8573,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483499</v>
+        <v>483342</v>
       </c>
       <c r="R83" t="n">
-        <v>6829120</v>
+        <v>6829286</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8659,7 +8659,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755469</v>
+        <v>125755493</v>
       </c>
       <c r="B84" t="n">
         <v>78977</v>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483342</v>
+        <v>483037</v>
       </c>
       <c r="R84" t="n">
-        <v>6829286</v>
+        <v>6828788</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8756,32 +8756,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755493</v>
+        <v>125755520</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483037</v>
+        <v>483458</v>
       </c>
       <c r="R85" t="n">
-        <v>6828788</v>
+        <v>6829089</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8853,32 +8853,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755520</v>
+        <v>125755526</v>
       </c>
       <c r="B86" t="n">
-        <v>92532</v>
+        <v>78644</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483458</v>
+        <v>483499</v>
       </c>
       <c r="R86" t="n">
-        <v>6829089</v>
+        <v>6829120</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10812,10 +10812,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125745158</v>
+        <v>125746064</v>
       </c>
       <c r="B106" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10823,45 +10823,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483359</v>
+        <v>483474</v>
       </c>
       <c r="R106" t="n">
-        <v>6829093</v>
+        <v>6829119</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10917,7 +10909,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125746064</v>
+        <v>125746931</v>
       </c>
       <c r="B107" t="n">
         <v>78977</v>
@@ -10948,14 +10940,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483474</v>
+        <v>483156</v>
       </c>
       <c r="R107" t="n">
-        <v>6829119</v>
+        <v>6828728</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10988,6 +10980,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11014,10 +11011,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125746931</v>
+        <v>125745158</v>
       </c>
       <c r="B108" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11025,37 +11022,45 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483156</v>
+        <v>483359</v>
       </c>
       <c r="R108" t="n">
-        <v>6828728</v>
+        <v>6829093</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11085,11 +11090,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755452</v>
+        <v>125755438</v>
       </c>
       <c r="B11" t="n">
-        <v>78735</v>
+        <v>79001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483587</v>
+        <v>483600</v>
       </c>
       <c r="R11" t="n">
-        <v>6829364</v>
+        <v>6829152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755438</v>
+        <v>125755452</v>
       </c>
       <c r="B12" t="n">
-        <v>79001</v>
+        <v>78735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483600</v>
+        <v>483587</v>
       </c>
       <c r="R12" t="n">
-        <v>6829152</v>
+        <v>6829364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755488</v>
+        <v>125755416</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483019</v>
+        <v>483454</v>
       </c>
       <c r="R15" t="n">
-        <v>6828737</v>
+        <v>6829082</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755475</v>
+        <v>125755488</v>
       </c>
       <c r="B16" t="n">
         <v>78977</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483169</v>
+        <v>483019</v>
       </c>
       <c r="R16" t="n">
-        <v>6829132</v>
+        <v>6828737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755416</v>
+        <v>125755475</v>
       </c>
       <c r="B17" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483454</v>
+        <v>483169</v>
       </c>
       <c r="R17" t="n">
-        <v>6829082</v>
+        <v>6829132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755506</v>
+        <v>125755421</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483162</v>
+        <v>483044</v>
       </c>
       <c r="R18" t="n">
-        <v>6828887</v>
+        <v>6828792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755480</v>
+        <v>125755506</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482885</v>
+        <v>483162</v>
       </c>
       <c r="R19" t="n">
-        <v>6828897</v>
+        <v>6828887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755494</v>
+        <v>125755480</v>
       </c>
       <c r="B20" t="n">
         <v>78977</v>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483047</v>
+        <v>482885</v>
       </c>
       <c r="R20" t="n">
-        <v>6828790</v>
+        <v>6828897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755445</v>
+        <v>125755494</v>
       </c>
       <c r="B21" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482900</v>
+        <v>483047</v>
       </c>
       <c r="R21" t="n">
-        <v>6828861</v>
+        <v>6828790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755421</v>
+        <v>125755445</v>
       </c>
       <c r="B22" t="n">
-        <v>79009</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483044</v>
+        <v>482900</v>
       </c>
       <c r="R22" t="n">
-        <v>6828792</v>
+        <v>6828861</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3304,32 +3304,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755502</v>
+        <v>125755460</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>91403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483078</v>
+        <v>482913</v>
       </c>
       <c r="R29" t="n">
-        <v>6828839</v>
+        <v>6829095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,7 +3401,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755473</v>
+        <v>125755502</v>
       </c>
       <c r="B30" t="n">
         <v>78977</v>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483182</v>
+        <v>483078</v>
       </c>
       <c r="R30" t="n">
-        <v>6829175</v>
+        <v>6828839</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,32 +3498,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755460</v>
+        <v>125755473</v>
       </c>
       <c r="B31" t="n">
-        <v>91403</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>482913</v>
+        <v>483182</v>
       </c>
       <c r="R31" t="n">
-        <v>6829095</v>
+        <v>6829175</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3595,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755478</v>
+        <v>125755411</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,21 +3606,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483147</v>
+        <v>482945</v>
       </c>
       <c r="R32" t="n">
-        <v>6829095</v>
+        <v>6829125</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3692,10 +3692,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755411</v>
+        <v>125755478</v>
       </c>
       <c r="B33" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3703,21 +3703,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>482945</v>
+        <v>483147</v>
       </c>
       <c r="R33" t="n">
-        <v>6829125</v>
+        <v>6829095</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755501</v>
+        <v>125755464</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483071</v>
+        <v>483423</v>
       </c>
       <c r="R35" t="n">
-        <v>6828833</v>
+        <v>6829325</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755464</v>
+        <v>125755508</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483423</v>
+        <v>483189</v>
       </c>
       <c r="R36" t="n">
-        <v>6829325</v>
+        <v>6828911</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755508</v>
+        <v>125755482</v>
       </c>
       <c r="B37" t="n">
         <v>78977</v>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483189</v>
+        <v>482960</v>
       </c>
       <c r="R37" t="n">
-        <v>6828911</v>
+        <v>6828769</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4177,7 +4177,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755482</v>
+        <v>125755501</v>
       </c>
       <c r="B38" t="n">
         <v>78977</v>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>482960</v>
+        <v>483071</v>
       </c>
       <c r="R38" t="n">
-        <v>6828769</v>
+        <v>6828833</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755466</v>
+        <v>125755456</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4285,21 +4285,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483400</v>
+        <v>483114</v>
       </c>
       <c r="R39" t="n">
-        <v>6829318</v>
+        <v>6828865</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755456</v>
+        <v>125755466</v>
       </c>
       <c r="B40" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483114</v>
+        <v>483400</v>
       </c>
       <c r="R40" t="n">
-        <v>6828865</v>
+        <v>6829318</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,32 +4866,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755458</v>
+        <v>125755437</v>
       </c>
       <c r="B45" t="n">
-        <v>58331</v>
+        <v>80081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103044</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483319</v>
+        <v>483307</v>
       </c>
       <c r="R45" t="n">
-        <v>6829293</v>
+        <v>6829287</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755437</v>
+        <v>125755491</v>
       </c>
       <c r="B47" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483307</v>
+        <v>483015</v>
       </c>
       <c r="R47" t="n">
-        <v>6829287</v>
+        <v>6828753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,32 +5157,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755491</v>
+        <v>125755458</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>58331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483015</v>
+        <v>483319</v>
       </c>
       <c r="R48" t="n">
-        <v>6828753</v>
+        <v>6829293</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6229,50 +6229,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755431</v>
+        <v>125755533</v>
       </c>
       <c r="B59" t="n">
-        <v>56848</v>
+        <v>78383</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483099</v>
+        <v>483472</v>
       </c>
       <c r="R59" t="n">
-        <v>6828858</v>
+        <v>6829305</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,10 +6326,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755533</v>
+        <v>125755517</v>
       </c>
       <c r="B60" t="n">
-        <v>78383</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6342,21 +6337,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6366,10 +6361,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483472</v>
+        <v>483386</v>
       </c>
       <c r="R60" t="n">
-        <v>6829305</v>
+        <v>6829003</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,45 +6423,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755517</v>
+        <v>125755431</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483386</v>
+        <v>483099</v>
       </c>
       <c r="R61" t="n">
-        <v>6829003</v>
+        <v>6828858</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6622,10 +6622,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755424</v>
+        <v>125755441</v>
       </c>
       <c r="B63" t="n">
-        <v>79009</v>
+        <v>78736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6633,21 +6633,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483162</v>
+        <v>483114</v>
       </c>
       <c r="R63" t="n">
-        <v>6828879</v>
+        <v>6828865</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6719,10 +6719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755472</v>
+        <v>125755424</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6730,21 +6730,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483203</v>
+        <v>483162</v>
       </c>
       <c r="R64" t="n">
-        <v>6829189</v>
+        <v>6828879</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6816,10 +6816,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755489</v>
+        <v>125755412</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6827,21 +6827,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483001</v>
+        <v>482912</v>
       </c>
       <c r="R65" t="n">
-        <v>6828740</v>
+        <v>6828922</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6913,10 +6913,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755451</v>
+        <v>125755472</v>
       </c>
       <c r="B66" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6924,21 +6924,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483278</v>
+        <v>483203</v>
       </c>
       <c r="R66" t="n">
-        <v>6828932</v>
+        <v>6829189</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7010,10 +7010,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755412</v>
+        <v>125755489</v>
       </c>
       <c r="B67" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7021,21 +7021,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>482912</v>
+        <v>483001</v>
       </c>
       <c r="R67" t="n">
-        <v>6828922</v>
+        <v>6828740</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755441</v>
+        <v>125755451</v>
       </c>
       <c r="B68" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7118,21 +7118,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483114</v>
+        <v>483278</v>
       </c>
       <c r="R68" t="n">
-        <v>6828865</v>
+        <v>6828932</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7204,10 +7204,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755522</v>
+        <v>125755515</v>
       </c>
       <c r="B69" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7215,21 +7215,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483303</v>
+        <v>483280</v>
       </c>
       <c r="R69" t="n">
-        <v>6829017</v>
+        <v>6828952</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755515</v>
+        <v>125755514</v>
       </c>
       <c r="B70" t="n">
         <v>78977</v>
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483280</v>
+        <v>483220</v>
       </c>
       <c r="R70" t="n">
-        <v>6828952</v>
+        <v>6828907</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7398,7 +7398,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755514</v>
+        <v>125755518</v>
       </c>
       <c r="B71" t="n">
         <v>78977</v>
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483220</v>
+        <v>483467</v>
       </c>
       <c r="R71" t="n">
-        <v>6828907</v>
+        <v>6829027</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7495,7 +7495,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755518</v>
+        <v>125755503</v>
       </c>
       <c r="B72" t="n">
         <v>78977</v>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483467</v>
+        <v>483095</v>
       </c>
       <c r="R72" t="n">
-        <v>6829027</v>
+        <v>6828845</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7592,7 +7592,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755503</v>
+        <v>125755474</v>
       </c>
       <c r="B73" t="n">
         <v>78977</v>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483095</v>
+        <v>483188</v>
       </c>
       <c r="R73" t="n">
-        <v>6828845</v>
+        <v>6829143</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755474</v>
+        <v>125755522</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7700,21 +7700,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483188</v>
+        <v>483303</v>
       </c>
       <c r="R74" t="n">
-        <v>6829143</v>
+        <v>6829017</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7786,10 +7786,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755414</v>
+        <v>125755418</v>
       </c>
       <c r="B75" t="n">
-        <v>79595</v>
+        <v>79009</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7797,21 +7797,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483240</v>
+        <v>482886</v>
       </c>
       <c r="R75" t="n">
-        <v>6828921</v>
+        <v>6828895</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7883,10 +7883,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755418</v>
+        <v>125755511</v>
       </c>
       <c r="B76" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7894,21 +7894,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>482886</v>
+        <v>483188</v>
       </c>
       <c r="R76" t="n">
-        <v>6828895</v>
+        <v>6828936</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755511</v>
+        <v>125755504</v>
       </c>
       <c r="B77" t="n">
         <v>78977</v>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483188</v>
+        <v>483117</v>
       </c>
       <c r="R77" t="n">
-        <v>6828936</v>
+        <v>6828857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8077,7 +8077,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755504</v>
+        <v>125755484</v>
       </c>
       <c r="B78" t="n">
         <v>78977</v>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483117</v>
+        <v>482976</v>
       </c>
       <c r="R78" t="n">
-        <v>6828857</v>
+        <v>6828720</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8174,10 +8174,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755484</v>
+        <v>125755414</v>
       </c>
       <c r="B79" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8185,21 +8185,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8209,10 +8209,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>482976</v>
+        <v>483240</v>
       </c>
       <c r="R79" t="n">
-        <v>6828720</v>
+        <v>6828921</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8465,10 +8465,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755435</v>
+        <v>125755526</v>
       </c>
       <c r="B82" t="n">
-        <v>58135</v>
+        <v>78644</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8476,21 +8476,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103018</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483450</v>
+        <v>483499</v>
       </c>
       <c r="R82" t="n">
-        <v>6829302</v>
+        <v>6829120</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8562,32 +8562,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755469</v>
+        <v>125755520</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483342</v>
+        <v>483458</v>
       </c>
       <c r="R83" t="n">
-        <v>6829286</v>
+        <v>6829089</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8659,7 +8659,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755493</v>
+        <v>125755469</v>
       </c>
       <c r="B84" t="n">
         <v>78977</v>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483037</v>
+        <v>483342</v>
       </c>
       <c r="R84" t="n">
-        <v>6828788</v>
+        <v>6829286</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8756,32 +8756,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755520</v>
+        <v>125755493</v>
       </c>
       <c r="B85" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483458</v>
+        <v>483037</v>
       </c>
       <c r="R85" t="n">
-        <v>6829089</v>
+        <v>6828788</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8853,10 +8853,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755526</v>
+        <v>125755446</v>
       </c>
       <c r="B86" t="n">
-        <v>78644</v>
+        <v>80080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8864,21 +8864,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483499</v>
+        <v>482885</v>
       </c>
       <c r="R86" t="n">
-        <v>6829120</v>
+        <v>6828845</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8950,10 +8950,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755446</v>
+        <v>125755413</v>
       </c>
       <c r="B87" t="n">
-        <v>80080</v>
+        <v>79595</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8961,21 +8961,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>482885</v>
+        <v>482962</v>
       </c>
       <c r="R87" t="n">
-        <v>6828845</v>
+        <v>6828771</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9047,10 +9047,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755413</v>
+        <v>125755444</v>
       </c>
       <c r="B88" t="n">
-        <v>79595</v>
+        <v>80080</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9058,21 +9058,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9082,10 +9082,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482962</v>
+        <v>483272</v>
       </c>
       <c r="R88" t="n">
-        <v>6828771</v>
+        <v>6829286</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9144,10 +9144,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755444</v>
+        <v>125755435</v>
       </c>
       <c r="B89" t="n">
-        <v>80080</v>
+        <v>58135</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9155,21 +9155,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9179,10 +9179,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483272</v>
+        <v>483450</v>
       </c>
       <c r="R89" t="n">
-        <v>6829286</v>
+        <v>6829302</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755457</v>
+        <v>125755486</v>
       </c>
       <c r="B99" t="n">
-        <v>56839</v>
+        <v>78977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10125,39 +10125,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483040</v>
+        <v>483015</v>
       </c>
       <c r="R99" t="n">
-        <v>6828774</v>
+        <v>6828711</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10216,10 +10211,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755427</v>
+        <v>125755471</v>
       </c>
       <c r="B100" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10227,21 +10222,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10251,10 +10246,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483472</v>
+        <v>483206</v>
       </c>
       <c r="R100" t="n">
-        <v>6829305</v>
+        <v>6829193</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10313,10 +10308,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755486</v>
+        <v>125755457</v>
       </c>
       <c r="B101" t="n">
-        <v>78977</v>
+        <v>56839</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10324,34 +10319,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483015</v>
+        <v>483040</v>
       </c>
       <c r="R101" t="n">
-        <v>6828711</v>
+        <v>6828774</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10410,10 +10410,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755471</v>
+        <v>125755427</v>
       </c>
       <c r="B102" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483206</v>
+        <v>483472</v>
       </c>
       <c r="R102" t="n">
-        <v>6829193</v>
+        <v>6829305</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10812,10 +10812,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125746064</v>
+        <v>125745158</v>
       </c>
       <c r="B106" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10823,37 +10823,45 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483474</v>
+        <v>483359</v>
       </c>
       <c r="R106" t="n">
-        <v>6829119</v>
+        <v>6829093</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10909,7 +10917,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125746931</v>
+        <v>125746064</v>
       </c>
       <c r="B107" t="n">
         <v>78977</v>
@@ -10940,14 +10948,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483156</v>
+        <v>483474</v>
       </c>
       <c r="R107" t="n">
-        <v>6828728</v>
+        <v>6829119</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10980,11 +10988,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11011,10 +11014,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125745158</v>
+        <v>125746931</v>
       </c>
       <c r="B108" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11022,45 +11025,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483359</v>
+        <v>483156</v>
       </c>
       <c r="R108" t="n">
-        <v>6829093</v>
+        <v>6828728</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11090,6 +11085,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11711,10 +11711,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125746848</v>
+        <v>125748935</v>
       </c>
       <c r="B115" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11722,21 +11722,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483247</v>
+        <v>483071</v>
       </c>
       <c r="R115" t="n">
-        <v>6828848</v>
+        <v>6828797</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11808,10 +11808,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125748935</v>
+        <v>125746848</v>
       </c>
       <c r="B116" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11819,21 +11819,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11843,10 +11843,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483071</v>
+        <v>483247</v>
       </c>
       <c r="R116" t="n">
-        <v>6828797</v>
+        <v>6828848</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -11512,10 +11512,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125747249</v>
+        <v>125748935</v>
       </c>
       <c r="B113" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R113" t="n">
-        <v>6828658</v>
+        <v>6828797</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11583,11 +11583,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11614,7 +11609,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125747099</v>
+        <v>125747249</v>
       </c>
       <c r="B114" t="n">
         <v>78977</v>
@@ -11649,7 +11644,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483090</v>
+        <v>483032</v>
       </c>
       <c r="R114" t="n">
         <v>6828658</v>
@@ -11685,6 +11680,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11711,10 +11711,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125748935</v>
+        <v>125747099</v>
       </c>
       <c r="B115" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11722,21 +11722,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483071</v>
+        <v>483090</v>
       </c>
       <c r="R115" t="n">
-        <v>6828797</v>
+        <v>6828658</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1852,7 +1852,7 @@
         <v>125744833</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>125691576</v>
       </c>
       <c r="B105" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125745158</v>
+        <v>125746064</v>
       </c>
       <c r="B106" t="n">
-        <v>57653</v>
+        <v>78980</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10823,45 +10823,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483359</v>
+        <v>483474</v>
       </c>
       <c r="R106" t="n">
-        <v>6829093</v>
+        <v>6829119</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10917,10 +10909,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125746064</v>
+        <v>125746931</v>
       </c>
       <c r="B107" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10948,14 +10940,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483474</v>
+        <v>483156</v>
       </c>
       <c r="R107" t="n">
-        <v>6829119</v>
+        <v>6828728</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10988,6 +10980,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11014,10 +11011,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125746931</v>
+        <v>125745158</v>
       </c>
       <c r="B108" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11025,37 +11022,45 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483156</v>
+        <v>483359</v>
       </c>
       <c r="R108" t="n">
-        <v>6828728</v>
+        <v>6829093</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11085,11 +11090,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11119,7 +11119,7 @@
         <v>125745798</v>
       </c>
       <c r="B109" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>125747349</v>
       </c>
       <c r="B110" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>125745325</v>
       </c>
       <c r="B111" t="n">
-        <v>91403</v>
+        <v>91406</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>125744923</v>
       </c>
       <c r="B112" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11512,10 +11512,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125748935</v>
+        <v>125747249</v>
       </c>
       <c r="B113" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483071</v>
+        <v>483032</v>
       </c>
       <c r="R113" t="n">
-        <v>6828797</v>
+        <v>6828658</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11583,6 +11583,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11609,10 +11614,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125747249</v>
+        <v>125747099</v>
       </c>
       <c r="B114" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11644,7 +11649,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483032</v>
+        <v>483090</v>
       </c>
       <c r="R114" t="n">
         <v>6828658</v>
@@ -11680,11 +11685,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11711,10 +11711,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125747099</v>
+        <v>125746848</v>
       </c>
       <c r="B115" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483090</v>
+        <v>483247</v>
       </c>
       <c r="R115" t="n">
-        <v>6828658</v>
+        <v>6828848</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11808,10 +11808,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125746848</v>
+        <v>125748935</v>
       </c>
       <c r="B116" t="n">
-        <v>78977</v>
+        <v>80083</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11819,21 +11819,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11843,10 +11843,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483247</v>
+        <v>483071</v>
       </c>
       <c r="R116" t="n">
-        <v>6828848</v>
+        <v>6828797</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11908,7 +11908,7 @@
         <v>125746158</v>
       </c>
       <c r="B117" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>125748016</v>
       </c>
       <c r="B118" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>125747880</v>
       </c>
       <c r="B119" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>125746359</v>
       </c>
       <c r="B120" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12298,10 +12298,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125747874</v>
+        <v>125746396</v>
       </c>
       <c r="B121" t="n">
-        <v>57656</v>
+        <v>78739</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12309,39 +12309,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>483012</v>
+        <v>483265</v>
       </c>
       <c r="R121" t="n">
-        <v>6828723</v>
+        <v>6828852</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12400,10 +12395,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125746396</v>
+        <v>125747874</v>
       </c>
       <c r="B122" t="n">
-        <v>78736</v>
+        <v>57657</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12411,34 +12406,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>483265</v>
+        <v>483012</v>
       </c>
       <c r="R122" t="n">
-        <v>6828852</v>
+        <v>6828723</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -12298,10 +12298,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125746396</v>
+        <v>125747874</v>
       </c>
       <c r="B121" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12309,34 +12309,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>483265</v>
+        <v>483012</v>
       </c>
       <c r="R121" t="n">
-        <v>6828852</v>
+        <v>6828723</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12395,10 +12400,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125747874</v>
+        <v>125746396</v>
       </c>
       <c r="B122" t="n">
-        <v>57657</v>
+        <v>78739</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12406,39 +12411,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>483012</v>
+        <v>483265</v>
       </c>
       <c r="R122" t="n">
-        <v>6828723</v>
+        <v>6828852</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -11512,10 +11512,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125747249</v>
+        <v>125748935</v>
       </c>
       <c r="B113" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483032</v>
+        <v>483071</v>
       </c>
       <c r="R113" t="n">
-        <v>6828658</v>
+        <v>6828797</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11583,11 +11583,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11614,7 +11609,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125747099</v>
+        <v>125746848</v>
       </c>
       <c r="B114" t="n">
         <v>78980</v>
@@ -11649,10 +11644,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483090</v>
+        <v>483247</v>
       </c>
       <c r="R114" t="n">
-        <v>6828658</v>
+        <v>6828848</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11711,7 +11706,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125746848</v>
+        <v>125747249</v>
       </c>
       <c r="B115" t="n">
         <v>78980</v>
@@ -11746,10 +11741,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483247</v>
+        <v>483032</v>
       </c>
       <c r="R115" t="n">
-        <v>6828848</v>
+        <v>6828658</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11782,6 +11777,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11808,10 +11808,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125748935</v>
+        <v>125747099</v>
       </c>
       <c r="B116" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11819,21 +11819,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11843,10 +11843,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483071</v>
+        <v>483090</v>
       </c>
       <c r="R116" t="n">
-        <v>6828797</v>
+        <v>6828658</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12298,10 +12298,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125747874</v>
+        <v>125746396</v>
       </c>
       <c r="B121" t="n">
-        <v>57657</v>
+        <v>78739</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12309,39 +12309,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>483012</v>
+        <v>483265</v>
       </c>
       <c r="R121" t="n">
-        <v>6828723</v>
+        <v>6828852</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12400,10 +12395,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125746396</v>
+        <v>125747874</v>
       </c>
       <c r="B122" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12411,34 +12406,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>483265</v>
+        <v>483012</v>
       </c>
       <c r="R122" t="n">
-        <v>6828852</v>
+        <v>6828723</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -11512,10 +11512,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125748935</v>
+        <v>125746848</v>
       </c>
       <c r="B113" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483071</v>
+        <v>483247</v>
       </c>
       <c r="R113" t="n">
-        <v>6828797</v>
+        <v>6828848</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11609,7 +11609,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125746848</v>
+        <v>125747249</v>
       </c>
       <c r="B114" t="n">
         <v>78980</v>
@@ -11644,10 +11644,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483247</v>
+        <v>483032</v>
       </c>
       <c r="R114" t="n">
-        <v>6828848</v>
+        <v>6828658</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11680,6 +11680,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11706,7 +11711,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125747249</v>
+        <v>125747099</v>
       </c>
       <c r="B115" t="n">
         <v>78980</v>
@@ -11741,7 +11746,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483032</v>
+        <v>483090</v>
       </c>
       <c r="R115" t="n">
         <v>6828658</v>
@@ -11777,11 +11782,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11808,10 +11808,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125747099</v>
+        <v>125748935</v>
       </c>
       <c r="B116" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11819,21 +11819,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11843,10 +11843,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483090</v>
+        <v>483071</v>
       </c>
       <c r="R116" t="n">
-        <v>6828658</v>
+        <v>6828797</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -11512,10 +11512,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125746848</v>
+        <v>125748935</v>
       </c>
       <c r="B113" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483247</v>
+        <v>483071</v>
       </c>
       <c r="R113" t="n">
-        <v>6828848</v>
+        <v>6828797</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11609,7 +11609,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125747249</v>
+        <v>125746848</v>
       </c>
       <c r="B114" t="n">
         <v>78980</v>
@@ -11644,10 +11644,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483032</v>
+        <v>483247</v>
       </c>
       <c r="R114" t="n">
-        <v>6828658</v>
+        <v>6828848</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11680,11 +11680,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11711,7 +11706,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125747099</v>
+        <v>125747249</v>
       </c>
       <c r="B115" t="n">
         <v>78980</v>
@@ -11746,7 +11741,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483090</v>
+        <v>483032</v>
       </c>
       <c r="R115" t="n">
         <v>6828658</v>
@@ -11782,6 +11777,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11808,10 +11808,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125748935</v>
+        <v>125747099</v>
       </c>
       <c r="B116" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11819,21 +11819,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11843,10 +11843,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483071</v>
+        <v>483090</v>
       </c>
       <c r="R116" t="n">
-        <v>6828797</v>
+        <v>6828658</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -1949,7 +1949,7 @@
         <v>133697662</v>
       </c>
       <c r="B15" t="n">
-        <v>60514</v>
+        <v>60521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>134098828</v>
       </c>
       <c r="B16" t="n">
-        <v>60514</v>
+        <v>60521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>134087680</v>
       </c>
       <c r="B17" t="n">
-        <v>60514</v>
+        <v>60521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>134100090</v>
       </c>
       <c r="B18" t="n">
-        <v>60514</v>
+        <v>60521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755443</v>
+        <v>125755528</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483528</v>
+        <v>483525</v>
       </c>
       <c r="R2" t="n">
-        <v>6829109</v>
+        <v>6829111</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755429</v>
+        <v>125755529</v>
       </c>
       <c r="B3" t="n">
-        <v>79566</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483591</v>
+        <v>483526</v>
       </c>
       <c r="R3" t="n">
-        <v>6829247</v>
+        <v>6829108</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755426</v>
+        <v>125755430</v>
       </c>
       <c r="B4" t="n">
-        <v>91207</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755529</v>
+        <v>125755426</v>
       </c>
       <c r="B5" t="n">
-        <v>78644</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483526</v>
+        <v>483636</v>
       </c>
       <c r="R5" t="n">
-        <v>6829108</v>
+        <v>6829343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755447</v>
+        <v>125744772</v>
       </c>
       <c r="B6" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483591</v>
+        <v>483642</v>
       </c>
       <c r="R6" t="n">
-        <v>6829246</v>
+        <v>6829342</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755430</v>
+        <v>125755438</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>79351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483636</v>
+        <v>483600</v>
       </c>
       <c r="R7" t="n">
-        <v>6829343</v>
+        <v>6829152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755528</v>
+        <v>125755447</v>
       </c>
       <c r="B8" t="n">
-        <v>78644</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,34 +1268,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483525</v>
+        <v>483591</v>
       </c>
       <c r="R8" t="n">
-        <v>6829111</v>
+        <v>6829246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755409</v>
+        <v>125755448</v>
       </c>
       <c r="B9" t="n">
-        <v>79595</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,34 +1370,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483587</v>
+        <v>483529</v>
       </c>
       <c r="R9" t="n">
-        <v>6829364</v>
+        <v>6829109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755448</v>
+        <v>125755452</v>
       </c>
       <c r="B10" t="n">
-        <v>78735</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1485,21 +1490,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483529</v>
+        <v>483587</v>
       </c>
       <c r="R10" t="n">
-        <v>6829109</v>
+        <v>6829364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755438</v>
+        <v>125755409</v>
       </c>
       <c r="B11" t="n">
-        <v>79001</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483600</v>
+        <v>483587</v>
       </c>
       <c r="R11" t="n">
-        <v>6829152</v>
+        <v>6829364</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755452</v>
+        <v>125755410</v>
       </c>
       <c r="B12" t="n">
-        <v>78735</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483587</v>
+        <v>483577</v>
       </c>
       <c r="R12" t="n">
-        <v>6829364</v>
+        <v>6829339</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,45 +1752,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755439</v>
+        <v>133697662</v>
       </c>
       <c r="B13" t="n">
-        <v>78736</v>
+        <v>60521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>101268</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Margaritifera margaritifera</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483586</v>
+        <v>483658</v>
       </c>
       <c r="R13" t="n">
-        <v>6829364</v>
+        <v>6829341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1817,12 +1822,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1831,66 +1836,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Dennis Nyström, Jesper Scharin, Mathilda Lundgren Lodetti</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125744833</v>
+        <v>134087680</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>60521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>101268</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Margaritifera margaritifera</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Skidbäcksmyran, Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483642</v>
+        <v>483651</v>
       </c>
       <c r="R14" t="n">
-        <v>6829342</v>
+        <v>6829339</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1914,12 +1920,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1934,19 +1950,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Nicklas Albertsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Nicklas Albertsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133697662</v>
+        <v>134098828</v>
       </c>
       <c r="B15" t="n">
         <v>60521</v>
@@ -1986,13 +2002,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483658</v>
+        <v>483648</v>
       </c>
       <c r="R15" t="n">
-        <v>6829341</v>
+        <v>6829339</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2016,12 +2032,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2037,19 +2053,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Dennis Nyström, Jesper Scharin, Mathilda Lundgren Lodetti</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134098828</v>
+        <v>134100090</v>
       </c>
       <c r="B16" t="n">
         <v>60521</v>
@@ -2077,7 +2093,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -2085,17 +2105,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>483648</v>
       </c>
       <c r="R16" t="n">
-        <v>6829339</v>
+        <v>6829338</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2122,9 +2142,19 @@
           <t>2026-06-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2140,60 +2170,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Annika Rastén, Nicklas Albertsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134087680</v>
+        <v>125755439</v>
       </c>
       <c r="B17" t="n">
-        <v>60521</v>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101268</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Margaritifera margaritifera</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483651</v>
+        <v>483586</v>
       </c>
       <c r="R17" t="n">
-        <v>6829339</v>
+        <v>6829364</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2217,22 +2247,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,69 +2267,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicklas Albertsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicklas Albertsson</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134100090</v>
+        <v>125755443</v>
       </c>
       <c r="B18" t="n">
-        <v>60521</v>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101268</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Margaritifera margaritifera</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483648</v>
+        <v>483528</v>
       </c>
       <c r="R18" t="n">
-        <v>6829338</v>
+        <v>6829109</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2333,22 +2344,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2357,29 +2358,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Annika Rastén, Nicklas Albertsson</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755416</v>
+        <v>125755429</v>
       </c>
       <c r="B19" t="n">
-        <v>79595</v>
+        <v>79917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483454</v>
+        <v>483591</v>
       </c>
       <c r="R19" t="n">
-        <v>6829082</v>
+        <v>6829247</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755488</v>
+        <v>125755418</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2484,21 +2484,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483019</v>
+        <v>482886</v>
       </c>
       <c r="R20" t="n">
-        <v>6828737</v>
+        <v>6828895</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755475</v>
+        <v>125755419</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483169</v>
+        <v>483005</v>
       </c>
       <c r="R21" t="n">
-        <v>6829132</v>
+        <v>6828754</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2670,7 +2670,7 @@
         <v>125755421</v>
       </c>
       <c r="B22" t="n">
-        <v>79009</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755506</v>
+        <v>125755422</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483162</v>
+        <v>483099</v>
       </c>
       <c r="R23" t="n">
-        <v>6828887</v>
+        <v>6828854</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755480</v>
+        <v>125755424</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>79359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482885</v>
+        <v>483162</v>
       </c>
       <c r="R24" t="n">
-        <v>6828897</v>
+        <v>6828879</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755494</v>
+        <v>125755522</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483047</v>
+        <v>483303</v>
       </c>
       <c r="R25" t="n">
-        <v>6828790</v>
+        <v>6829017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755445</v>
+        <v>125755523</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>78993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,21 +3066,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482900</v>
+        <v>483313</v>
       </c>
       <c r="R26" t="n">
-        <v>6828861</v>
+        <v>6829017</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755440</v>
+        <v>125755525</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>78993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3163,21 +3163,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482960</v>
+        <v>483442</v>
       </c>
       <c r="R27" t="n">
-        <v>6828991</v>
+        <v>6829028</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3249,27 +3249,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755530</v>
+        <v>125744889</v>
       </c>
       <c r="B28" t="n">
-        <v>80115</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3278,19 +3278,22 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483303</v>
+        <v>483126</v>
       </c>
       <c r="R28" t="n">
-        <v>6829288</v>
+        <v>6829064</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3328,32 +3331,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755513</v>
+        <v>125746083</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3377,14 +3381,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483206</v>
+        <v>483342</v>
       </c>
       <c r="R29" t="n">
-        <v>6828917</v>
+        <v>6828971</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,26 +3435,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755516</v>
+        <v>125746359</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3474,14 +3478,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483291</v>
+        <v>483265</v>
       </c>
       <c r="R30" t="n">
-        <v>6828969</v>
+        <v>6828852</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3528,26 +3532,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755481</v>
+        <v>125746416</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3571,14 +3575,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>482929</v>
+        <v>483247</v>
       </c>
       <c r="R31" t="n">
-        <v>6828797</v>
+        <v>6828848</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3625,57 +3629,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755428</v>
+        <v>125746931</v>
       </c>
       <c r="B32" t="n">
-        <v>79566</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483280</v>
+        <v>483156</v>
       </c>
       <c r="R32" t="n">
-        <v>6828942</v>
+        <v>6828728</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3710,6 +3714,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3722,22 +3731,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755460</v>
+        <v>125747099</v>
       </c>
       <c r="B33" t="n">
-        <v>91403</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3745,34 +3754,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>482913</v>
+        <v>483090</v>
       </c>
       <c r="R33" t="n">
-        <v>6829095</v>
+        <v>6828658</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3819,26 +3828,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755502</v>
+        <v>125747249</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3862,14 +3871,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483078</v>
+        <v>483032</v>
       </c>
       <c r="R34" t="n">
-        <v>6828839</v>
+        <v>6828658</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3904,6 +3913,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -3916,26 +3930,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755473</v>
+        <v>125747349</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3959,14 +3973,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483182</v>
+        <v>482981</v>
       </c>
       <c r="R35" t="n">
-        <v>6829175</v>
+        <v>6828687</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4013,57 +4027,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755411</v>
+        <v>125747880</v>
       </c>
       <c r="B36" t="n">
-        <v>79595</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>482945</v>
+        <v>483012</v>
       </c>
       <c r="R36" t="n">
-        <v>6829125</v>
+        <v>6828723</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4110,26 +4124,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755478</v>
+        <v>125755462</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4157,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483147</v>
+        <v>483199</v>
       </c>
       <c r="R37" t="n">
-        <v>6829095</v>
+        <v>6828937</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,6 +4207,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>150 cm långt i område mycket rikt på hänglavar och keloved. Saknar hänsynsband.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4219,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755417</v>
+        <v>125755479</v>
       </c>
       <c r="B38" t="n">
-        <v>79009</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4254,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>482974</v>
+        <v>482918</v>
       </c>
       <c r="R38" t="n">
-        <v>6829143</v>
+        <v>6828932</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4316,14 +4335,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755464</v>
+        <v>125755480</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4351,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483423</v>
+        <v>482885</v>
       </c>
       <c r="R39" t="n">
-        <v>6829325</v>
+        <v>6828897</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4413,14 +4432,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755508</v>
+        <v>125755481</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4448,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483189</v>
+        <v>482929</v>
       </c>
       <c r="R40" t="n">
-        <v>6828911</v>
+        <v>6828797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4513,11 +4532,11 @@
         <v>125755482</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4607,14 +4626,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755501</v>
+        <v>125755483</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4642,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483071</v>
+        <v>482971</v>
       </c>
       <c r="R42" t="n">
-        <v>6828833</v>
+        <v>6828738</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4704,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755456</v>
+        <v>125755484</v>
       </c>
       <c r="B43" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4739,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483114</v>
+        <v>482976</v>
       </c>
       <c r="R43" t="n">
-        <v>6828865</v>
+        <v>6828720</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4801,14 +4820,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755466</v>
+        <v>125755485</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4836,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483400</v>
+        <v>483002</v>
       </c>
       <c r="R44" t="n">
-        <v>6829318</v>
+        <v>6828695</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4898,14 +4917,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755510</v>
+        <v>125755486</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4933,10 +4952,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483191</v>
+        <v>483015</v>
       </c>
       <c r="R45" t="n">
-        <v>6828929</v>
+        <v>6828711</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4995,32 +5014,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755453</v>
+        <v>125755488</v>
       </c>
       <c r="B46" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5030,10 +5049,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>482979</v>
+        <v>483019</v>
       </c>
       <c r="R46" t="n">
-        <v>6829140</v>
+        <v>6828737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5092,14 +5111,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755500</v>
+        <v>125755489</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5127,10 +5146,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483068</v>
+        <v>483001</v>
       </c>
       <c r="R47" t="n">
-        <v>6828819</v>
+        <v>6828740</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5189,50 +5208,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755536</v>
+        <v>125755490</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483037</v>
+        <v>483007</v>
       </c>
       <c r="R48" t="n">
-        <v>6828775</v>
+        <v>6828754</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5265,11 +5279,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5296,32 +5305,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755437</v>
+        <v>125755491</v>
       </c>
       <c r="B49" t="n">
-        <v>80081</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5340,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483307</v>
+        <v>483015</v>
       </c>
       <c r="R49" t="n">
-        <v>6829287</v>
+        <v>6828753</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,14 +5402,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755483</v>
+        <v>125755492</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5428,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>482971</v>
+        <v>483032</v>
       </c>
       <c r="R50" t="n">
-        <v>6828738</v>
+        <v>6828773</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,14 +5499,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755491</v>
+        <v>125755493</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5525,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483015</v>
+        <v>483037</v>
       </c>
       <c r="R51" t="n">
-        <v>6828753</v>
+        <v>6828788</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,32 +5596,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755458</v>
+        <v>125755494</v>
       </c>
       <c r="B52" t="n">
-        <v>58331</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5631,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483319</v>
+        <v>483047</v>
       </c>
       <c r="R52" t="n">
-        <v>6829293</v>
+        <v>6828790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,32 +5693,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755442</v>
+        <v>125755496</v>
       </c>
       <c r="B53" t="n">
-        <v>78736</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5728,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483201</v>
+        <v>483054</v>
       </c>
       <c r="R53" t="n">
-        <v>6828916</v>
+        <v>6828788</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5781,14 +5790,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755492</v>
+        <v>125755497</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5816,10 +5825,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483032</v>
+        <v>483063</v>
       </c>
       <c r="R54" t="n">
-        <v>6828773</v>
+        <v>6828803</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5881,11 +5890,11 @@
         <v>125755498</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -5975,14 +5984,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755468</v>
+        <v>125755500</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6010,10 +6019,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483391</v>
+        <v>483068</v>
       </c>
       <c r="R56" t="n">
-        <v>6829308</v>
+        <v>6828819</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,50 +6081,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755432</v>
+        <v>125755501</v>
       </c>
       <c r="B57" t="n">
-        <v>56848</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483446</v>
+        <v>483071</v>
       </c>
       <c r="R57" t="n">
-        <v>6829026</v>
+        <v>6828833</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6174,32 +6178,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755459</v>
+        <v>125755502</v>
       </c>
       <c r="B58" t="n">
-        <v>91256</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6209,10 +6213,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483398</v>
+        <v>483078</v>
       </c>
       <c r="R58" t="n">
-        <v>6829316</v>
+        <v>6828839</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6271,32 +6275,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755419</v>
+        <v>125755503</v>
       </c>
       <c r="B59" t="n">
-        <v>79009</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6306,10 +6310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483005</v>
+        <v>483095</v>
       </c>
       <c r="R59" t="n">
-        <v>6828754</v>
+        <v>6828845</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6368,14 +6372,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755496</v>
+        <v>125755504</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6403,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483054</v>
+        <v>483117</v>
       </c>
       <c r="R60" t="n">
-        <v>6828788</v>
+        <v>6828857</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6465,14 +6469,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755463</v>
+        <v>125755506</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6500,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483450</v>
+        <v>483162</v>
       </c>
       <c r="R61" t="n">
-        <v>6829306</v>
+        <v>6828887</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6562,32 +6566,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755525</v>
+        <v>125755507</v>
       </c>
       <c r="B62" t="n">
-        <v>78644</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6597,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483442</v>
+        <v>483178</v>
       </c>
       <c r="R62" t="n">
-        <v>6829028</v>
+        <v>6828902</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6659,32 +6663,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755533</v>
+        <v>125755508</v>
       </c>
       <c r="B63" t="n">
-        <v>78383</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6694,10 +6698,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483472</v>
+        <v>483189</v>
       </c>
       <c r="R63" t="n">
-        <v>6829305</v>
+        <v>6828911</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6756,14 +6760,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755517</v>
+        <v>125755510</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6791,10 +6795,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483386</v>
+        <v>483191</v>
       </c>
       <c r="R64" t="n">
-        <v>6829003</v>
+        <v>6828929</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6853,50 +6857,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755431</v>
+        <v>125755511</v>
       </c>
       <c r="B65" t="n">
-        <v>56848</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483099</v>
+        <v>483188</v>
       </c>
       <c r="R65" t="n">
-        <v>6828858</v>
+        <v>6828936</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6955,32 +6954,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755433</v>
+        <v>125755512</v>
       </c>
       <c r="B66" t="n">
-        <v>57816</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6990,10 +6989,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483307</v>
+        <v>483190</v>
       </c>
       <c r="R66" t="n">
-        <v>6829287</v>
+        <v>6828942</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7052,32 +7051,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755441</v>
+        <v>125755513</v>
       </c>
       <c r="B67" t="n">
-        <v>78736</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7087,10 +7086,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483114</v>
+        <v>483206</v>
       </c>
       <c r="R67" t="n">
-        <v>6828865</v>
+        <v>6828917</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7149,32 +7148,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755424</v>
+        <v>125755514</v>
       </c>
       <c r="B68" t="n">
-        <v>79009</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7184,10 +7183,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483162</v>
+        <v>483220</v>
       </c>
       <c r="R68" t="n">
-        <v>6828879</v>
+        <v>6828907</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7246,32 +7245,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755412</v>
+        <v>125755515</v>
       </c>
       <c r="B69" t="n">
-        <v>79595</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7281,10 +7280,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>482912</v>
+        <v>483280</v>
       </c>
       <c r="R69" t="n">
-        <v>6828922</v>
+        <v>6828952</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7343,14 +7342,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755472</v>
+        <v>125755516</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -7378,10 +7377,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483203</v>
+        <v>483291</v>
       </c>
       <c r="R70" t="n">
-        <v>6829189</v>
+        <v>6828969</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7440,14 +7439,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755489</v>
+        <v>125755517</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -7475,10 +7474,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483001</v>
+        <v>483386</v>
       </c>
       <c r="R71" t="n">
-        <v>6828740</v>
+        <v>6829003</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7537,32 +7536,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755451</v>
+        <v>125755518</v>
       </c>
       <c r="B72" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7572,10 +7571,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483278</v>
+        <v>483467</v>
       </c>
       <c r="R72" t="n">
-        <v>6828932</v>
+        <v>6829027</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7634,10 +7633,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755515</v>
+        <v>125755451</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7645,21 +7644,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7669,10 +7668,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483280</v>
+        <v>483278</v>
       </c>
       <c r="R73" t="n">
-        <v>6828952</v>
+        <v>6828932</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7731,10 +7730,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755514</v>
+        <v>125755455</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7742,21 +7741,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7766,10 +7765,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483220</v>
+        <v>482942</v>
       </c>
       <c r="R74" t="n">
-        <v>6828907</v>
+        <v>6828979</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7828,10 +7827,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755518</v>
+        <v>125755456</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7839,21 +7838,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7863,10 +7862,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483467</v>
+        <v>483114</v>
       </c>
       <c r="R75" t="n">
-        <v>6829027</v>
+        <v>6828865</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7925,10 +7924,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755503</v>
+        <v>125755412</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>79946</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7936,21 +7935,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7960,10 +7959,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483095</v>
+        <v>482912</v>
       </c>
       <c r="R76" t="n">
-        <v>6828845</v>
+        <v>6828922</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8022,10 +8021,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755474</v>
+        <v>125755413</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>79946</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8033,21 +8032,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8057,10 +8056,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483188</v>
+        <v>482962</v>
       </c>
       <c r="R77" t="n">
-        <v>6829143</v>
+        <v>6828771</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8119,10 +8118,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755522</v>
+        <v>125755414</v>
       </c>
       <c r="B78" t="n">
-        <v>78644</v>
+        <v>79946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8130,21 +8129,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8154,10 +8153,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483303</v>
+        <v>483240</v>
       </c>
       <c r="R78" t="n">
-        <v>6829017</v>
+        <v>6828921</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8216,10 +8215,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755418</v>
+        <v>125755415</v>
       </c>
       <c r="B79" t="n">
-        <v>79009</v>
+        <v>79946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8227,21 +8226,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8251,10 +8250,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>482886</v>
+        <v>483456</v>
       </c>
       <c r="R79" t="n">
-        <v>6828895</v>
+        <v>6829062</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8313,10 +8312,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755511</v>
+        <v>125748935</v>
       </c>
       <c r="B80" t="n">
-        <v>78977</v>
+        <v>80432</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8324,34 +8323,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483188</v>
+        <v>483071</v>
       </c>
       <c r="R80" t="n">
-        <v>6828936</v>
+        <v>6828797</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8398,22 +8397,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755504</v>
+        <v>125755445</v>
       </c>
       <c r="B81" t="n">
-        <v>78977</v>
+        <v>80432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8421,21 +8420,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8445,10 +8444,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483117</v>
+        <v>482900</v>
       </c>
       <c r="R81" t="n">
-        <v>6828857</v>
+        <v>6828861</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8507,10 +8506,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755484</v>
+        <v>125755446</v>
       </c>
       <c r="B82" t="n">
-        <v>78977</v>
+        <v>80432</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8518,21 +8517,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8542,10 +8541,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>482976</v>
+        <v>482885</v>
       </c>
       <c r="R82" t="n">
-        <v>6828720</v>
+        <v>6828845</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8604,10 +8603,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755414</v>
+        <v>125747874</v>
       </c>
       <c r="B83" t="n">
-        <v>79595</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8615,34 +8614,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483240</v>
+        <v>483012</v>
       </c>
       <c r="R83" t="n">
-        <v>6828921</v>
+        <v>6828723</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8689,22 +8693,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755479</v>
+        <v>125748016</v>
       </c>
       <c r="B84" t="n">
-        <v>78977</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8712,34 +8716,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>482918</v>
+        <v>483071</v>
       </c>
       <c r="R84" t="n">
-        <v>6828932</v>
+        <v>6828797</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8786,22 +8795,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755512</v>
+        <v>125755536</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8809,34 +8818,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483190</v>
+        <v>483037</v>
       </c>
       <c r="R85" t="n">
-        <v>6828942</v>
+        <v>6828775</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8869,6 +8883,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Granlåga med gammalt bohål</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8895,45 +8914,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755526</v>
+        <v>125755431</v>
       </c>
       <c r="B86" t="n">
-        <v>78644</v>
+        <v>57141</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483499</v>
+        <v>483099</v>
       </c>
       <c r="R86" t="n">
-        <v>6829120</v>
+        <v>6828858</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8992,10 +9016,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755520</v>
+        <v>125755432</v>
       </c>
       <c r="B87" t="n">
-        <v>92532</v>
+        <v>57141</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9003,34 +9027,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483458</v>
+        <v>483446</v>
       </c>
       <c r="R87" t="n">
-        <v>6829089</v>
+        <v>6829026</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9089,45 +9118,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755469</v>
+        <v>125755457</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>57132</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483342</v>
+        <v>483040</v>
       </c>
       <c r="R88" t="n">
-        <v>6829286</v>
+        <v>6828774</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9186,10 +9220,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755493</v>
+        <v>125746396</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>79085</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9197,34 +9231,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Abborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483037</v>
+        <v>483265</v>
       </c>
       <c r="R89" t="n">
-        <v>6828788</v>
+        <v>6828852</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9271,22 +9305,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755446</v>
+        <v>125755440</v>
       </c>
       <c r="B90" t="n">
-        <v>80080</v>
+        <v>79085</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9294,21 +9328,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9318,10 +9352,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482885</v>
+        <v>482960</v>
       </c>
       <c r="R90" t="n">
-        <v>6828845</v>
+        <v>6828991</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9380,10 +9414,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755413</v>
+        <v>125755441</v>
       </c>
       <c r="B91" t="n">
-        <v>79595</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9391,21 +9425,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9415,10 +9449,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>482962</v>
+        <v>483114</v>
       </c>
       <c r="R91" t="n">
-        <v>6828771</v>
+        <v>6828865</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9477,10 +9511,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755444</v>
+        <v>125755442</v>
       </c>
       <c r="B92" t="n">
-        <v>80080</v>
+        <v>79085</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9488,21 +9522,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9512,10 +9546,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483272</v>
+        <v>483201</v>
       </c>
       <c r="R92" t="n">
-        <v>6829286</v>
+        <v>6828916</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9574,10 +9608,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755435</v>
+        <v>125755428</v>
       </c>
       <c r="B93" t="n">
-        <v>58135</v>
+        <v>79917</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9585,21 +9619,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103018</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9609,10 +9643,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483450</v>
+        <v>483280</v>
       </c>
       <c r="R93" t="n">
-        <v>6829302</v>
+        <v>6828942</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9671,10 +9705,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755422</v>
+        <v>125755417</v>
       </c>
       <c r="B94" t="n">
-        <v>79009</v>
+        <v>79359</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9706,10 +9740,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483099</v>
+        <v>482974</v>
       </c>
       <c r="R94" t="n">
-        <v>6828854</v>
+        <v>6829143</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9768,10 +9802,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755507</v>
+        <v>125755526</v>
       </c>
       <c r="B95" t="n">
-        <v>78977</v>
+        <v>78993</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9779,21 +9813,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9803,10 +9837,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483178</v>
+        <v>483499</v>
       </c>
       <c r="R95" t="n">
-        <v>6828902</v>
+        <v>6829120</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9865,32 +9899,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755415</v>
+        <v>125755459</v>
       </c>
       <c r="B96" t="n">
-        <v>79595</v>
+        <v>91923</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9900,10 +9934,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483456</v>
+        <v>483398</v>
       </c>
       <c r="R96" t="n">
-        <v>6829062</v>
+        <v>6829316</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9962,48 +9996,51 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755497</v>
+        <v>125745325</v>
       </c>
       <c r="B97" t="n">
-        <v>78977</v>
+        <v>92083</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483063</v>
+        <v>483279</v>
       </c>
       <c r="R97" t="n">
-        <v>6828803</v>
+        <v>6829148</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10041,50 +10078,51 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755490</v>
+        <v>125755460</v>
       </c>
       <c r="B98" t="n">
-        <v>78977</v>
+        <v>92083</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10094,10 +10132,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483007</v>
+        <v>482913</v>
       </c>
       <c r="R98" t="n">
-        <v>6828754</v>
+        <v>6829095</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10156,10 +10194,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755485</v>
+        <v>125755437</v>
       </c>
       <c r="B99" t="n">
-        <v>78977</v>
+        <v>80433</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10167,21 +10205,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10191,10 +10229,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483002</v>
+        <v>483307</v>
       </c>
       <c r="R99" t="n">
-        <v>6828695</v>
+        <v>6829287</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10253,10 +10291,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755523</v>
+        <v>125755520</v>
       </c>
       <c r="B100" t="n">
-        <v>78644</v>
+        <v>93197</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10264,21 +10302,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10288,10 +10326,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483313</v>
+        <v>483458</v>
       </c>
       <c r="R100" t="n">
-        <v>6829017</v>
+        <v>6829089</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10350,45 +10388,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755455</v>
+        <v>125745710</v>
       </c>
       <c r="B101" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Aborrsjöbäcken, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>482942</v>
+        <v>483474</v>
       </c>
       <c r="R101" t="n">
-        <v>6828979</v>
+        <v>6829119</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10435,39 +10473,39 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755532</v>
+        <v>125755463</v>
       </c>
       <c r="B102" t="n">
-        <v>80115</v>
+        <v>79327</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10482,10 +10520,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483294</v>
+        <v>483450</v>
       </c>
       <c r="R102" t="n">
-        <v>6829294</v>
+        <v>6829306</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10544,14 +10582,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755486</v>
+        <v>125755464</v>
       </c>
       <c r="B103" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -10579,10 +10617,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483015</v>
+        <v>483423</v>
       </c>
       <c r="R103" t="n">
-        <v>6828711</v>
+        <v>6829325</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10641,14 +10679,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755471</v>
+        <v>125755466</v>
       </c>
       <c r="B104" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -10676,10 +10714,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483206</v>
+        <v>483400</v>
       </c>
       <c r="R104" t="n">
-        <v>6829193</v>
+        <v>6829318</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10738,50 +10776,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755457</v>
+        <v>125755468</v>
       </c>
       <c r="B105" t="n">
-        <v>56839</v>
+        <v>79327</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483040</v>
+        <v>483391</v>
       </c>
       <c r="R105" t="n">
-        <v>6828774</v>
+        <v>6829308</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10840,32 +10873,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755427</v>
+        <v>125755469</v>
       </c>
       <c r="B106" t="n">
-        <v>79566</v>
+        <v>79327</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10875,10 +10908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483472</v>
+        <v>483342</v>
       </c>
       <c r="R106" t="n">
-        <v>6829305</v>
+        <v>6829286</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10937,32 +10970,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755436</v>
+        <v>125755471</v>
       </c>
       <c r="B107" t="n">
-        <v>80109</v>
+        <v>79327</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10972,10 +11005,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R107" t="n">
-        <v>6829290</v>
+        <v>6829193</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11034,14 +11067,14 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755462</v>
+        <v>125755472</v>
       </c>
       <c r="B108" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -11069,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483199</v>
+        <v>483203</v>
       </c>
       <c r="R108" t="n">
-        <v>6828937</v>
+        <v>6829189</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11105,11 +11138,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>150 cm långt i område mycket rikt på hänglavar och keloved. Saknar hänsynsband.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11136,48 +11164,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125691576</v>
+        <v>125755473</v>
       </c>
       <c r="B109" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483361</v>
+        <v>483182</v>
       </c>
       <c r="R109" t="n">
-        <v>6829179</v>
+        <v>6829175</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11204,52 +11229,46 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF109" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125746064</v>
+        <v>125755474</v>
       </c>
       <c r="B110" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -11273,14 +11292,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483474</v>
+        <v>483188</v>
       </c>
       <c r="R110" t="n">
-        <v>6829119</v>
+        <v>6829143</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11327,26 +11346,26 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125746931</v>
+        <v>125755475</v>
       </c>
       <c r="B111" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -11370,14 +11389,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483156</v>
+        <v>483169</v>
       </c>
       <c r="R111" t="n">
-        <v>6828728</v>
+        <v>6829132</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11412,11 +11431,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I en radie av ca 50 meter!</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -11429,68 +11443,60 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125745158</v>
+        <v>125755478</v>
       </c>
       <c r="B112" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483359</v>
+        <v>483147</v>
       </c>
       <c r="R112" t="n">
-        <v>6829093</v>
+        <v>6829095</v>
       </c>
       <c r="S112" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11534,22 +11540,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125745798</v>
+        <v>125755533</v>
       </c>
       <c r="B113" t="n">
-        <v>79598</v>
+        <v>78730</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11557,34 +11563,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Skidbäcksmyran, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483474</v>
+        <v>483472</v>
       </c>
       <c r="R113" t="n">
-        <v>6829119</v>
+        <v>6829305</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,22 +11637,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125747349</v>
+        <v>125755453</v>
       </c>
       <c r="B114" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11654,34 +11660,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>482981</v>
+        <v>482979</v>
       </c>
       <c r="R114" t="n">
-        <v>6828687</v>
+        <v>6829140</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,44 +11734,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125745325</v>
+        <v>125691576</v>
       </c>
       <c r="B115" t="n">
-        <v>91406</v>
+        <v>79946</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11774,17 +11780,17 @@
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483279</v>
+        <v>483361</v>
       </c>
       <c r="R115" t="n">
-        <v>6829148</v>
+        <v>6829179</v>
       </c>
       <c r="S115" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11808,19 +11814,24 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
@@ -11841,10 +11852,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125744923</v>
+        <v>125745798</v>
       </c>
       <c r="B116" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11852,40 +11863,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Skidbäcksmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483126</v>
+        <v>483474</v>
       </c>
       <c r="R116" t="n">
-        <v>6829064</v>
+        <v>6829119</v>
       </c>
       <c r="S116" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11923,7 +11931,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -11942,10 +11949,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125746848</v>
+        <v>125755411</v>
       </c>
       <c r="B117" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11953,34 +11960,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483247</v>
+        <v>482945</v>
       </c>
       <c r="R117" t="n">
-        <v>6828848</v>
+        <v>6829125</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12027,22 +12034,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125747249</v>
+        <v>125755416</v>
       </c>
       <c r="B118" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12050,34 +12057,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483032</v>
+        <v>483454</v>
       </c>
       <c r="R118" t="n">
-        <v>6828658</v>
+        <v>6829082</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12112,11 +12119,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter, rikligt!</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12129,22 +12131,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125747099</v>
+        <v>125755444</v>
       </c>
       <c r="B119" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12152,34 +12154,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483090</v>
+        <v>483272</v>
       </c>
       <c r="R119" t="n">
-        <v>6828658</v>
+        <v>6829286</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12226,57 +12228,57 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125748935</v>
+        <v>125755436</v>
       </c>
       <c r="B120" t="n">
-        <v>80083</v>
+        <v>80461</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>483071</v>
+        <v>483303</v>
       </c>
       <c r="R120" t="n">
-        <v>6828797</v>
+        <v>6829290</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12323,39 +12325,39 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125746158</v>
+        <v>125755530</v>
       </c>
       <c r="B121" t="n">
-        <v>78980</v>
+        <v>80467</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -12366,14 +12368,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>483342</v>
+        <v>483303</v>
       </c>
       <c r="R121" t="n">
-        <v>6828971</v>
+        <v>6829288</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12420,62 +12422,57 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125748016</v>
+        <v>125755532</v>
       </c>
       <c r="B122" t="n">
-        <v>57657</v>
+        <v>80467</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>483071</v>
+        <v>483294</v>
       </c>
       <c r="R122" t="n">
-        <v>6828797</v>
+        <v>6829294</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12522,60 +12519,68 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125747880</v>
+        <v>125745158</v>
       </c>
       <c r="B123" t="n">
-        <v>78980</v>
+        <v>57950</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483012</v>
+        <v>483359</v>
       </c>
       <c r="R123" t="n">
-        <v>6828723</v>
+        <v>6829093</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12631,45 +12636,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125746359</v>
+        <v>125755435</v>
       </c>
       <c r="B124" t="n">
-        <v>78980</v>
+        <v>58439</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483265</v>
+        <v>483450</v>
       </c>
       <c r="R124" t="n">
-        <v>6828852</v>
+        <v>6829302</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12716,22 +12721,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125746396</v>
+        <v>125755433</v>
       </c>
       <c r="B125" t="n">
-        <v>78739</v>
+        <v>58114</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12739,34 +12744,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483265</v>
+        <v>483307</v>
       </c>
       <c r="R125" t="n">
-        <v>6828852</v>
+        <v>6829287</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12813,39 +12818,39 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125747874</v>
+        <v>125755458</v>
       </c>
       <c r="B126" t="n">
-        <v>57657</v>
+        <v>58636</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>103044</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -12854,21 +12859,16 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Abborrsjöbäcken, Dlr</t>
+          <t>Aborrsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483012</v>
+        <v>483319</v>
       </c>
       <c r="R126" t="n">
-        <v>6828723</v>
+        <v>6829293</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12915,15 +12915,209 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125755427</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Aborrsjöbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>483472</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6829305</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>125755434</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Aborrsjöbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>483189</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6829144</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25389-2025 artfynd.xlsx
+++ b/artfynd/A 25389-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY128"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755528</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755529</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755430</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755426</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125744772</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755438</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755447</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755448</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755452</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755409</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755410</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697662</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134087680</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,6 +2132,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134098828</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2179,6 +2254,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134100090</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2276,6 +2356,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755439</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2373,6 +2458,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755443</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2470,6 +2560,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755429</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755417</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2664,6 +2764,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755418</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2761,6 +2866,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755419</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2858,6 +2968,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755421</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2955,6 +3070,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755422</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3052,6 +3172,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755424</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3149,6 +3274,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755522</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3246,6 +3376,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755523</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3343,6 +3478,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755525</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3440,6 +3580,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755526</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3537,6 +3682,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755459</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3638,6 +3788,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125745325</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3735,6 +3890,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755460</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3832,6 +3992,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755437</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3929,6 +4094,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755520</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4030,6 +4200,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125744889</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4127,6 +4302,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125745710</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4224,6 +4404,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125746083</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4321,6 +4506,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125746359</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4418,6 +4608,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125746416</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4520,6 +4715,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125746931</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4617,6 +4817,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747099</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4719,6 +4924,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747249</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4816,6 +5026,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747349</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4913,6 +5128,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747880</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5015,6 +5235,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755462</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5112,6 +5337,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755463</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5209,6 +5439,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755464</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5306,6 +5541,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755466</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5403,6 +5643,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755468</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5500,6 +5745,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755469</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5597,6 +5847,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755471</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5694,6 +5949,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755472</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5791,6 +6051,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755473</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5888,6 +6153,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755474</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5985,6 +6255,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755475</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6082,6 +6357,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755478</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6179,6 +6459,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755479</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6276,6 +6561,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755480</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6373,6 +6663,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755481</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6470,6 +6765,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755482</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6567,6 +6867,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755483</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6664,6 +6969,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755484</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6761,6 +7071,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755485</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6858,6 +7173,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755486</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6955,6 +7275,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755488</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7052,6 +7377,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755489</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7149,6 +7479,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755490</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7246,6 +7581,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755491</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7343,6 +7683,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755492</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7440,6 +7785,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755493</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7537,6 +7887,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755494</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7634,6 +7989,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755496</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7731,6 +8091,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755497</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7828,6 +8193,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755498</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7925,6 +8295,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755500</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8022,6 +8397,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755501</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8119,6 +8499,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755502</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8216,6 +8601,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755503</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8313,6 +8703,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755504</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8410,6 +8805,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755506</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8507,6 +8907,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755507</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8604,6 +9009,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755508</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8701,6 +9111,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755510</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8798,6 +9213,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755511</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8895,6 +9315,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755512</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8992,6 +9417,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755513</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9089,6 +9519,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755514</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9186,6 +9621,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755515</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9283,6 +9723,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755516</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9380,6 +9825,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755517</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9477,6 +9927,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755518</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9574,6 +10029,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755533</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9671,6 +10131,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755451</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9768,6 +10233,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755453</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9865,6 +10335,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755455</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9962,6 +10437,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755456</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10068,6 +10548,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125691576</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10165,6 +10650,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125745798</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10262,6 +10752,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755411</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10359,6 +10854,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755412</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10456,6 +10956,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755413</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10553,6 +11058,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755414</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10650,6 +11160,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755415</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10747,6 +11262,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755416</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10844,6 +11364,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125748935</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10941,6 +11466,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755444</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11038,6 +11568,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755445</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11135,6 +11670,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755446</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11232,6 +11772,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755436</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11329,6 +11874,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755530</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11426,6 +11976,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755532</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11531,6 +12086,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125745158</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11633,6 +12193,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747874</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11735,6 +12300,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125748016</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11842,6 +12412,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755536</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11944,6 +12519,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755431</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12046,6 +12626,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755432</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12148,6 +12733,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755457</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12245,6 +12835,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755435</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12342,6 +12937,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755433</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12439,6 +13039,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755458</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12536,6 +13141,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125746396</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12633,6 +13243,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755440</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12730,6 +13345,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755441</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12827,6 +13447,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755442</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12924,6 +13549,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755427</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13021,6 +13651,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755428</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13118,8 +13753,142 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755434</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>